--- a/docs/Chiraath-Summary-May26.xlsx
+++ b/docs/Chiraath-Summary-May26.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/anooppremachandran/Desktop/CHIRAATH/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BA0C66F7-6348-4B46-A32F-4277A9C2859D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7F42F432-6B06-E442-A201-74085750FDE0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="18000" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="18000" tabRatio="500" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Notes" sheetId="1" r:id="rId1"/>
@@ -46,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2245" uniqueCount="902">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2255" uniqueCount="906">
   <si>
     <t>Notes:</t>
   </si>
@@ -2731,16 +2731,42 @@
     <t>CHR-119 - Black</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <u/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Trebuchet MS"/>
-        <family val="2"/>
-      </rPr>
-      <t>Old batch:</t>
-    </r>
+    <t>Lily Kutty (Kottayam)</t>
+  </si>
+  <si>
+    <t>Sindhu (Pkd)</t>
+  </si>
+  <si>
+    <t>CHR-119 - Green</t>
+  </si>
+  <si>
+    <t>CHR-119 - Maroon</t>
+  </si>
+  <si>
+    <t>royal blue/rani pink, parrot green/red, deep red/bottle green</t>
+  </si>
+  <si>
+    <t>Matka Silk Saree Collection</t>
+  </si>
+  <si>
+    <t>Soft Silk Saree Collection</t>
+  </si>
+  <si>
+    <t>Tussar Silk Collection</t>
+  </si>
+  <si>
+    <t>Tissue Silk Saree Collection</t>
+  </si>
+  <si>
+    <t>Chanderi Silk Saree Collection</t>
+  </si>
+  <si>
+    <t>Aasha (EKM)</t>
+  </si>
+  <si>
+    <t>Boosting - March &amp; April</t>
+  </si>
+  <si>
     <r>
       <rPr>
         <sz val="11"/>
@@ -2749,7 +2775,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">  Off white (1) 
+      <t xml:space="preserve">
 </t>
     </r>
     <r>
@@ -2791,41 +2817,8 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve"> Black(7), White(5), Rani Pink(2)</t>
+      <t xml:space="preserve"> Black(7), White(5), Rani Pink(1)</t>
     </r>
-  </si>
-  <si>
-    <t>Lily Kutty (Kottayam)</t>
-  </si>
-  <si>
-    <t>Sindhu (Pkd)</t>
-  </si>
-  <si>
-    <t>CHR-119 - Green</t>
-  </si>
-  <si>
-    <t>CHR-119 - Maroon</t>
-  </si>
-  <si>
-    <t>royal blue/rani pink, parrot green/red, deep red/bottle green</t>
-  </si>
-  <si>
-    <t>Matka Silk Saree Collection</t>
-  </si>
-  <si>
-    <t>Soft Silk Saree Collection</t>
-  </si>
-  <si>
-    <t>Tussar Silk Collection</t>
-  </si>
-  <si>
-    <t>Tissue Silk Saree Collection</t>
-  </si>
-  <si>
-    <t>Chanderi Silk Saree Collection</t>
-  </si>
-  <si>
-    <t>Aasha (EKM)</t>
   </si>
   <si>
     <r>
@@ -2876,11 +2869,20 @@
         <rFont val="Trebuchet MS"/>
         <family val="2"/>
       </rPr>
-      <t>, Gopika - Black, Aji Roy - Black, Aji Roy - Mustard, Lili Kutty - Maroon, Sindhu - Black, Asha - Green</t>
+      <t>, Gopika - Black, Aji Roy - Black, Aji Roy - Mustard, Lili Kutty - Maroon, Sindhu - Black, Asha - Green, Soorya - Rani Pink, Asha Latha - Offwhite</t>
     </r>
   </si>
   <si>
-    <t>Boosting - March &amp; April</t>
+    <t>Soorya (Perumbavoor)</t>
+  </si>
+  <si>
+    <t>CHR-119 - Rani Pink</t>
+  </si>
+  <si>
+    <t>Asha Latha</t>
+  </si>
+  <si>
+    <t>CHR-119 - Off white</t>
   </si>
 </sst>
 </file>
@@ -3813,7 +3815,7 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="3"/>
                 <c:pt idx="0">
-                  <c:v>158</c:v>
+                  <c:v>163</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>81</c:v>
@@ -3916,7 +3918,7 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="3"/>
                 <c:pt idx="0">
-                  <c:v>114</c:v>
+                  <c:v>109</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>64</c:v>
@@ -4249,7 +4251,7 @@
                   <c:v>66578</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>76776.529999999984</c:v>
+                  <c:v>74681.763333333321</c:v>
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>1829</c:v>
@@ -4736,7 +4738,7 @@
                   <c:v>56636</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0</c:v>
+                  <c:v>1389</c:v>
                 </c:pt>
                 <c:pt idx="5">
                   <c:v>0</c:v>
@@ -5176,7 +5178,7 @@
                   <c:v>-14366</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0</c:v>
+                  <c:v>1389</c:v>
                 </c:pt>
                 <c:pt idx="5">
                   <c:v>0</c:v>
@@ -5646,10 +5648,10 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="2"/>
                 <c:pt idx="0">
-                  <c:v>241</c:v>
+                  <c:v>246</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>183</c:v>
+                  <c:v>178</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6836,7 +6838,7 @@
       </c>
       <c r="B4" s="10">
         <f>SUMIFS(Sales!C:C, Sales!I:I, "Completed")</f>
-        <v>290079</v>
+        <v>291468</v>
       </c>
       <c r="E4" s="9" t="str">
         <f>PartnerShares!A3</f>
@@ -6853,7 +6855,7 @@
       </c>
       <c r="B5" s="12">
         <f>SUM(Sales!C:C)</f>
-        <v>303448</v>
+        <v>304837</v>
       </c>
       <c r="E5" s="11" t="str">
         <f>PartnerShares!A4</f>
@@ -6870,7 +6872,7 @@
       </c>
       <c r="B6" s="10">
         <f>B4-B3</f>
-        <v>-60214</v>
+        <v>-58825</v>
       </c>
       <c r="E6" s="9" t="str">
         <f>PartnerShares!A5</f>
@@ -7082,15 +7084,15 @@
       </c>
       <c r="B26" s="10">
         <f>'Cash Pool'!B4</f>
-        <v>269130</v>
+        <v>270519</v>
       </c>
       <c r="C26" s="10">
         <f>'Cash Pool'!D4</f>
-        <v>96712.338599999988</v>
+        <v>97175.431199999992</v>
       </c>
       <c r="D26" s="10">
         <f>'Cash Pool'!E4</f>
-        <v>172417.66140000001</v>
+        <v>173343.56880000001</v>
       </c>
       <c r="E26" s="10">
         <f>'Cash Pool'!F4</f>
@@ -7098,11 +7100,11 @@
       </c>
       <c r="F26" s="13">
         <f>'Cash Pool'!G4</f>
-        <v>35107.635399999999</v>
+        <v>36033.542799999996</v>
       </c>
       <c r="G26" s="17" t="str">
         <f>IF(ROUND(F26,0)&gt;0,"Pay ₹"&amp;TEXT(ABS(F26),"#,##0"),IF(ROUND(F26,0)&lt;0,"Receive ₹"&amp;TEXT(ABS(F26),"#,##0"),"✓ Settled"))</f>
-        <v>Pay ₹35,108</v>
+        <v>Pay ₹36,034</v>
       </c>
     </row>
     <row r="27" spans="1:7" ht="13.5" customHeight="1">
@@ -7116,11 +7118,11 @@
       </c>
       <c r="C27" s="12">
         <f>'Cash Pool'!D5</f>
-        <v>96654.322799999994</v>
+        <v>97117.137600000002</v>
       </c>
       <c r="D27" s="12">
         <f>'Cash Pool'!E5</f>
-        <v>-88235.322799999994</v>
+        <v>-88698.137600000002</v>
       </c>
       <c r="E27" s="12">
         <f>'Cash Pool'!F5</f>
@@ -7128,11 +7130,11 @@
       </c>
       <c r="F27" s="14">
         <f>'Cash Pool'!G5</f>
-        <v>-16648.280799999993</v>
+        <v>-17111.095600000001</v>
       </c>
       <c r="G27" s="18" t="str">
         <f>IF(ROUND(F27,0)&gt;0,"Pay ₹"&amp;TEXT(ABS(F27),"#,##0"),IF(ROUND(F27,0)&lt;0,"Receive ₹"&amp;TEXT(ABS(F27),"#,##0"),"✓ Settled"))</f>
-        <v>Receive ₹16,648</v>
+        <v>Receive ₹17,111</v>
       </c>
     </row>
     <row r="28" spans="1:7" ht="13.5" customHeight="1">
@@ -7146,11 +7148,11 @@
       </c>
       <c r="C28" s="10">
         <f>'Cash Pool'!D6</f>
-        <v>96712.338599999988</v>
+        <v>97175.431199999992</v>
       </c>
       <c r="D28" s="10">
         <f>'Cash Pool'!E6</f>
-        <v>-84182.338599999988</v>
+        <v>-84645.431199999992</v>
       </c>
       <c r="E28" s="10">
         <f>'Cash Pool'!F6</f>
@@ -7158,11 +7160,11 @@
       </c>
       <c r="F28" s="13">
         <f>'Cash Pool'!G6</f>
-        <v>-18459.354599999977</v>
+        <v>-18922.447199999981</v>
       </c>
       <c r="G28" s="16" t="str">
         <f>IF(ROUND(F28,0)&gt;0,"Pay ₹"&amp;TEXT(ABS(F28),"#,##0"),IF(ROUND(F28,0)&lt;0,"Receive ₹"&amp;TEXT(ABS(F28),"#,##0"),"✓ Settled"))</f>
-        <v>Receive ₹18,459</v>
+        <v>Receive ₹18,922</v>
       </c>
     </row>
     <row r="32" spans="1:7" ht="15.75" customHeight="1">
@@ -7274,7 +7276,7 @@
       </c>
       <c r="B3" s="20">
         <f ca="1">TODAY()</f>
-        <v>46143</v>
+        <v>46146</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="15" customHeight="1">
@@ -7290,7 +7292,7 @@
       </c>
       <c r="E5" s="21">
         <f>Summary!B4</f>
-        <v>290079</v>
+        <v>291468</v>
       </c>
     </row>
     <row r="6" spans="1:8" ht="15" customHeight="1">
@@ -7299,14 +7301,14 @@
       </c>
       <c r="B6" s="21">
         <f>Summary!B6</f>
-        <v>-60214</v>
+        <v>-58825</v>
       </c>
       <c r="D6" s="19" t="s">
         <v>71</v>
       </c>
       <c r="E6" s="21">
         <f>SUMIFS(INVENTORY!K:K, INVENTORY!N:N, "&lt;&gt;Sold Out")</f>
-        <v>141112.72999999998</v>
+        <v>139017.96333333332</v>
       </c>
     </row>
     <row r="7" spans="1:8" ht="15.75" customHeight="1">
@@ -7358,7 +7360,7 @@
       </c>
       <c r="G10" s="21">
         <f>SUM(INVENTORY!F:F)</f>
-        <v>241</v>
+        <v>246</v>
       </c>
     </row>
     <row r="11" spans="1:8" ht="15" customHeight="1">
@@ -7382,7 +7384,7 @@
       </c>
       <c r="G11" s="27">
         <f>SUM(INVENTORY!G:G)</f>
-        <v>183</v>
+        <v>178</v>
       </c>
     </row>
     <row r="12" spans="1:8" ht="15" customHeight="1">
@@ -7429,11 +7431,11 @@
       </c>
       <c r="C14" s="21">
         <f>IFERROR(SUMPRODUCT((TEXT(Sales!$A$2:$A$996,"MMM")=$A14)*(YEAR(Sales!$A$2:$A$996)=$B$7)*Sales!$C$2:$C$996),0)</f>
-        <v>0</v>
+        <v>1389</v>
       </c>
       <c r="D14" s="21">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1389</v>
       </c>
     </row>
     <row r="15" spans="1:8" ht="15" customHeight="1">
@@ -7578,11 +7580,11 @@
       </c>
       <c r="G47" s="30">
         <f>SUMIF(INVENTORY!C:C, F47, INVENTORY!F:F)</f>
-        <v>158</v>
+        <v>163</v>
       </c>
       <c r="H47" s="30">
         <f>SUMIF(INVENTORY!C:C, F47, INVENTORY!G:G)</f>
-        <v>114</v>
+        <v>109</v>
       </c>
       <c r="J47" s="30" t="s">
         <v>96</v>
@@ -7609,7 +7611,7 @@
       </c>
       <c r="K48" s="31">
         <f t="array" ref="K48">SUMPRODUCT((INVENTORY!$C$2:$C$477=J48)*(INVENTORY!$D$2:$D$477)*(INVENTORY!$G$2:$G$477))</f>
-        <v>76776.529999999984</v>
+        <v>74681.763333333321</v>
       </c>
     </row>
     <row r="49" spans="5:12" ht="15" customHeight="1">
@@ -8702,7 +8704,7 @@
         <v>4000</v>
       </c>
       <c r="D71" s="39" t="s">
-        <v>901</v>
+        <v>899</v>
       </c>
     </row>
     <row r="72" spans="1:4" ht="15" customHeight="1">
@@ -12632,7 +12634,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="70" spans="1:9" ht="28">
+    <row r="70" spans="1:9" ht="14">
       <c r="A70" s="75">
         <v>46011</v>
       </c>
@@ -15442,7 +15444,7 @@
         <v>46142</v>
       </c>
       <c r="B183" s="80" t="s">
-        <v>889</v>
+        <v>888</v>
       </c>
       <c r="C183" s="81">
         <v>690</v>
@@ -15456,7 +15458,7 @@
       <c r="F183" s="91"/>
       <c r="G183" s="91"/>
       <c r="H183" s="92" t="s">
-        <v>892</v>
+        <v>891</v>
       </c>
       <c r="I183" s="80" t="s">
         <v>140</v>
@@ -15467,7 +15469,7 @@
         <v>46142</v>
       </c>
       <c r="B184" s="76" t="s">
-        <v>890</v>
+        <v>889</v>
       </c>
       <c r="C184" s="77">
         <v>690</v>
@@ -15492,7 +15494,7 @@
         <v>46142</v>
       </c>
       <c r="B185" s="80" t="s">
-        <v>899</v>
+        <v>898</v>
       </c>
       <c r="C185" s="81">
         <v>609</v>
@@ -15506,33 +15508,61 @@
       <c r="F185" s="91"/>
       <c r="G185" s="91"/>
       <c r="H185" s="92" t="s">
-        <v>891</v>
+        <v>890</v>
       </c>
       <c r="I185" s="80" t="s">
         <v>140</v>
       </c>
     </row>
-    <row r="186" spans="1:9">
-      <c r="A186" s="79"/>
-      <c r="B186" s="80"/>
-      <c r="C186" s="81"/>
-      <c r="D186" s="80"/>
-      <c r="E186" s="80"/>
+    <row r="186" spans="1:9" ht="14">
+      <c r="A186" s="79">
+        <v>46144</v>
+      </c>
+      <c r="B186" s="80" t="s">
+        <v>902</v>
+      </c>
+      <c r="C186" s="81">
+        <v>699</v>
+      </c>
+      <c r="D186" s="80" t="s">
+        <v>154</v>
+      </c>
+      <c r="E186" s="80" t="s">
+        <v>49</v>
+      </c>
       <c r="F186" s="91"/>
       <c r="G186" s="91"/>
-      <c r="H186" s="92"/>
-      <c r="I186" s="80"/>
-    </row>
-    <row r="187" spans="1:9">
-      <c r="A187" s="75"/>
-      <c r="B187" s="76"/>
-      <c r="C187" s="77"/>
-      <c r="D187" s="76"/>
-      <c r="E187" s="76"/>
+      <c r="H186" s="92" t="s">
+        <v>903</v>
+      </c>
+      <c r="I186" s="80" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="187" spans="1:9" ht="14">
+      <c r="A187" s="75">
+        <v>46144</v>
+      </c>
+      <c r="B187" s="76" t="s">
+        <v>904</v>
+      </c>
+      <c r="C187" s="77">
+        <v>690</v>
+      </c>
+      <c r="D187" s="76" t="s">
+        <v>154</v>
+      </c>
+      <c r="E187" s="76" t="s">
+        <v>49</v>
+      </c>
       <c r="F187" s="76"/>
       <c r="G187" s="76"/>
-      <c r="H187" s="78"/>
-      <c r="I187" s="76"/>
+      <c r="H187" s="78" t="s">
+        <v>905</v>
+      </c>
+      <c r="I187" s="76" t="s">
+        <v>140</v>
+      </c>
     </row>
     <row r="188" spans="1:9">
       <c r="A188" s="79"/>
@@ -26159,7 +26189,7 @@
       <c r="S119" s="42"/>
       <c r="T119" s="42"/>
     </row>
-    <row r="120" spans="1:246" ht="90">
+    <row r="120" spans="1:246" ht="105">
       <c r="A120" s="48" t="s">
         <v>640</v>
       </c>
@@ -26176,10 +26206,10 @@
         <v>699</v>
       </c>
       <c r="F120" s="49">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="G120" s="49">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="H120" s="48">
         <f t="shared" si="9"/>
@@ -26191,14 +26221,14 @@
       </c>
       <c r="J120" s="48">
         <f t="shared" si="10"/>
-        <v>5446.3933333333289</v>
+        <v>7541.1599999999935</v>
       </c>
       <c r="K120" s="48">
         <f t="shared" si="11"/>
-        <v>15082.319999999987</v>
+        <v>12987.553333333322</v>
       </c>
       <c r="L120" s="94" t="s">
-        <v>900</v>
+        <v>901</v>
       </c>
       <c r="M120" s="48" t="s">
         <v>49</v>
@@ -26207,8 +26237,8 @@
         <v>451</v>
       </c>
       <c r="O120" s="48"/>
-      <c r="P120" s="94" t="s">
-        <v>888</v>
+      <c r="P120" s="48" t="s">
+        <v>900</v>
       </c>
       <c r="Q120" s="48"/>
       <c r="R120" s="48"/>
@@ -29776,7 +29806,7 @@
         <v>868</v>
       </c>
       <c r="B176" s="48" t="s">
-        <v>895</v>
+        <v>894</v>
       </c>
       <c r="C176" s="48" t="s">
         <v>95</v>
@@ -29828,7 +29858,7 @@
         <v>870</v>
       </c>
       <c r="B177" s="42" t="s">
-        <v>896</v>
+        <v>895</v>
       </c>
       <c r="C177" s="42" t="s">
         <v>95</v>
@@ -29880,7 +29910,7 @@
         <v>871</v>
       </c>
       <c r="B178" s="48" t="s">
-        <v>897</v>
+        <v>896</v>
       </c>
       <c r="C178" s="48" t="s">
         <v>95</v>
@@ -29932,7 +29962,7 @@
         <v>872</v>
       </c>
       <c r="B179" s="42" t="s">
-        <v>898</v>
+        <v>897</v>
       </c>
       <c r="C179" s="42" t="s">
         <v>95</v>
@@ -29984,7 +30014,7 @@
         <v>873</v>
       </c>
       <c r="B180" s="48" t="s">
-        <v>894</v>
+        <v>893</v>
       </c>
       <c r="C180" s="48" t="s">
         <v>95</v>
@@ -30024,7 +30054,7 @@
       </c>
       <c r="O180" s="48"/>
       <c r="P180" s="48" t="s">
-        <v>893</v>
+        <v>892</v>
       </c>
       <c r="Q180" s="48"/>
       <c r="R180" s="48"/>
@@ -34851,7 +34881,7 @@
       </c>
       <c r="B4" s="9">
         <f>IFERROR(SUMIFS(Sales!$C:$C,Sales!$E:$E,$A4,Sales!$I:$I,"Completed"),0)</f>
-        <v>269130</v>
+        <v>270519</v>
       </c>
       <c r="C4" s="9">
         <f>VLOOKUP($A4,PartnerShares!$A$3:$B$5,2,FALSE())</f>
@@ -34859,11 +34889,11 @@
       </c>
       <c r="D4" s="9">
         <f>Summary!$B$4*C4</f>
-        <v>96712.338599999988</v>
+        <v>97175.431199999992</v>
       </c>
       <c r="E4" s="9">
         <f>B4-D4</f>
-        <v>172417.66140000001</v>
+        <v>173343.56880000001</v>
       </c>
       <c r="F4" s="9">
         <f>IFERROR(SUMIFS(PartnerShares!$E$13:$E$499,PartnerShares!$D$13:$D$499,$A4,PartnerShares!$B$13:$B$499,"Cash"),0)-IFERROR(SUMIFS(PartnerShares!$E$13:$E$499,PartnerShares!$C$13:$C$499,$A4,PartnerShares!$B$13:$B$499,"Cash"),0)</f>
@@ -34871,7 +34901,7 @@
       </c>
       <c r="G4" s="69">
         <f>E4+F4</f>
-        <v>35107.635399999999</v>
+        <v>36033.542799999996</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="13.5" customHeight="1">
@@ -34888,11 +34918,11 @@
       </c>
       <c r="D5" s="11">
         <f>Summary!$B$4*C5</f>
-        <v>96654.322799999994</v>
+        <v>97117.137600000002</v>
       </c>
       <c r="E5" s="11">
         <f>B5-D5</f>
-        <v>-88235.322799999994</v>
+        <v>-88698.137600000002</v>
       </c>
       <c r="F5" s="11">
         <f>IFERROR(SUMIFS(PartnerShares!$E$13:$E$499,PartnerShares!$D$13:$D$499,$A5,PartnerShares!$B$13:$B$499,"Cash"),0)-IFERROR(SUMIFS(PartnerShares!$E$13:$E$499,PartnerShares!$C$13:$C$499,$A5,PartnerShares!$B$13:$B$499,"Cash"),0)</f>
@@ -34900,7 +34930,7 @@
       </c>
       <c r="G5" s="70">
         <f>E5+F5</f>
-        <v>-16648.280799999993</v>
+        <v>-17111.095600000001</v>
       </c>
     </row>
     <row r="6" spans="1:7" ht="13.5" customHeight="1">
@@ -34917,11 +34947,11 @@
       </c>
       <c r="D6" s="9">
         <f>Summary!$B$4*C6</f>
-        <v>96712.338599999988</v>
+        <v>97175.431199999992</v>
       </c>
       <c r="E6" s="9">
         <f>B6-D6</f>
-        <v>-84182.338599999988</v>
+        <v>-84645.431199999992</v>
       </c>
       <c r="F6" s="9">
         <f>IFERROR(SUMIFS(PartnerShares!$E$13:$E$499,PartnerShares!$D$13:$D$499,$A6,PartnerShares!$B$13:$B$499,"Cash"),0)-IFERROR(SUMIFS(PartnerShares!$E$13:$E$499,PartnerShares!$C$13:$C$499,$A6,PartnerShares!$B$13:$B$499,"Cash"),0)</f>
@@ -34929,7 +34959,7 @@
       </c>
       <c r="G6" s="69">
         <f>E6+F6</f>
-        <v>-18459.354599999977</v>
+        <v>-18922.447199999981</v>
       </c>
     </row>
     <row r="9" spans="1:7" ht="13.5" customHeight="1">

--- a/docs/Chiraath-Summary-May26.xlsx
+++ b/docs/Chiraath-Summary-May26.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/anooppremachandran/Desktop/CHIRAATH/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7F42F432-6B06-E442-A201-74085750FDE0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1880A21F-87A7-CA4C-87A0-12B7B6F7184F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="18000" tabRatio="500" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="18000" tabRatio="500" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Notes" sheetId="1" r:id="rId1"/>
@@ -46,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2255" uniqueCount="906">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2260" uniqueCount="908">
   <si>
     <t>Notes:</t>
   </si>
@@ -2646,14 +2646,6 @@
   </si>
   <si>
     <t>Sherin - Maroon/navy blue(1099)</t>
-  </si>
-  <si>
-    <t>Blue/bottle green - Saranya Hyd, Blue/red - Jothika, Mustard - Vineetha, Bottle Green/Golden Yellow - Swapna (Thrissur)-1200, Black/Golden yellow - Kavya(Kasargod) - 1200</t>
-  </si>
-  <si>
-    <t>Bottle Green/Golden Yellow - 2 
-Black/Golden Yellow - 1
-Navy Blue/Bottle Green - 2</t>
   </si>
   <si>
     <t>Kavya (Kasargod)</t>
@@ -2883,6 +2875,19 @@
   </si>
   <si>
     <t>CHR-119 - Off white</t>
+  </si>
+  <si>
+    <t>Subha</t>
+  </si>
+  <si>
+    <t>Matka - Black/Mustard yellow</t>
+  </si>
+  <si>
+    <t>Bottle Green/Golden Yellow - 2 
+Navy Blue/Bottle Green - 2</t>
+  </si>
+  <si>
+    <t>Blue/bottle green - Saranya Hyd, Blue/red - Jothika, Mustard - Vineetha, Bottle Green/Golden Yellow - Swapna (Thrissur)-1200, Black/Golden yellow - Kavya(Kasargod) - 1200, Back/Yellow - Subha - 1200</t>
   </si>
 </sst>
 </file>
@@ -3815,7 +3820,7 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="3"/>
                 <c:pt idx="0">
-                  <c:v>163</c:v>
+                  <c:v>164</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>81</c:v>
@@ -3918,7 +3923,7 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="3"/>
                 <c:pt idx="0">
-                  <c:v>109</c:v>
+                  <c:v>108</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>64</c:v>
@@ -4251,7 +4256,7 @@
                   <c:v>66578</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>74681.763333333321</c:v>
+                  <c:v>73962.763333333321</c:v>
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>1829</c:v>
@@ -4738,7 +4743,7 @@
                   <c:v>56636</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>1389</c:v>
+                  <c:v>2589</c:v>
                 </c:pt>
                 <c:pt idx="5">
                   <c:v>0</c:v>
@@ -5178,7 +5183,7 @@
                   <c:v>-14366</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>1389</c:v>
+                  <c:v>2589</c:v>
                 </c:pt>
                 <c:pt idx="5">
                   <c:v>0</c:v>
@@ -5648,10 +5653,10 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="2"/>
                 <c:pt idx="0">
-                  <c:v>246</c:v>
+                  <c:v>247</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>178</c:v>
+                  <c:v>177</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6838,7 +6843,7 @@
       </c>
       <c r="B4" s="10">
         <f>SUMIFS(Sales!C:C, Sales!I:I, "Completed")</f>
-        <v>291468</v>
+        <v>292668</v>
       </c>
       <c r="E4" s="9" t="str">
         <f>PartnerShares!A3</f>
@@ -6855,7 +6860,7 @@
       </c>
       <c r="B5" s="12">
         <f>SUM(Sales!C:C)</f>
-        <v>304837</v>
+        <v>306037</v>
       </c>
       <c r="E5" s="11" t="str">
         <f>PartnerShares!A4</f>
@@ -6872,7 +6877,7 @@
       </c>
       <c r="B6" s="10">
         <f>B4-B3</f>
-        <v>-58825</v>
+        <v>-57625</v>
       </c>
       <c r="E6" s="9" t="str">
         <f>PartnerShares!A5</f>
@@ -7084,15 +7089,15 @@
       </c>
       <c r="B26" s="10">
         <f>'Cash Pool'!B4</f>
-        <v>270519</v>
+        <v>271719</v>
       </c>
       <c r="C26" s="10">
         <f>'Cash Pool'!D4</f>
-        <v>97175.431199999992</v>
+        <v>97575.511199999994</v>
       </c>
       <c r="D26" s="10">
         <f>'Cash Pool'!E4</f>
-        <v>173343.56880000001</v>
+        <v>174143.48879999999</v>
       </c>
       <c r="E26" s="10">
         <f>'Cash Pool'!F4</f>
@@ -7100,11 +7105,11 @@
       </c>
       <c r="F26" s="13">
         <f>'Cash Pool'!G4</f>
-        <v>36033.542799999996</v>
+        <v>36833.462799999979</v>
       </c>
       <c r="G26" s="17" t="str">
         <f>IF(ROUND(F26,0)&gt;0,"Pay ₹"&amp;TEXT(ABS(F26),"#,##0"),IF(ROUND(F26,0)&lt;0,"Receive ₹"&amp;TEXT(ABS(F26),"#,##0"),"✓ Settled"))</f>
-        <v>Pay ₹36,034</v>
+        <v>Pay ₹36,833</v>
       </c>
     </row>
     <row r="27" spans="1:7" ht="13.5" customHeight="1">
@@ -7118,11 +7123,11 @@
       </c>
       <c r="C27" s="12">
         <f>'Cash Pool'!D5</f>
-        <v>97117.137600000002</v>
+        <v>97516.977599999998</v>
       </c>
       <c r="D27" s="12">
         <f>'Cash Pool'!E5</f>
-        <v>-88698.137600000002</v>
+        <v>-89097.977599999998</v>
       </c>
       <c r="E27" s="12">
         <f>'Cash Pool'!F5</f>
@@ -7130,11 +7135,11 @@
       </c>
       <c r="F27" s="14">
         <f>'Cash Pool'!G5</f>
-        <v>-17111.095600000001</v>
+        <v>-17510.935599999997</v>
       </c>
       <c r="G27" s="18" t="str">
         <f>IF(ROUND(F27,0)&gt;0,"Pay ₹"&amp;TEXT(ABS(F27),"#,##0"),IF(ROUND(F27,0)&lt;0,"Receive ₹"&amp;TEXT(ABS(F27),"#,##0"),"✓ Settled"))</f>
-        <v>Receive ₹17,111</v>
+        <v>Receive ₹17,511</v>
       </c>
     </row>
     <row r="28" spans="1:7" ht="13.5" customHeight="1">
@@ -7148,11 +7153,11 @@
       </c>
       <c r="C28" s="10">
         <f>'Cash Pool'!D6</f>
-        <v>97175.431199999992</v>
+        <v>97575.511199999994</v>
       </c>
       <c r="D28" s="10">
         <f>'Cash Pool'!E6</f>
-        <v>-84645.431199999992</v>
+        <v>-85045.511199999994</v>
       </c>
       <c r="E28" s="10">
         <f>'Cash Pool'!F6</f>
@@ -7160,11 +7165,11 @@
       </c>
       <c r="F28" s="13">
         <f>'Cash Pool'!G6</f>
-        <v>-18922.447199999981</v>
+        <v>-19322.527199999982</v>
       </c>
       <c r="G28" s="16" t="str">
         <f>IF(ROUND(F28,0)&gt;0,"Pay ₹"&amp;TEXT(ABS(F28),"#,##0"),IF(ROUND(F28,0)&lt;0,"Receive ₹"&amp;TEXT(ABS(F28),"#,##0"),"✓ Settled"))</f>
-        <v>Receive ₹18,922</v>
+        <v>Receive ₹19,323</v>
       </c>
     </row>
     <row r="32" spans="1:7" ht="15.75" customHeight="1">
@@ -7276,7 +7281,7 @@
       </c>
       <c r="B3" s="20">
         <f ca="1">TODAY()</f>
-        <v>46146</v>
+        <v>46147</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="15" customHeight="1">
@@ -7292,7 +7297,7 @@
       </c>
       <c r="E5" s="21">
         <f>Summary!B4</f>
-        <v>291468</v>
+        <v>292668</v>
       </c>
     </row>
     <row r="6" spans="1:8" ht="15" customHeight="1">
@@ -7301,14 +7306,14 @@
       </c>
       <c r="B6" s="21">
         <f>Summary!B6</f>
-        <v>-58825</v>
+        <v>-57625</v>
       </c>
       <c r="D6" s="19" t="s">
         <v>71</v>
       </c>
       <c r="E6" s="21">
         <f>SUMIFS(INVENTORY!K:K, INVENTORY!N:N, "&lt;&gt;Sold Out")</f>
-        <v>139017.96333333332</v>
+        <v>138298.96333333332</v>
       </c>
     </row>
     <row r="7" spans="1:8" ht="15.75" customHeight="1">
@@ -7360,7 +7365,7 @@
       </c>
       <c r="G10" s="21">
         <f>SUM(INVENTORY!F:F)</f>
-        <v>246</v>
+        <v>247</v>
       </c>
     </row>
     <row r="11" spans="1:8" ht="15" customHeight="1">
@@ -7384,7 +7389,7 @@
       </c>
       <c r="G11" s="27">
         <f>SUM(INVENTORY!G:G)</f>
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="12" spans="1:8" ht="15" customHeight="1">
@@ -7431,11 +7436,11 @@
       </c>
       <c r="C14" s="21">
         <f>IFERROR(SUMPRODUCT((TEXT(Sales!$A$2:$A$996,"MMM")=$A14)*(YEAR(Sales!$A$2:$A$996)=$B$7)*Sales!$C$2:$C$996),0)</f>
-        <v>1389</v>
+        <v>2589</v>
       </c>
       <c r="D14" s="21">
         <f t="shared" si="0"/>
-        <v>1389</v>
+        <v>2589</v>
       </c>
     </row>
     <row r="15" spans="1:8" ht="15" customHeight="1">
@@ -7580,11 +7585,11 @@
       </c>
       <c r="G47" s="30">
         <f>SUMIF(INVENTORY!C:C, F47, INVENTORY!F:F)</f>
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="H47" s="30">
         <f>SUMIF(INVENTORY!C:C, F47, INVENTORY!G:G)</f>
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="J47" s="30" t="s">
         <v>96</v>
@@ -7611,7 +7616,7 @@
       </c>
       <c r="K48" s="31">
         <f t="array" ref="K48">SUMPRODUCT((INVENTORY!$C$2:$C$477=J48)*(INVENTORY!$D$2:$D$477)*(INVENTORY!$G$2:$G$477))</f>
-        <v>74681.763333333321</v>
+        <v>73962.763333333321</v>
       </c>
     </row>
     <row r="49" spans="5:12" ht="15" customHeight="1">
@@ -8704,7 +8709,7 @@
         <v>4000</v>
       </c>
       <c r="D71" s="39" t="s">
-        <v>899</v>
+        <v>897</v>
       </c>
     </row>
     <row r="72" spans="1:4" ht="15" customHeight="1">
@@ -15344,7 +15349,7 @@
         <v>46140</v>
       </c>
       <c r="B179" s="80" t="s">
-        <v>863</v>
+        <v>861</v>
       </c>
       <c r="C179" s="81">
         <v>1200</v>
@@ -15358,7 +15363,7 @@
       <c r="F179" s="91"/>
       <c r="G179" s="91"/>
       <c r="H179" s="92" t="s">
-        <v>864</v>
+        <v>862</v>
       </c>
       <c r="I179" s="80" t="s">
         <v>140</v>
@@ -15369,7 +15374,7 @@
         <v>46140</v>
       </c>
       <c r="B180" s="76" t="s">
-        <v>866</v>
+        <v>864</v>
       </c>
       <c r="C180" s="77">
         <v>1899</v>
@@ -15383,7 +15388,7 @@
       <c r="F180" s="76"/>
       <c r="G180" s="76"/>
       <c r="H180" s="78" t="s">
-        <v>865</v>
+        <v>863</v>
       </c>
       <c r="I180" s="76" t="s">
         <v>334</v>
@@ -15394,7 +15399,7 @@
         <v>46141</v>
       </c>
       <c r="B181" s="80" t="s">
-        <v>884</v>
+        <v>882</v>
       </c>
       <c r="C181" s="81">
         <v>1380</v>
@@ -15408,7 +15413,7 @@
       <c r="F181" s="91"/>
       <c r="G181" s="91"/>
       <c r="H181" s="92" t="s">
-        <v>885</v>
+        <v>883</v>
       </c>
       <c r="I181" s="80" t="s">
         <v>140</v>
@@ -15419,7 +15424,7 @@
         <v>46141</v>
       </c>
       <c r="B182" s="76" t="s">
-        <v>886</v>
+        <v>884</v>
       </c>
       <c r="C182" s="77">
         <v>690</v>
@@ -15433,7 +15438,7 @@
       <c r="F182" s="76"/>
       <c r="G182" s="76"/>
       <c r="H182" s="78" t="s">
-        <v>887</v>
+        <v>885</v>
       </c>
       <c r="I182" s="76" t="s">
         <v>140</v>
@@ -15444,7 +15449,7 @@
         <v>46142</v>
       </c>
       <c r="B183" s="80" t="s">
-        <v>888</v>
+        <v>886</v>
       </c>
       <c r="C183" s="81">
         <v>690</v>
@@ -15458,7 +15463,7 @@
       <c r="F183" s="91"/>
       <c r="G183" s="91"/>
       <c r="H183" s="92" t="s">
-        <v>891</v>
+        <v>889</v>
       </c>
       <c r="I183" s="80" t="s">
         <v>140</v>
@@ -15469,7 +15474,7 @@
         <v>46142</v>
       </c>
       <c r="B184" s="76" t="s">
-        <v>889</v>
+        <v>887</v>
       </c>
       <c r="C184" s="77">
         <v>690</v>
@@ -15483,7 +15488,7 @@
       <c r="F184" s="76"/>
       <c r="G184" s="76"/>
       <c r="H184" s="78" t="s">
-        <v>887</v>
+        <v>885</v>
       </c>
       <c r="I184" s="76" t="s">
         <v>140</v>
@@ -15494,7 +15499,7 @@
         <v>46142</v>
       </c>
       <c r="B185" s="80" t="s">
-        <v>898</v>
+        <v>896</v>
       </c>
       <c r="C185" s="81">
         <v>609</v>
@@ -15508,7 +15513,7 @@
       <c r="F185" s="91"/>
       <c r="G185" s="91"/>
       <c r="H185" s="92" t="s">
-        <v>890</v>
+        <v>888</v>
       </c>
       <c r="I185" s="80" t="s">
         <v>140</v>
@@ -15519,7 +15524,7 @@
         <v>46144</v>
       </c>
       <c r="B186" s="80" t="s">
-        <v>902</v>
+        <v>900</v>
       </c>
       <c r="C186" s="81">
         <v>699</v>
@@ -15533,7 +15538,7 @@
       <c r="F186" s="91"/>
       <c r="G186" s="91"/>
       <c r="H186" s="92" t="s">
-        <v>903</v>
+        <v>901</v>
       </c>
       <c r="I186" s="80" t="s">
         <v>140</v>
@@ -15544,7 +15549,7 @@
         <v>46144</v>
       </c>
       <c r="B187" s="76" t="s">
-        <v>904</v>
+        <v>902</v>
       </c>
       <c r="C187" s="77">
         <v>690</v>
@@ -15558,22 +15563,36 @@
       <c r="F187" s="76"/>
       <c r="G187" s="76"/>
       <c r="H187" s="78" t="s">
-        <v>905</v>
+        <v>903</v>
       </c>
       <c r="I187" s="76" t="s">
         <v>140</v>
       </c>
     </row>
-    <row r="188" spans="1:9">
-      <c r="A188" s="79"/>
-      <c r="B188" s="80"/>
-      <c r="C188" s="81"/>
-      <c r="D188" s="80"/>
-      <c r="E188" s="80"/>
+    <row r="188" spans="1:9" ht="14">
+      <c r="A188" s="79">
+        <v>46145</v>
+      </c>
+      <c r="B188" s="80" t="s">
+        <v>904</v>
+      </c>
+      <c r="C188" s="81">
+        <v>1200</v>
+      </c>
+      <c r="D188" s="80" t="s">
+        <v>154</v>
+      </c>
+      <c r="E188" s="80" t="s">
+        <v>49</v>
+      </c>
       <c r="F188" s="91"/>
       <c r="G188" s="91"/>
-      <c r="H188" s="92"/>
-      <c r="I188" s="80"/>
+      <c r="H188" s="92" t="s">
+        <v>905</v>
+      </c>
+      <c r="I188" s="80" t="s">
+        <v>140</v>
+      </c>
     </row>
     <row r="189" spans="1:9">
       <c r="A189" s="75"/>
@@ -26228,7 +26247,7 @@
         <v>12987.553333333322</v>
       </c>
       <c r="L120" s="94" t="s">
-        <v>901</v>
+        <v>899</v>
       </c>
       <c r="M120" s="48" t="s">
         <v>49</v>
@@ -26238,7 +26257,7 @@
       </c>
       <c r="O120" s="48"/>
       <c r="P120" s="48" t="s">
-        <v>900</v>
+        <v>898</v>
       </c>
       <c r="Q120" s="48"/>
       <c r="R120" s="48"/>
@@ -28277,7 +28296,7 @@
       <c r="S146" s="48"/>
       <c r="T146" s="48"/>
     </row>
-    <row r="147" spans="1:20" ht="45" customHeight="1">
+    <row r="147" spans="1:20" ht="64" customHeight="1">
       <c r="A147" s="42" t="s">
         <v>711</v>
       </c>
@@ -28294,10 +28313,10 @@
         <v>1200</v>
       </c>
       <c r="F147" s="60">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G147" s="60">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H147" s="59">
         <f t="shared" si="12"/>
@@ -28309,14 +28328,14 @@
       </c>
       <c r="J147" s="59">
         <f t="shared" si="13"/>
-        <v>2876</v>
+        <v>3595</v>
       </c>
       <c r="K147" s="59">
         <f t="shared" si="14"/>
-        <v>5033</v>
+        <v>4314</v>
       </c>
       <c r="L147" s="42" t="s">
-        <v>861</v>
+        <v>907</v>
       </c>
       <c r="M147" s="42"/>
       <c r="N147" s="42" t="s">
@@ -28324,7 +28343,7 @@
       </c>
       <c r="O147" s="42"/>
       <c r="P147" s="42" t="s">
-        <v>862</v>
+        <v>906</v>
       </c>
       <c r="Q147" s="42"/>
       <c r="R147" s="42"/>
@@ -29803,10 +29822,10 @@
     </row>
     <row r="176" spans="1:20" ht="15">
       <c r="A176" s="48" t="s">
-        <v>868</v>
+        <v>866</v>
       </c>
       <c r="B176" s="48" t="s">
-        <v>894</v>
+        <v>892</v>
       </c>
       <c r="C176" s="48" t="s">
         <v>95</v>
@@ -29846,7 +29865,7 @@
       </c>
       <c r="O176" s="48"/>
       <c r="P176" s="48" t="s">
-        <v>867</v>
+        <v>865</v>
       </c>
       <c r="Q176" s="48"/>
       <c r="R176" s="48"/>
@@ -29855,10 +29874,10 @@
     </row>
     <row r="177" spans="1:20" ht="15">
       <c r="A177" s="42" t="s">
-        <v>870</v>
+        <v>868</v>
       </c>
       <c r="B177" s="42" t="s">
-        <v>895</v>
+        <v>893</v>
       </c>
       <c r="C177" s="42" t="s">
         <v>95</v>
@@ -29898,7 +29917,7 @@
       </c>
       <c r="O177" s="42"/>
       <c r="P177" s="42" t="s">
-        <v>869</v>
+        <v>867</v>
       </c>
       <c r="Q177" s="42"/>
       <c r="R177" s="42"/>
@@ -29907,10 +29926,10 @@
     </row>
     <row r="178" spans="1:20" ht="15">
       <c r="A178" s="48" t="s">
-        <v>871</v>
+        <v>869</v>
       </c>
       <c r="B178" s="48" t="s">
-        <v>896</v>
+        <v>894</v>
       </c>
       <c r="C178" s="48" t="s">
         <v>95</v>
@@ -29950,7 +29969,7 @@
       </c>
       <c r="O178" s="48"/>
       <c r="P178" s="48" t="s">
-        <v>882</v>
+        <v>880</v>
       </c>
       <c r="Q178" s="48"/>
       <c r="R178" s="48"/>
@@ -29959,10 +29978,10 @@
     </row>
     <row r="179" spans="1:20" ht="15">
       <c r="A179" s="42" t="s">
-        <v>872</v>
+        <v>870</v>
       </c>
       <c r="B179" s="42" t="s">
-        <v>897</v>
+        <v>895</v>
       </c>
       <c r="C179" s="42" t="s">
         <v>95</v>
@@ -30002,7 +30021,7 @@
       </c>
       <c r="O179" s="42"/>
       <c r="P179" s="42" t="s">
-        <v>883</v>
+        <v>881</v>
       </c>
       <c r="Q179" s="42"/>
       <c r="R179" s="42"/>
@@ -30011,10 +30030,10 @@
     </row>
     <row r="180" spans="1:20" ht="15">
       <c r="A180" s="48" t="s">
-        <v>873</v>
+        <v>871</v>
       </c>
       <c r="B180" s="48" t="s">
-        <v>893</v>
+        <v>891</v>
       </c>
       <c r="C180" s="48" t="s">
         <v>95</v>
@@ -30054,7 +30073,7 @@
       </c>
       <c r="O180" s="48"/>
       <c r="P180" s="48" t="s">
-        <v>892</v>
+        <v>890</v>
       </c>
       <c r="Q180" s="48"/>
       <c r="R180" s="48"/>
@@ -30063,7 +30082,7 @@
     </row>
     <row r="181" spans="1:20" ht="15">
       <c r="A181" s="42" t="s">
-        <v>874</v>
+        <v>872</v>
       </c>
       <c r="B181" s="42"/>
       <c r="C181" s="42"/>
@@ -30087,7 +30106,7 @@
     </row>
     <row r="182" spans="1:20" ht="15">
       <c r="A182" s="48" t="s">
-        <v>875</v>
+        <v>873</v>
       </c>
       <c r="B182" s="48"/>
       <c r="C182" s="48"/>
@@ -30111,7 +30130,7 @@
     </row>
     <row r="183" spans="1:20" ht="15">
       <c r="A183" s="42" t="s">
-        <v>876</v>
+        <v>874</v>
       </c>
       <c r="B183" s="42"/>
       <c r="C183" s="42"/>
@@ -30135,7 +30154,7 @@
     </row>
     <row r="184" spans="1:20" ht="15">
       <c r="A184" s="48" t="s">
-        <v>877</v>
+        <v>875</v>
       </c>
       <c r="B184" s="48"/>
       <c r="C184" s="48"/>
@@ -30159,7 +30178,7 @@
     </row>
     <row r="185" spans="1:20" ht="15">
       <c r="A185" s="42" t="s">
-        <v>878</v>
+        <v>876</v>
       </c>
       <c r="B185" s="42"/>
       <c r="C185" s="42"/>
@@ -30183,7 +30202,7 @@
     </row>
     <row r="186" spans="1:20" ht="15">
       <c r="A186" s="48" t="s">
-        <v>879</v>
+        <v>877</v>
       </c>
       <c r="B186" s="48"/>
       <c r="C186" s="48"/>
@@ -30207,7 +30226,7 @@
     </row>
     <row r="187" spans="1:20" ht="15">
       <c r="A187" s="42" t="s">
-        <v>880</v>
+        <v>878</v>
       </c>
       <c r="B187" s="42"/>
       <c r="C187" s="42"/>
@@ -30231,7 +30250,7 @@
     </row>
     <row r="188" spans="1:20" ht="15">
       <c r="A188" s="48" t="s">
-        <v>881</v>
+        <v>879</v>
       </c>
       <c r="B188" s="48"/>
       <c r="C188" s="48"/>
@@ -34881,7 +34900,7 @@
       </c>
       <c r="B4" s="9">
         <f>IFERROR(SUMIFS(Sales!$C:$C,Sales!$E:$E,$A4,Sales!$I:$I,"Completed"),0)</f>
-        <v>270519</v>
+        <v>271719</v>
       </c>
       <c r="C4" s="9">
         <f>VLOOKUP($A4,PartnerShares!$A$3:$B$5,2,FALSE())</f>
@@ -34889,11 +34908,11 @@
       </c>
       <c r="D4" s="9">
         <f>Summary!$B$4*C4</f>
-        <v>97175.431199999992</v>
+        <v>97575.511199999994</v>
       </c>
       <c r="E4" s="9">
         <f>B4-D4</f>
-        <v>173343.56880000001</v>
+        <v>174143.48879999999</v>
       </c>
       <c r="F4" s="9">
         <f>IFERROR(SUMIFS(PartnerShares!$E$13:$E$499,PartnerShares!$D$13:$D$499,$A4,PartnerShares!$B$13:$B$499,"Cash"),0)-IFERROR(SUMIFS(PartnerShares!$E$13:$E$499,PartnerShares!$C$13:$C$499,$A4,PartnerShares!$B$13:$B$499,"Cash"),0)</f>
@@ -34901,7 +34920,7 @@
       </c>
       <c r="G4" s="69">
         <f>E4+F4</f>
-        <v>36033.542799999996</v>
+        <v>36833.462799999979</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="13.5" customHeight="1">
@@ -34918,11 +34937,11 @@
       </c>
       <c r="D5" s="11">
         <f>Summary!$B$4*C5</f>
-        <v>97117.137600000002</v>
+        <v>97516.977599999998</v>
       </c>
       <c r="E5" s="11">
         <f>B5-D5</f>
-        <v>-88698.137600000002</v>
+        <v>-89097.977599999998</v>
       </c>
       <c r="F5" s="11">
         <f>IFERROR(SUMIFS(PartnerShares!$E$13:$E$499,PartnerShares!$D$13:$D$499,$A5,PartnerShares!$B$13:$B$499,"Cash"),0)-IFERROR(SUMIFS(PartnerShares!$E$13:$E$499,PartnerShares!$C$13:$C$499,$A5,PartnerShares!$B$13:$B$499,"Cash"),0)</f>
@@ -34930,7 +34949,7 @@
       </c>
       <c r="G5" s="70">
         <f>E5+F5</f>
-        <v>-17111.095600000001</v>
+        <v>-17510.935599999997</v>
       </c>
     </row>
     <row r="6" spans="1:7" ht="13.5" customHeight="1">
@@ -34947,11 +34966,11 @@
       </c>
       <c r="D6" s="9">
         <f>Summary!$B$4*C6</f>
-        <v>97175.431199999992</v>
+        <v>97575.511199999994</v>
       </c>
       <c r="E6" s="9">
         <f>B6-D6</f>
-        <v>-84645.431199999992</v>
+        <v>-85045.511199999994</v>
       </c>
       <c r="F6" s="9">
         <f>IFERROR(SUMIFS(PartnerShares!$E$13:$E$499,PartnerShares!$D$13:$D$499,$A6,PartnerShares!$B$13:$B$499,"Cash"),0)-IFERROR(SUMIFS(PartnerShares!$E$13:$E$499,PartnerShares!$C$13:$C$499,$A6,PartnerShares!$B$13:$B$499,"Cash"),0)</f>
@@ -34959,7 +34978,7 @@
       </c>
       <c r="G6" s="69">
         <f>E6+F6</f>
-        <v>-18922.447199999981</v>
+        <v>-19322.527199999982</v>
       </c>
     </row>
     <row r="9" spans="1:7" ht="13.5" customHeight="1">

--- a/docs/Chiraath-Summary-May26.xlsx
+++ b/docs/Chiraath-Summary-May26.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/anooppremachandran/Desktop/CHIRAATH/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1880A21F-87A7-CA4C-87A0-12B7B6F7184F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6F2DC9B1-6D09-014D-BDCA-F115EE68D788}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="18000" tabRatio="500" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -46,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2260" uniqueCount="908">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2321" uniqueCount="934">
   <si>
     <t>Notes:</t>
   </si>
@@ -1431,9 +1431,6 @@
     <t>CHR-51</t>
   </si>
   <si>
-    <t>M, L, XXL</t>
-  </si>
-  <si>
     <t>Red</t>
   </si>
   <si>
@@ -1672,12 +1669,6 @@
   </si>
   <si>
     <t>Silk blend 3 piece salwar set(indigo blue)</t>
-  </si>
-  <si>
-    <t>Saida (1600), Lathika (L-1400)</t>
-  </si>
-  <si>
-    <t>Size: M, XXL</t>
   </si>
   <si>
     <t>CHR-80</t>
@@ -2001,9 +1992,6 @@
     <t>Roman Silk Salwar Set</t>
   </si>
   <si>
-    <t>Sushitha (XXL-1600)</t>
-  </si>
-  <si>
     <t>M, L, XL</t>
   </si>
   <si>
@@ -2191,9 +2179,6 @@
     <t>Linen Saree with Check (Maroon with golden checks, Rust Orange with golden checks)</t>
   </si>
   <si>
-    <t>Chris (1000 - Green)</t>
-  </si>
-  <si>
     <t>CHR-146</t>
   </si>
   <si>
@@ -2215,9 +2200,6 @@
     <t>SAREES 5619 (Tissue Silk Saree Golden Color)</t>
   </si>
   <si>
-    <t>Chris (Goldern with flowers)</t>
-  </si>
-  <si>
     <t>CHR-149</t>
   </si>
   <si>
@@ -2281,9 +2263,6 @@
     <t>Black cotton 3-piece salwar set with printed dupatta</t>
   </si>
   <si>
-    <t>M, L, XL, XXL</t>
-  </si>
-  <si>
     <t>CHR-156</t>
   </si>
   <si>
@@ -2320,24 +2299,15 @@
     <t>CHR-161</t>
   </si>
   <si>
-    <t>Black &amp; Beige Leaf Print Cotton Silk Saree</t>
-  </si>
-  <si>
     <t>CHR-162</t>
   </si>
   <si>
-    <t>Teal &amp; Coral Abstract Print Cotton Silk Saree</t>
-  </si>
-  <si>
     <t>CHR-163</t>
   </si>
   <si>
     <t>Narayanpet sarees</t>
   </si>
   <si>
-    <t xml:space="preserve">Grey-Black/Red, Maroon-Yellow/Bottle Green, Purple-Yellow/Bottle Green, Bottle Green-Yellow/Red, Peacock Blue-Purple/Golden Yellow  </t>
-  </si>
-  <si>
     <t>CHR-164</t>
   </si>
   <si>
@@ -2509,9 +2479,6 @@
     <t>Leena - Chikku Green, Prema - Chikku Maroon, Shini - Green</t>
   </si>
   <si>
-    <t>Sourabhya (XL - 580)</t>
-  </si>
-  <si>
     <t>L, XXL</t>
   </si>
   <si>
@@ -2530,12 +2497,6 @@
     <t>Praneetha (L), Rameez Cousin (M), Indu (XL)</t>
   </si>
   <si>
-    <t>Indu - XXL</t>
-  </si>
-  <si>
-    <t>M, L, XL, XXXL</t>
-  </si>
-  <si>
     <t>Indu - M</t>
   </si>
   <si>
@@ -2572,15 +2533,9 @@
     <t xml:space="preserve">Sudhisha - </t>
   </si>
   <si>
-    <t>CHR-119 - Chanderi Silk Black &amp; Blue</t>
-  </si>
-  <si>
     <t>CHR-119 - Chanderi Silk Pink</t>
   </si>
   <si>
-    <t>Tussar silk Green(CHR-70) - 500 advance</t>
-  </si>
-  <si>
     <t>Salwar maroon single piece M (CHR-78)</t>
   </si>
   <si>
@@ -2611,9 +2566,6 @@
     <t>Sreelekha (Kayamkulam)</t>
   </si>
   <si>
-    <t>CHR-119 - Black?</t>
-  </si>
-  <si>
     <t>matka - Maroon/Navy Blue</t>
   </si>
   <si>
@@ -2636,181 +2588,278 @@
   </si>
   <si>
     <t>Yellow, Dark Green</t>
+  </si>
+  <si>
+    <t>Kavya (Kasargod)</t>
+  </si>
+  <si>
+    <t>Matka Black with Golden Yellow</t>
+  </si>
+  <si>
+    <t>Matka Green/Yellow &amp; Bengal Cotton (Adv:100)</t>
+  </si>
+  <si>
+    <t>Silpa Kannur</t>
+  </si>
+  <si>
+    <t>CHR-175</t>
+  </si>
+  <si>
+    <t>CHR-176</t>
+  </si>
+  <si>
+    <t>CHR-177</t>
+  </si>
+  <si>
+    <t>CHR-178</t>
+  </si>
+  <si>
+    <t>CHR-179</t>
+  </si>
+  <si>
+    <t>CHR-180</t>
+  </si>
+  <si>
+    <t>CHR-181</t>
+  </si>
+  <si>
+    <t>CHR-182</t>
+  </si>
+  <si>
+    <t>CHR-183</t>
+  </si>
+  <si>
+    <t>CHR-184</t>
+  </si>
+  <si>
+    <t>CHR-185</t>
+  </si>
+  <si>
+    <t>CHR-186</t>
+  </si>
+  <si>
+    <t>CHR-187</t>
+  </si>
+  <si>
+    <t>Aji Roy(Trichue)</t>
+  </si>
+  <si>
+    <t>CHR-119 - Black &amp; Mustard</t>
+  </si>
+  <si>
+    <t>Gopika (TVM)</t>
+  </si>
+  <si>
+    <t>CHR-119 - Black</t>
+  </si>
+  <si>
+    <t>Lily Kutty (Kottayam)</t>
+  </si>
+  <si>
+    <t>Sindhu (Pkd)</t>
+  </si>
+  <si>
+    <t>CHR-119 - Green</t>
+  </si>
+  <si>
+    <t>CHR-119 - Maroon</t>
+  </si>
+  <si>
+    <t>Matka Silk Saree Collection</t>
+  </si>
+  <si>
+    <t>Soft Silk Saree Collection</t>
+  </si>
+  <si>
+    <t>Tussar Silk Collection</t>
+  </si>
+  <si>
+    <t>Tissue Silk Saree Collection</t>
+  </si>
+  <si>
+    <t>Chanderi Silk Saree Collection</t>
+  </si>
+  <si>
+    <t>Aasha (EKM)</t>
+  </si>
+  <si>
+    <t>Boosting - March &amp; April</t>
+  </si>
+  <si>
+    <t>Soorya (Perumbavoor)</t>
+  </si>
+  <si>
+    <t>CHR-119 - Rani Pink</t>
+  </si>
+  <si>
+    <t>Asha Latha</t>
+  </si>
+  <si>
+    <t>CHR-119 - Off white</t>
+  </si>
+  <si>
+    <t>Subha</t>
+  </si>
+  <si>
+    <t>Matka - Black/Mustard yellow</t>
+  </si>
+  <si>
+    <t>Bottle Green/Golden Yellow - 2 
+Navy Blue/Bottle Green - 2</t>
+  </si>
+  <si>
+    <t>Blue/bottle green - Saranya Hyd, Blue/red - Jothika, Mustard - Vineetha, Bottle Green/Golden Yellow - Swapna (Thrissur)-1200, Black/Golden yellow - Kavya(Kasargod) - 1200, Back/Yellow - Subha - 1200</t>
+  </si>
+  <si>
+    <t>Subi</t>
+  </si>
+  <si>
+    <t>Roman Silk(L)</t>
+  </si>
+  <si>
+    <t>Sushitha (XXL-1600), M-Returned, L - Subi(), XL-Lipsy(1500)</t>
+  </si>
+  <si>
+    <t>Tussar silk Green(CHR-70)</t>
+  </si>
+  <si>
+    <t>Khadee Saree - Black &amp; Beige Leaf Print Cotton Silk Saree</t>
+  </si>
+  <si>
+    <t>Khadee Saree - Teal &amp; Coral Abstract Print Cotton Silk Saree</t>
+  </si>
+  <si>
+    <t>Khadee saree - black &amp; biege lief print</t>
+  </si>
+  <si>
+    <t>Smita Michigan</t>
+  </si>
+  <si>
+    <t>Saida (1600), Lathika (L-1400), Smitha - M</t>
+  </si>
+  <si>
+    <t>Size: XXL</t>
+  </si>
+  <si>
+    <t>Smita</t>
+  </si>
+  <si>
+    <t>Chanderi Black/Parrot Green, Silk Blend Salwar 3 piece set - M, Kerala Saree Floral Design, Tussar Silk - Burned Orange and Onion peel</t>
+  </si>
+  <si>
+    <t>Lipcy Michigan</t>
+  </si>
+  <si>
+    <t>Smitha - Rust orange &amp; Onion Peel, Lipcy - Blue</t>
+  </si>
+  <si>
+    <t>Grey, wine (damaged)</t>
+  </si>
+  <si>
+    <t>Light brown</t>
+  </si>
+  <si>
+    <t>Lipcy - Green</t>
+  </si>
+  <si>
+    <t>Tussar Silk Blue, Tussar Silk Green, Roman Silk XL, Matka Saree red/green</t>
+  </si>
+  <si>
+    <t>Lipcy - Red/Green</t>
+  </si>
+  <si>
+    <t>royal blue/rani pink, parrot green/red</t>
+  </si>
+  <si>
+    <t>206-05-10</t>
+  </si>
+  <si>
+    <t>Chithra</t>
+  </si>
+  <si>
+    <t>Chris (1000 - Green), Chithra - Maroon</t>
+  </si>
+  <si>
+    <t>Rust Orange</t>
+  </si>
+  <si>
+    <t>Narayanpett peacock blue, Linen Saree maroon, cotton 3 piece salwar set mirror work - XL, soft silk saree- black</t>
+  </si>
+  <si>
+    <t>Lakshmi</t>
+  </si>
+  <si>
+    <t>black/pink</t>
+  </si>
+  <si>
+    <t>Sourabhya (XL - 580), Lakshmi - L</t>
+  </si>
+  <si>
+    <t>Sherin - Maroon/navy blue(1099), Lakshmi - Navy Blue &amp; Maroon</t>
   </si>
   <si>
     <t>Peacok Blue/Maroon - 3
 Purple/Green - 1
-Navy Blue/Maroon - 2
+Navy Blue/Maroon - 1
 Lavender/Violet - 1
 Grey/Blue - 1</t>
   </si>
   <si>
-    <t>Sherin - Maroon/navy blue(1099)</t>
-  </si>
-  <si>
-    <t>Kavya (Kasargod)</t>
-  </si>
-  <si>
-    <t>Matka Black with Golden Yellow</t>
-  </si>
-  <si>
-    <t>Matka Green/Yellow &amp; Bengal Cotton (Adv:100)</t>
-  </si>
-  <si>
-    <t>Silpa Kannur</t>
-  </si>
-  <si>
-    <t>violet, black, navy blue, maroon</t>
-  </si>
-  <si>
-    <t>CHR-175</t>
-  </si>
-  <si>
-    <t>burned orange, Grey, wine, violet/grape, onion peal</t>
-  </si>
-  <si>
-    <t>CHR-176</t>
-  </si>
-  <si>
-    <t>CHR-177</t>
-  </si>
-  <si>
-    <t>CHR-178</t>
-  </si>
-  <si>
-    <t>CHR-179</t>
-  </si>
-  <si>
-    <t>CHR-180</t>
-  </si>
-  <si>
-    <t>CHR-181</t>
-  </si>
-  <si>
-    <t>CHR-182</t>
-  </si>
-  <si>
-    <t>CHR-183</t>
-  </si>
-  <si>
-    <t>CHR-184</t>
-  </si>
-  <si>
-    <t>CHR-185</t>
-  </si>
-  <si>
-    <t>CHR-186</t>
-  </si>
-  <si>
-    <t>CHR-187</t>
-  </si>
-  <si>
-    <t>Light brown, Pista green</t>
-  </si>
-  <si>
-    <t>black/pink, orange/black, black/parrot green</t>
-  </si>
-  <si>
-    <t>Aji Roy(Trichue)</t>
-  </si>
-  <si>
-    <t>CHR-119 - Black &amp; Mustard</t>
-  </si>
-  <si>
-    <t>Gopika (TVM)</t>
-  </si>
-  <si>
-    <t>CHR-119 - Black</t>
-  </si>
-  <si>
-    <t>Lily Kutty (Kottayam)</t>
-  </si>
-  <si>
-    <t>Sindhu (Pkd)</t>
-  </si>
-  <si>
-    <t>CHR-119 - Green</t>
-  </si>
-  <si>
-    <t>CHR-119 - Maroon</t>
-  </si>
-  <si>
-    <t>royal blue/rani pink, parrot green/red, deep red/bottle green</t>
-  </si>
-  <si>
-    <t>Matka Silk Saree Collection</t>
-  </si>
-  <si>
-    <t>Soft Silk Saree Collection</t>
-  </si>
-  <si>
-    <t>Tussar Silk Collection</t>
-  </si>
-  <si>
-    <t>Tissue Silk Saree Collection</t>
-  </si>
-  <si>
-    <t>Chanderi Silk Saree Collection</t>
-  </si>
-  <si>
-    <t>Aasha (EKM)</t>
-  </si>
-  <si>
-    <t>Boosting - March &amp; April</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Trebuchet MS"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <u/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Trebuchet MS"/>
-        <family val="2"/>
-      </rPr>
-      <t>New batch:</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Trebuchet MS"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve"> Blue (2), mustard yellow (1), navy blue (3), Green (2), Rani pink (2), Maroon (3), off white (3), Orange (2)
-</t>
-    </r>
-    <r>
-      <rPr>
-        <u/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Trebuchet MS"/>
-        <family val="2"/>
-      </rPr>
-      <t>New batch2:</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Trebuchet MS"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve"> Black(7), White(5), Rani Pink(1)</t>
-    </r>
+    <t>Chanderi Black/Orange, Jute - L, Matka - Blue &amp; Red, Matka Navy Blue &amp; maroon</t>
+  </si>
+  <si>
+    <t>Indukala</t>
+  </si>
+  <si>
+    <t>Indu Varrier</t>
+  </si>
+  <si>
+    <t>Aanchal Blue Salwar XL, Mul cottoan floral salwar with lace detailing L, Tussar silk golden color, Narayanpet green</t>
+  </si>
+  <si>
+    <t>Soft Silk Black - Chithra, Violet - Susmi</t>
+  </si>
+  <si>
+    <t>Chithra- peacok blue, Indu Varier - Green, Susmi - Maroon</t>
+  </si>
+  <si>
+    <t>navy blue, maroon</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Grey-Black/Red, Purple-Yellow/Bottle Green </t>
+  </si>
+  <si>
+    <t>Indu - XXL, Susmi - M</t>
+  </si>
+  <si>
+    <t>L, XL, XXXL</t>
+  </si>
+  <si>
+    <t>Indukala - L</t>
+  </si>
+  <si>
+    <t>Kathakali Saree, Chanderi Black/Pink, Aanchal Black Salwar set with Printed Dupatta(L), Aanchal white 3 piece salwar XL</t>
+  </si>
+  <si>
+    <t>Indukala - XL</t>
+  </si>
+  <si>
+    <t>XL, XXL</t>
+  </si>
+  <si>
+    <t>Smita - Parrot Green, Lakshmi - Black &amp; Orange, Indukala - Black/Pink</t>
+  </si>
+  <si>
+    <t>Jiji-XL, Indu varrier-L</t>
+  </si>
+  <si>
+    <t>M, XXL</t>
+  </si>
+  <si>
+    <t>Chris (Goldern with flowers), Indu Varrier</t>
+  </si>
+  <si>
+    <t>Narayanpett Maroon, Aanchal Olive Green with floral details M, Chanferi Off white, Soft Silk Saree Violet</t>
   </si>
   <si>
     <r>
@@ -2852,7 +2901,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve"> Dona - Black, Dona - navy Blue, Jayalakshmi - Pink, Jyothimol - Navy Blue, Amrutha - Maroon, Athira - Black, Jini - Maroon</t>
+      <t xml:space="preserve"> Sreelekha - Black, Dona - navy Blue, Jayalakshmi - Pink, Jyothimol - Navy Blue, Amrutha - Maroon, Athira - Black, Jini - Maroon</t>
     </r>
     <r>
       <rPr>
@@ -2861,33 +2910,55 @@
         <rFont val="Trebuchet MS"/>
         <family val="2"/>
       </rPr>
-      <t>, Gopika - Black, Aji Roy - Black, Aji Roy - Mustard, Lili Kutty - Maroon, Sindhu - Black, Asha - Green, Soorya - Rani Pink, Asha Latha - Offwhite</t>
+      <t>, Gopika - Black, Aji Roy - Black, Aji Roy - Mustard, Lili Kutty - Maroon, Sindhu - Black, Asha - Green, Soorya - Rani Pink, Asha Latha - Offwhite, Susmi - Off white</t>
     </r>
   </si>
   <si>
-    <t>Soorya (Perumbavoor)</t>
-  </si>
-  <si>
-    <t>CHR-119 - Rani Pink</t>
-  </si>
-  <si>
-    <t>Asha Latha</t>
-  </si>
-  <si>
-    <t>CHR-119 - Off white</t>
-  </si>
-  <si>
-    <t>Subha</t>
-  </si>
-  <si>
-    <t>Matka - Black/Mustard yellow</t>
-  </si>
-  <si>
-    <t>Bottle Green/Golden Yellow - 2 
-Navy Blue/Bottle Green - 2</t>
-  </si>
-  <si>
-    <t>Blue/bottle green - Saranya Hyd, Blue/red - Jothika, Mustard - Vineetha, Bottle Green/Golden Yellow - Swapna (Thrissur)-1200, Black/Golden yellow - Kavya(Kasargod) - 1200, Back/Yellow - Subha - 1200</t>
+    <r>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Trebuchet MS"/>
+        <family val="2"/>
+      </rPr>
+      <t>New batch:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Trebuchet MS"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve"> Blue (2), mustard yellow (1), navy blue (3), Green (2), Rani pink (2), Maroon (3), off white (2), Orange (2)
+</t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Trebuchet MS"/>
+        <family val="2"/>
+      </rPr>
+      <t>New batch2:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Trebuchet MS"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve"> Black(7), White(5), Rani Pink(1)</t>
+    </r>
   </si>
 </sst>
 </file>
@@ -3820,13 +3891,13 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="3"/>
                 <c:pt idx="0">
-                  <c:v>164</c:v>
+                  <c:v>182</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>81</c:v>
+                  <c:v>86</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>2</c:v>
+                  <c:v>3</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3923,13 +3994,13 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="3"/>
                 <c:pt idx="0">
-                  <c:v>108</c:v>
+                  <c:v>93</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>64</c:v>
+                  <c:v>59</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>5</c:v>
+                  <c:v>4</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4253,13 +4324,13 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="3"/>
                 <c:pt idx="0">
-                  <c:v>66578</c:v>
+                  <c:v>61609</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>73962.763333333321</c:v>
+                  <c:v>61548.609999999993</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>1829</c:v>
+                  <c:v>1357</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4583,7 +4654,7 @@
                   <c:v>71002</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0</c:v>
+                  <c:v>3944</c:v>
                 </c:pt>
                 <c:pt idx="5">
                   <c:v>0</c:v>
@@ -4731,19 +4802,19 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="12"/>
                 <c:pt idx="0">
-                  <c:v>45448</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>19089</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>16248</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>56636</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>2589</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="5">
                   <c:v>0</c:v>
@@ -5171,19 +5242,19 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="12"/>
                 <c:pt idx="0">
-                  <c:v>-1863</c:v>
+                  <c:v>-47311</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>14299</c:v>
+                  <c:v>-4790</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>-5924</c:v>
+                  <c:v>-22172</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>-14366</c:v>
+                  <c:v>-71002</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>2589</c:v>
+                  <c:v>-3944</c:v>
                 </c:pt>
                 <c:pt idx="5">
                   <c:v>0</c:v>
@@ -5653,10 +5724,10 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="2"/>
                 <c:pt idx="0">
-                  <c:v>247</c:v>
+                  <c:v>271</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>177</c:v>
+                  <c:v>156</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6813,7 +6884,7 @@
     <col min="4" max="4" width="30.1640625" style="6" customWidth="1"/>
     <col min="5" max="5" width="22.1640625" style="6" customWidth="1"/>
     <col min="6" max="6" width="31.1640625" style="6" customWidth="1"/>
-    <col min="7" max="7" width="16.5" style="6" customWidth="1"/>
+    <col min="7" max="7" width="14.6640625" style="6" bestFit="1" customWidth="1"/>
     <col min="8" max="16384" width="8.83203125" style="6"/>
   </cols>
   <sheetData>
@@ -6828,7 +6899,7 @@
       </c>
       <c r="B3" s="8">
         <f>SUM(Purchases!C:C)</f>
-        <v>350293</v>
+        <v>354237</v>
       </c>
       <c r="E3" s="8" t="s">
         <v>42</v>
@@ -6843,7 +6914,7 @@
       </c>
       <c r="B4" s="10">
         <f>SUMIFS(Sales!C:C, Sales!I:I, "Completed")</f>
-        <v>292668</v>
+        <v>327368</v>
       </c>
       <c r="E4" s="9" t="str">
         <f>PartnerShares!A3</f>
@@ -6860,7 +6931,7 @@
       </c>
       <c r="B5" s="12">
         <f>SUM(Sales!C:C)</f>
-        <v>306037</v>
+        <v>342137</v>
       </c>
       <c r="E5" s="11" t="str">
         <f>PartnerShares!A4</f>
@@ -6877,7 +6948,7 @@
       </c>
       <c r="B6" s="10">
         <f>B4-B3</f>
-        <v>-57625</v>
+        <v>-26869</v>
       </c>
       <c r="E6" s="9" t="str">
         <f>PartnerShares!A5</f>
@@ -6912,7 +6983,7 @@
       </c>
       <c r="B10" s="13">
         <f>PartnerShares!H8</f>
-        <v>19192.326666666671</v>
+        <v>17877.66</v>
       </c>
       <c r="C10" s="9"/>
     </row>
@@ -6922,7 +6993,7 @@
       </c>
       <c r="B11" s="14">
         <f>PartnerShares!H9</f>
-        <v>5029.3366666666698</v>
+        <v>7658.6699999999983</v>
       </c>
       <c r="C11" s="11"/>
     </row>
@@ -6932,7 +7003,7 @@
       </c>
       <c r="B12" s="13">
         <f>PartnerShares!H10</f>
-        <v>-24221.66333333333</v>
+        <v>-25536.33</v>
       </c>
       <c r="C12" s="9"/>
     </row>
@@ -6975,11 +7046,11 @@
       </c>
       <c r="C18" s="10">
         <f>PartnerShares!C8</f>
-        <v>116764.33333333333</v>
+        <v>118079</v>
       </c>
       <c r="D18" s="10">
         <f>PartnerShares!D8</f>
-        <v>37495.666666666672</v>
+        <v>36181</v>
       </c>
       <c r="E18" s="10">
         <f>IFERROR(SUMIFS(PartnerShares!$E$14:$E$500,PartnerShares!$D$14:$D$500,$A18,PartnerShares!$B$14:$B$500,"Contribution"),0)-IFERROR(SUMIFS(PartnerShares!$E$14:$E$500,PartnerShares!$C$14:$C$500,$A18,PartnerShares!$B$14:$B$500,"Contribution"),0)</f>
@@ -6987,11 +7058,11 @@
       </c>
       <c r="F18" s="13">
         <f>D18-E18</f>
-        <v>19192.326666666671</v>
+        <v>17877.66</v>
       </c>
       <c r="G18" s="16" t="str">
         <f>IF(ROUND(F18,0)&gt;0,"Receive ₹"&amp;TEXT(ABS(F18),"#,##0"),IF(ROUND(F18,0)&lt;0,"Pay ₹"&amp;TEXT(ABS(F18),"#,##0"),"✓ Settled"))</f>
-        <v>Receive ₹19,192</v>
+        <v>Receive ₹17,878</v>
       </c>
     </row>
     <row r="19" spans="1:7" ht="13.5" customHeight="1">
@@ -7001,15 +7072,15 @@
       </c>
       <c r="B19" s="12">
         <f>PartnerShares!B9</f>
-        <v>163433</v>
+        <v>167377</v>
       </c>
       <c r="C19" s="12">
         <f>PartnerShares!C9</f>
-        <v>116764.33333333333</v>
+        <v>118079</v>
       </c>
       <c r="D19" s="12">
         <f>PartnerShares!D9</f>
-        <v>46668.666666666672</v>
+        <v>49298</v>
       </c>
       <c r="E19" s="12">
         <f>IFERROR(SUMIFS(PartnerShares!$E$14:$E$500,PartnerShares!$D$14:$D$500,$A19,PartnerShares!$B$14:$B$500,"Contribution"),0)-IFERROR(SUMIFS(PartnerShares!$E$14:$E$500,PartnerShares!$C$14:$C$500,$A19,PartnerShares!$B$14:$B$500,"Contribution"),0)</f>
@@ -7017,11 +7088,11 @@
       </c>
       <c r="F19" s="14">
         <f>D19-E19</f>
-        <v>5029.3366666666698</v>
+        <v>7658.6699999999983</v>
       </c>
       <c r="G19" s="17" t="str">
         <f>IF(ROUND(F19,0)&gt;0,"Receive ₹"&amp;TEXT(ABS(F19),"#,##0"),IF(ROUND(F19,0)&lt;0,"Pay ₹"&amp;TEXT(ABS(F19),"#,##0"),"✓ Settled"))</f>
-        <v>Receive ₹5,029</v>
+        <v>Receive ₹7,659</v>
       </c>
     </row>
     <row r="20" spans="1:7" ht="13.5" customHeight="1">
@@ -7035,11 +7106,11 @@
       </c>
       <c r="C20" s="10">
         <f>PartnerShares!C10</f>
-        <v>116764.33333333333</v>
+        <v>118079</v>
       </c>
       <c r="D20" s="10">
         <f>PartnerShares!D10</f>
-        <v>-84164.333333333328</v>
+        <v>-85479</v>
       </c>
       <c r="E20" s="10">
         <f>IFERROR(SUMIFS(PartnerShares!$E$14:$E$500,PartnerShares!$D$14:$D$500,$A20,PartnerShares!$B$14:$B$500,"Contribution"),0)-IFERROR(SUMIFS(PartnerShares!$E$14:$E$500,PartnerShares!$C$14:$C$500,$A20,PartnerShares!$B$14:$B$500,"Contribution"),0)</f>
@@ -7047,11 +7118,11 @@
       </c>
       <c r="F20" s="13">
         <f>D20-E20</f>
-        <v>-24221.66333333333</v>
+        <v>-25536.33</v>
       </c>
       <c r="G20" s="17" t="str">
         <f>IF(ROUND(F20,0)&gt;0,"Receive ₹"&amp;TEXT(ABS(F20),"#,##0"),IF(ROUND(F20,0)&lt;0,"Pay ₹"&amp;TEXT(ABS(F20),"#,##0"),"✓ Settled"))</f>
-        <v>Pay ₹24,222</v>
+        <v>Pay ₹25,536</v>
       </c>
     </row>
     <row r="24" spans="1:7" ht="15.75" customHeight="1">
@@ -7089,15 +7160,15 @@
       </c>
       <c r="B26" s="10">
         <f>'Cash Pool'!B4</f>
-        <v>271719</v>
+        <v>274469</v>
       </c>
       <c r="C26" s="10">
         <f>'Cash Pool'!D4</f>
-        <v>97575.511199999994</v>
+        <v>109144.49119999999</v>
       </c>
       <c r="D26" s="10">
         <f>'Cash Pool'!E4</f>
-        <v>174143.48879999999</v>
+        <v>165324.50880000001</v>
       </c>
       <c r="E26" s="10">
         <f>'Cash Pool'!F4</f>
@@ -7105,11 +7176,11 @@
       </c>
       <c r="F26" s="13">
         <f>'Cash Pool'!G4</f>
-        <v>36833.462799999979</v>
+        <v>28014.482799999998</v>
       </c>
       <c r="G26" s="17" t="str">
         <f>IF(ROUND(F26,0)&gt;0,"Pay ₹"&amp;TEXT(ABS(F26),"#,##0"),IF(ROUND(F26,0)&lt;0,"Receive ₹"&amp;TEXT(ABS(F26),"#,##0"),"✓ Settled"))</f>
-        <v>Pay ₹36,833</v>
+        <v>Pay ₹28,014</v>
       </c>
     </row>
     <row r="27" spans="1:7" ht="13.5" customHeight="1">
@@ -7119,15 +7190,15 @@
       </c>
       <c r="B27" s="12">
         <f>'Cash Pool'!B5</f>
-        <v>8419</v>
+        <v>40369</v>
       </c>
       <c r="C27" s="12">
         <f>'Cash Pool'!D5</f>
-        <v>97516.977599999998</v>
+        <v>109079.01759999999</v>
       </c>
       <c r="D27" s="12">
         <f>'Cash Pool'!E5</f>
-        <v>-89097.977599999998</v>
+        <v>-68710.017599999992</v>
       </c>
       <c r="E27" s="12">
         <f>'Cash Pool'!F5</f>
@@ -7135,11 +7206,11 @@
       </c>
       <c r="F27" s="14">
         <f>'Cash Pool'!G5</f>
-        <v>-17510.935599999997</v>
+        <v>2877.0244000000093</v>
       </c>
       <c r="G27" s="18" t="str">
         <f>IF(ROUND(F27,0)&gt;0,"Pay ₹"&amp;TEXT(ABS(F27),"#,##0"),IF(ROUND(F27,0)&lt;0,"Receive ₹"&amp;TEXT(ABS(F27),"#,##0"),"✓ Settled"))</f>
-        <v>Receive ₹17,511</v>
+        <v>Pay ₹2,877</v>
       </c>
     </row>
     <row r="28" spans="1:7" ht="13.5" customHeight="1">
@@ -7153,11 +7224,11 @@
       </c>
       <c r="C28" s="10">
         <f>'Cash Pool'!D6</f>
-        <v>97575.511199999994</v>
+        <v>109144.49119999999</v>
       </c>
       <c r="D28" s="10">
         <f>'Cash Pool'!E6</f>
-        <v>-85045.511199999994</v>
+        <v>-96614.491199999989</v>
       </c>
       <c r="E28" s="10">
         <f>'Cash Pool'!F6</f>
@@ -7165,11 +7236,11 @@
       </c>
       <c r="F28" s="13">
         <f>'Cash Pool'!G6</f>
-        <v>-19322.527199999982</v>
+        <v>-30891.507199999978</v>
       </c>
       <c r="G28" s="16" t="str">
         <f>IF(ROUND(F28,0)&gt;0,"Pay ₹"&amp;TEXT(ABS(F28),"#,##0"),IF(ROUND(F28,0)&lt;0,"Receive ₹"&amp;TEXT(ABS(F28),"#,##0"),"✓ Settled"))</f>
-        <v>Receive ₹19,323</v>
+        <v>Receive ₹30,892</v>
       </c>
     </row>
     <row r="32" spans="1:7" ht="15.75" customHeight="1">
@@ -7281,7 +7352,7 @@
       </c>
       <c r="B3" s="20">
         <f ca="1">TODAY()</f>
-        <v>46147</v>
+        <v>46159</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="15" customHeight="1">
@@ -7290,14 +7361,14 @@
       </c>
       <c r="B5" s="21">
         <f>Summary!B3</f>
-        <v>350293</v>
+        <v>354237</v>
       </c>
       <c r="D5" s="19" t="s">
         <v>69</v>
       </c>
       <c r="E5" s="21">
         <f>Summary!B4</f>
-        <v>292668</v>
+        <v>327368</v>
       </c>
     </row>
     <row r="6" spans="1:8" ht="15" customHeight="1">
@@ -7306,14 +7377,14 @@
       </c>
       <c r="B6" s="21">
         <f>Summary!B6</f>
-        <v>-57625</v>
+        <v>-26869</v>
       </c>
       <c r="D6" s="19" t="s">
         <v>71</v>
       </c>
       <c r="E6" s="21">
         <f>SUMIFS(INVENTORY!K:K, INVENTORY!N:N, "&lt;&gt;Sold Out")</f>
-        <v>138298.96333333332</v>
+        <v>115210.80999999998</v>
       </c>
     </row>
     <row r="7" spans="1:8" ht="15.75" customHeight="1">
@@ -7354,18 +7425,18 @@
       </c>
       <c r="C10" s="21">
         <f>IFERROR(SUMPRODUCT((TEXT(Sales!$A$2:$A$996,"MMM")=$A10)*(YEAR(Sales!$A$2:$A$996)=$B$7)*Sales!$C$2:$C$996),0)</f>
-        <v>45448</v>
+        <v>0</v>
       </c>
       <c r="D10" s="21">
         <f t="shared" ref="D10:D21" si="0">C10-B10</f>
-        <v>-1863</v>
+        <v>-47311</v>
       </c>
       <c r="F10" s="25" t="s">
         <v>80</v>
       </c>
       <c r="G10" s="21">
         <f>SUM(INVENTORY!F:F)</f>
-        <v>247</v>
+        <v>271</v>
       </c>
     </row>
     <row r="11" spans="1:8" ht="15" customHeight="1">
@@ -7378,18 +7449,18 @@
       </c>
       <c r="C11" s="27">
         <f>IFERROR(SUMPRODUCT((TEXT(Sales!$A$2:$A$996,"MMM")=$A11)*(YEAR(Sales!$A$2:$A$996)=$B$7)*Sales!$C$2:$C$996),0)</f>
-        <v>19089</v>
+        <v>0</v>
       </c>
       <c r="D11" s="27">
         <f t="shared" si="0"/>
-        <v>14299</v>
+        <v>-4790</v>
       </c>
       <c r="F11" s="26" t="s">
         <v>82</v>
       </c>
       <c r="G11" s="27">
         <f>SUM(INVENTORY!G:G)</f>
-        <v>177</v>
+        <v>156</v>
       </c>
     </row>
     <row r="12" spans="1:8" ht="15" customHeight="1">
@@ -7402,11 +7473,11 @@
       </c>
       <c r="C12" s="21">
         <f>IFERROR(SUMPRODUCT((TEXT(Sales!$A$2:$A$996,"MMM")=$A12)*(YEAR(Sales!$A$2:$A$996)=$B$7)*Sales!$C$2:$C$996),0)</f>
-        <v>16248</v>
+        <v>0</v>
       </c>
       <c r="D12" s="21">
         <f t="shared" si="0"/>
-        <v>-5924</v>
+        <v>-22172</v>
       </c>
     </row>
     <row r="13" spans="1:8" ht="15" customHeight="1">
@@ -7419,11 +7490,11 @@
       </c>
       <c r="C13" s="27">
         <f>IFERROR(SUMPRODUCT((TEXT(Sales!$A$2:$A$996,"MMM")=$A13)*(YEAR(Sales!$A$2:$A$996)=$B$7)*Sales!$C$2:$C$996),0)</f>
-        <v>56636</v>
+        <v>0</v>
       </c>
       <c r="D13" s="27">
         <f t="shared" si="0"/>
-        <v>-14366</v>
+        <v>-71002</v>
       </c>
     </row>
     <row r="14" spans="1:8" ht="15" customHeight="1">
@@ -7432,15 +7503,15 @@
       </c>
       <c r="B14" s="21">
         <f>IFERROR(SUMPRODUCT((TEXT(Purchases!$A$2:$A$998,"MMM")=$A14)*(YEAR(Purchases!$A$2:$A$998)=$B$7)*Purchases!$C$2:$C$998),0)</f>
-        <v>0</v>
+        <v>3944</v>
       </c>
       <c r="C14" s="21">
         <f>IFERROR(SUMPRODUCT((TEXT(Sales!$A$2:$A$996,"MMM")=$A14)*(YEAR(Sales!$A$2:$A$996)=$B$7)*Sales!$C$2:$C$996),0)</f>
-        <v>2589</v>
+        <v>0</v>
       </c>
       <c r="D14" s="21">
         <f t="shared" si="0"/>
-        <v>2589</v>
+        <v>-3944</v>
       </c>
     </row>
     <row r="15" spans="1:8" ht="15" customHeight="1">
@@ -7585,18 +7656,18 @@
       </c>
       <c r="G47" s="30">
         <f>SUMIF(INVENTORY!C:C, F47, INVENTORY!F:F)</f>
-        <v>164</v>
+        <v>182</v>
       </c>
       <c r="H47" s="30">
         <f>SUMIF(INVENTORY!C:C, F47, INVENTORY!G:G)</f>
-        <v>108</v>
+        <v>93</v>
       </c>
       <c r="J47" s="30" t="s">
         <v>96</v>
       </c>
       <c r="K47" s="31">
         <f t="array" ref="K47">SUMPRODUCT((INVENTORY!$C$2:$C$477=J47)*(INVENTORY!$D$2:$D$477)*(INVENTORY!$G$2:$G$477))</f>
-        <v>66578</v>
+        <v>61609</v>
       </c>
     </row>
     <row r="48" spans="6:11" ht="15" customHeight="1">
@@ -7605,18 +7676,18 @@
       </c>
       <c r="G48" s="30">
         <f>SUMIF(INVENTORY!C:C, F48, INVENTORY!F:F)</f>
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="H48" s="30">
         <f>SUMIF(INVENTORY!C:C, F48, INVENTORY!G:G)</f>
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="J48" s="30" t="s">
         <v>95</v>
       </c>
       <c r="K48" s="31">
         <f t="array" ref="K48">SUMPRODUCT((INVENTORY!$C$2:$C$477=J48)*(INVENTORY!$D$2:$D$477)*(INVENTORY!$G$2:$G$477))</f>
-        <v>73962.763333333321</v>
+        <v>61548.609999999993</v>
       </c>
     </row>
     <row r="49" spans="5:12" ht="15" customHeight="1">
@@ -7625,18 +7696,18 @@
       </c>
       <c r="G49" s="30">
         <f>SUMIF(INVENTORY!C:C, F49, INVENTORY!F:F)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H49" s="30">
         <f>SUMIF(INVENTORY!C:C, F49, INVENTORY!G:G)</f>
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J49" s="30" t="s">
         <v>97</v>
       </c>
       <c r="K49" s="31">
         <f t="array" ref="K49">SUMPRODUCT((INVENTORY!$C$2:$C$477=J49)*(INVENTORY!$D$2:$D$477)*(INVENTORY!$G$2:$G$477))</f>
-        <v>1829</v>
+        <v>1357</v>
       </c>
     </row>
     <row r="55" spans="5:12" ht="15" customHeight="1">
@@ -8611,7 +8682,7 @@
         <v>100</v>
       </c>
       <c r="D64" s="36" t="s">
-        <v>813</v>
+        <v>803</v>
       </c>
     </row>
     <row r="65" spans="1:4" ht="15" customHeight="1">
@@ -8709,14 +8780,22 @@
         <v>4000</v>
       </c>
       <c r="D71" s="39" t="s">
-        <v>897</v>
+        <v>874</v>
       </c>
     </row>
     <row r="72" spans="1:4" ht="15" customHeight="1">
-      <c r="A72" s="35"/>
-      <c r="B72" s="36"/>
-      <c r="C72" s="37"/>
-      <c r="D72" s="36"/>
+      <c r="A72" s="35">
+        <v>46151</v>
+      </c>
+      <c r="B72" s="36" t="s">
+        <v>50</v>
+      </c>
+      <c r="C72" s="37">
+        <v>3944</v>
+      </c>
+      <c r="D72" s="36" t="s">
+        <v>118</v>
+      </c>
     </row>
     <row r="73" spans="1:4" ht="15" customHeight="1">
       <c r="A73" s="38"/>
@@ -14560,10 +14639,10 @@
       <c r="F146" s="91"/>
       <c r="G146" s="91"/>
       <c r="H146" s="92" t="s">
-        <v>839</v>
+        <v>886</v>
       </c>
       <c r="I146" s="80" t="s">
-        <v>334</v>
+        <v>140</v>
       </c>
     </row>
     <row r="147" spans="1:9" ht="14">
@@ -14897,14 +14976,16 @@
       <c r="C160" s="81">
         <v>1380</v>
       </c>
-      <c r="D160" s="80"/>
+      <c r="D160" s="80" t="s">
+        <v>154</v>
+      </c>
       <c r="E160" s="80" t="s">
         <v>49</v>
       </c>
       <c r="F160" s="91"/>
       <c r="G160" s="91"/>
       <c r="H160" s="92" t="s">
-        <v>814</v>
+        <v>804</v>
       </c>
       <c r="I160" s="80" t="s">
         <v>334</v>
@@ -14915,7 +14996,7 @@
         <v>46132</v>
       </c>
       <c r="B161" s="76" t="s">
-        <v>828</v>
+        <v>815</v>
       </c>
       <c r="C161" s="77">
         <v>1100</v>
@@ -14945,14 +15026,16 @@
       <c r="C162" s="81">
         <v>5880</v>
       </c>
-      <c r="D162" s="80"/>
+      <c r="D162" s="80" t="s">
+        <v>154</v>
+      </c>
       <c r="E162" s="80" t="s">
         <v>49</v>
       </c>
       <c r="F162" s="91"/>
       <c r="G162" s="91"/>
       <c r="H162" s="92" t="s">
-        <v>841</v>
+        <v>826</v>
       </c>
       <c r="I162" s="80" t="s">
         <v>140</v>
@@ -14963,19 +15046,21 @@
         <v>46133</v>
       </c>
       <c r="B163" s="76" t="s">
-        <v>818</v>
+        <v>807</v>
       </c>
       <c r="C163" s="77">
         <v>1350</v>
       </c>
-      <c r="D163" s="76"/>
+      <c r="D163" s="76" t="s">
+        <v>154</v>
+      </c>
       <c r="E163" s="76" t="s">
         <v>49</v>
       </c>
       <c r="F163" s="76"/>
       <c r="G163" s="76"/>
       <c r="H163" s="78" t="s">
-        <v>819</v>
+        <v>808</v>
       </c>
       <c r="I163" s="76" t="s">
         <v>140</v>
@@ -14998,7 +15083,7 @@
       <c r="F164" s="91"/>
       <c r="G164" s="91"/>
       <c r="H164" s="92" t="s">
-        <v>820</v>
+        <v>809</v>
       </c>
       <c r="I164" s="80" t="s">
         <v>334</v>
@@ -15021,7 +15106,7 @@
       <c r="F165" s="76"/>
       <c r="G165" s="76"/>
       <c r="H165" s="78" t="s">
-        <v>821</v>
+        <v>810</v>
       </c>
       <c r="I165" s="76" t="s">
         <v>334</v>
@@ -15032,7 +15117,7 @@
         <v>46134</v>
       </c>
       <c r="B166" s="80" t="s">
-        <v>833</v>
+        <v>820</v>
       </c>
       <c r="C166" s="81">
         <v>1280</v>
@@ -15046,7 +15131,7 @@
       <c r="F166" s="91"/>
       <c r="G166" s="91"/>
       <c r="H166" s="92" t="s">
-        <v>835</v>
+        <v>822</v>
       </c>
       <c r="I166" s="80" t="s">
         <v>140</v>
@@ -15069,7 +15154,7 @@
       <c r="F167" s="76"/>
       <c r="G167" s="76"/>
       <c r="H167" s="78" t="s">
-        <v>831</v>
+        <v>818</v>
       </c>
       <c r="I167" s="76" t="s">
         <v>334</v>
@@ -15092,7 +15177,7 @@
       <c r="F168" s="76"/>
       <c r="G168" s="76"/>
       <c r="H168" s="78" t="s">
-        <v>840</v>
+        <v>825</v>
       </c>
       <c r="I168" s="76" t="s">
         <v>334</v>
@@ -15106,7 +15191,7 @@
         <v>169</v>
       </c>
       <c r="C169" s="81">
-        <v>1300</v>
+        <v>650</v>
       </c>
       <c r="D169" s="80"/>
       <c r="E169" s="80" t="s">
@@ -15115,7 +15200,7 @@
       <c r="F169" s="91"/>
       <c r="G169" s="91"/>
       <c r="H169" s="92" t="s">
-        <v>837</v>
+        <v>827</v>
       </c>
       <c r="I169" s="80" t="s">
         <v>334</v>
@@ -15126,7 +15211,7 @@
         <v>46134</v>
       </c>
       <c r="B170" s="76" t="s">
-        <v>832</v>
+        <v>819</v>
       </c>
       <c r="C170" s="77">
         <v>650</v>
@@ -15140,7 +15225,7 @@
       <c r="F170" s="76"/>
       <c r="G170" s="76"/>
       <c r="H170" s="78" t="s">
-        <v>838</v>
+        <v>824</v>
       </c>
       <c r="I170" s="76" t="s">
         <v>140</v>
@@ -15163,7 +15248,7 @@
       <c r="F171" s="91"/>
       <c r="G171" s="91"/>
       <c r="H171" s="92" t="s">
-        <v>842</v>
+        <v>827</v>
       </c>
       <c r="I171" s="80" t="s">
         <v>334</v>
@@ -15174,7 +15259,7 @@
         <v>46138</v>
       </c>
       <c r="B172" s="76" t="s">
-        <v>844</v>
+        <v>829</v>
       </c>
       <c r="C172" s="77">
         <v>690</v>
@@ -15188,7 +15273,7 @@
       <c r="F172" s="76"/>
       <c r="G172" s="76"/>
       <c r="H172" s="78" t="s">
-        <v>843</v>
+        <v>828</v>
       </c>
       <c r="I172" s="76" t="s">
         <v>140</v>
@@ -15199,7 +15284,7 @@
         <v>46138</v>
       </c>
       <c r="B173" s="80" t="s">
-        <v>845</v>
+        <v>830</v>
       </c>
       <c r="C173" s="81">
         <v>1099</v>
@@ -15213,7 +15298,7 @@
       <c r="F173" s="91"/>
       <c r="G173" s="91"/>
       <c r="H173" s="92" t="s">
-        <v>851</v>
+        <v>835</v>
       </c>
       <c r="I173" s="80" t="s">
         <v>140</v>
@@ -15224,7 +15309,7 @@
         <v>46139</v>
       </c>
       <c r="B174" s="76" t="s">
-        <v>846</v>
+        <v>831</v>
       </c>
       <c r="C174" s="77">
         <v>690</v>
@@ -15238,7 +15323,7 @@
       <c r="F174" s="76"/>
       <c r="G174" s="76"/>
       <c r="H174" s="78" t="s">
-        <v>847</v>
+        <v>832</v>
       </c>
       <c r="I174" s="76" t="s">
         <v>140</v>
@@ -15249,7 +15334,7 @@
         <v>46139</v>
       </c>
       <c r="B175" s="80" t="s">
-        <v>848</v>
+        <v>833</v>
       </c>
       <c r="C175" s="81">
         <v>690</v>
@@ -15263,7 +15348,7 @@
       <c r="F175" s="91"/>
       <c r="G175" s="91"/>
       <c r="H175" s="92" t="s">
-        <v>843</v>
+        <v>828</v>
       </c>
       <c r="I175" s="80" t="s">
         <v>140</v>
@@ -15274,7 +15359,7 @@
         <v>46139</v>
       </c>
       <c r="B176" s="76" t="s">
-        <v>849</v>
+        <v>834</v>
       </c>
       <c r="C176" s="77">
         <v>690</v>
@@ -15288,7 +15373,7 @@
       <c r="F176" s="76"/>
       <c r="G176" s="76"/>
       <c r="H176" s="78" t="s">
-        <v>850</v>
+        <v>863</v>
       </c>
       <c r="I176" s="76" t="s">
         <v>140</v>
@@ -15299,7 +15384,7 @@
         <v>46140</v>
       </c>
       <c r="B177" s="80" t="s">
-        <v>852</v>
+        <v>836</v>
       </c>
       <c r="C177" s="81">
         <v>1380</v>
@@ -15313,7 +15398,7 @@
       <c r="F177" s="91"/>
       <c r="G177" s="91"/>
       <c r="H177" s="92" t="s">
-        <v>853</v>
+        <v>837</v>
       </c>
       <c r="I177" s="80" t="s">
         <v>140</v>
@@ -15338,7 +15423,7 @@
       <c r="F178" s="76"/>
       <c r="G178" s="76"/>
       <c r="H178" s="78" t="s">
-        <v>854</v>
+        <v>838</v>
       </c>
       <c r="I178" s="76" t="s">
         <v>140</v>
@@ -15349,7 +15434,7 @@
         <v>46140</v>
       </c>
       <c r="B179" s="80" t="s">
-        <v>861</v>
+        <v>843</v>
       </c>
       <c r="C179" s="81">
         <v>1200</v>
@@ -15363,7 +15448,7 @@
       <c r="F179" s="91"/>
       <c r="G179" s="91"/>
       <c r="H179" s="92" t="s">
-        <v>862</v>
+        <v>844</v>
       </c>
       <c r="I179" s="80" t="s">
         <v>140</v>
@@ -15374,7 +15459,7 @@
         <v>46140</v>
       </c>
       <c r="B180" s="76" t="s">
-        <v>864</v>
+        <v>846</v>
       </c>
       <c r="C180" s="77">
         <v>1899</v>
@@ -15388,7 +15473,7 @@
       <c r="F180" s="76"/>
       <c r="G180" s="76"/>
       <c r="H180" s="78" t="s">
-        <v>863</v>
+        <v>845</v>
       </c>
       <c r="I180" s="76" t="s">
         <v>334</v>
@@ -15399,7 +15484,7 @@
         <v>46141</v>
       </c>
       <c r="B181" s="80" t="s">
-        <v>882</v>
+        <v>860</v>
       </c>
       <c r="C181" s="81">
         <v>1380</v>
@@ -15413,7 +15498,7 @@
       <c r="F181" s="91"/>
       <c r="G181" s="91"/>
       <c r="H181" s="92" t="s">
-        <v>883</v>
+        <v>861</v>
       </c>
       <c r="I181" s="80" t="s">
         <v>140</v>
@@ -15424,7 +15509,7 @@
         <v>46141</v>
       </c>
       <c r="B182" s="76" t="s">
-        <v>884</v>
+        <v>862</v>
       </c>
       <c r="C182" s="77">
         <v>690</v>
@@ -15438,7 +15523,7 @@
       <c r="F182" s="76"/>
       <c r="G182" s="76"/>
       <c r="H182" s="78" t="s">
-        <v>885</v>
+        <v>863</v>
       </c>
       <c r="I182" s="76" t="s">
         <v>140</v>
@@ -15449,7 +15534,7 @@
         <v>46142</v>
       </c>
       <c r="B183" s="80" t="s">
-        <v>886</v>
+        <v>864</v>
       </c>
       <c r="C183" s="81">
         <v>690</v>
@@ -15463,7 +15548,7 @@
       <c r="F183" s="91"/>
       <c r="G183" s="91"/>
       <c r="H183" s="92" t="s">
-        <v>889</v>
+        <v>867</v>
       </c>
       <c r="I183" s="80" t="s">
         <v>140</v>
@@ -15474,7 +15559,7 @@
         <v>46142</v>
       </c>
       <c r="B184" s="76" t="s">
-        <v>887</v>
+        <v>865</v>
       </c>
       <c r="C184" s="77">
         <v>690</v>
@@ -15488,7 +15573,7 @@
       <c r="F184" s="76"/>
       <c r="G184" s="76"/>
       <c r="H184" s="78" t="s">
-        <v>885</v>
+        <v>863</v>
       </c>
       <c r="I184" s="76" t="s">
         <v>140</v>
@@ -15499,7 +15584,7 @@
         <v>46142</v>
       </c>
       <c r="B185" s="80" t="s">
-        <v>896</v>
+        <v>873</v>
       </c>
       <c r="C185" s="81">
         <v>609</v>
@@ -15513,7 +15598,7 @@
       <c r="F185" s="91"/>
       <c r="G185" s="91"/>
       <c r="H185" s="92" t="s">
-        <v>888</v>
+        <v>866</v>
       </c>
       <c r="I185" s="80" t="s">
         <v>140</v>
@@ -15524,7 +15609,7 @@
         <v>46144</v>
       </c>
       <c r="B186" s="80" t="s">
-        <v>900</v>
+        <v>875</v>
       </c>
       <c r="C186" s="81">
         <v>699</v>
@@ -15538,7 +15623,7 @@
       <c r="F186" s="91"/>
       <c r="G186" s="91"/>
       <c r="H186" s="92" t="s">
-        <v>901</v>
+        <v>876</v>
       </c>
       <c r="I186" s="80" t="s">
         <v>140</v>
@@ -15549,7 +15634,7 @@
         <v>46144</v>
       </c>
       <c r="B187" s="76" t="s">
-        <v>902</v>
+        <v>877</v>
       </c>
       <c r="C187" s="77">
         <v>690</v>
@@ -15563,7 +15648,7 @@
       <c r="F187" s="76"/>
       <c r="G187" s="76"/>
       <c r="H187" s="78" t="s">
-        <v>903</v>
+        <v>878</v>
       </c>
       <c r="I187" s="76" t="s">
         <v>140</v>
@@ -15574,7 +15659,7 @@
         <v>46145</v>
       </c>
       <c r="B188" s="80" t="s">
-        <v>904</v>
+        <v>879</v>
       </c>
       <c r="C188" s="81">
         <v>1200</v>
@@ -15588,110 +15673,232 @@
       <c r="F188" s="91"/>
       <c r="G188" s="91"/>
       <c r="H188" s="92" t="s">
-        <v>905</v>
+        <v>880</v>
       </c>
       <c r="I188" s="80" t="s">
         <v>140</v>
       </c>
     </row>
-    <row r="189" spans="1:9">
-      <c r="A189" s="75"/>
-      <c r="B189" s="76"/>
-      <c r="C189" s="77"/>
-      <c r="D189" s="76"/>
-      <c r="E189" s="76"/>
+    <row r="189" spans="1:9" ht="14">
+      <c r="A189" s="75">
+        <v>46145</v>
+      </c>
+      <c r="B189" s="76" t="s">
+        <v>883</v>
+      </c>
+      <c r="C189" s="77">
+        <v>1200</v>
+      </c>
+      <c r="D189" s="76" t="s">
+        <v>154</v>
+      </c>
+      <c r="E189" s="76" t="s">
+        <v>49</v>
+      </c>
       <c r="F189" s="76"/>
       <c r="G189" s="76"/>
-      <c r="H189" s="78"/>
-      <c r="I189" s="76"/>
-    </row>
-    <row r="190" spans="1:9">
-      <c r="A190" s="79"/>
-      <c r="B190" s="80"/>
-      <c r="C190" s="81"/>
-      <c r="D190" s="80"/>
-      <c r="E190" s="80"/>
+      <c r="H189" s="78" t="s">
+        <v>884</v>
+      </c>
+      <c r="I189" s="76" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="190" spans="1:9" ht="14">
+      <c r="A190" s="79">
+        <v>46145</v>
+      </c>
+      <c r="B190" s="80" t="s">
+        <v>153</v>
+      </c>
+      <c r="C190" s="81">
+        <v>600</v>
+      </c>
+      <c r="D190" s="80" t="s">
+        <v>154</v>
+      </c>
+      <c r="E190" s="80" t="s">
+        <v>49</v>
+      </c>
       <c r="F190" s="91"/>
       <c r="G190" s="91"/>
-      <c r="H190" s="92"/>
-      <c r="I190" s="80"/>
-    </row>
-    <row r="191" spans="1:9">
-      <c r="A191" s="75"/>
-      <c r="B191" s="76"/>
-      <c r="C191" s="77"/>
-      <c r="D191" s="76"/>
-      <c r="E191" s="76"/>
+      <c r="H190" s="92" t="s">
+        <v>889</v>
+      </c>
+      <c r="I190" s="80" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="191" spans="1:9" ht="42">
+      <c r="A191" s="75">
+        <v>46151</v>
+      </c>
+      <c r="B191" s="76" t="s">
+        <v>890</v>
+      </c>
+      <c r="C191" s="77">
+        <v>5600</v>
+      </c>
+      <c r="D191" s="76" t="s">
+        <v>142</v>
+      </c>
+      <c r="E191" s="76" t="s">
+        <v>50</v>
+      </c>
       <c r="F191" s="76"/>
       <c r="G191" s="76"/>
-      <c r="H191" s="78"/>
-      <c r="I191" s="76"/>
-    </row>
-    <row r="192" spans="1:9">
-      <c r="A192" s="79"/>
-      <c r="B192" s="80"/>
-      <c r="C192" s="81"/>
-      <c r="D192" s="80"/>
-      <c r="E192" s="80"/>
+      <c r="H191" s="78" t="s">
+        <v>894</v>
+      </c>
+      <c r="I191" s="76" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="192" spans="1:9" ht="28">
+      <c r="A192" s="79">
+        <v>46152</v>
+      </c>
+      <c r="B192" s="80" t="s">
+        <v>895</v>
+      </c>
+      <c r="C192" s="81">
+        <v>5600</v>
+      </c>
+      <c r="D192" s="80" t="s">
+        <v>142</v>
+      </c>
+      <c r="E192" s="80" t="s">
+        <v>50</v>
+      </c>
       <c r="F192" s="91"/>
       <c r="G192" s="91"/>
-      <c r="H192" s="92"/>
-      <c r="I192" s="80"/>
-    </row>
-    <row r="193" spans="1:9">
-      <c r="A193" s="75"/>
-      <c r="B193" s="76"/>
-      <c r="C193" s="77"/>
-      <c r="D193" s="76"/>
-      <c r="E193" s="76"/>
+      <c r="H192" s="92" t="s">
+        <v>900</v>
+      </c>
+      <c r="I192" s="80" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="193" spans="1:9" ht="42">
+      <c r="A193" s="75" t="s">
+        <v>903</v>
+      </c>
+      <c r="B193" s="76" t="s">
+        <v>904</v>
+      </c>
+      <c r="C193" s="77">
+        <v>5600</v>
+      </c>
+      <c r="D193" s="76" t="s">
+        <v>142</v>
+      </c>
+      <c r="E193" s="76" t="s">
+        <v>50</v>
+      </c>
       <c r="F193" s="76"/>
       <c r="G193" s="76"/>
-      <c r="H193" s="78"/>
-      <c r="I193" s="76"/>
-    </row>
-    <row r="194" spans="1:9">
-      <c r="A194" s="79"/>
-      <c r="B194" s="80"/>
-      <c r="C194" s="81"/>
+      <c r="H193" s="78" t="s">
+        <v>907</v>
+      </c>
+      <c r="I193" s="76" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="194" spans="1:9" ht="28">
+      <c r="A194" s="79">
+        <v>46151</v>
+      </c>
+      <c r="B194" s="80" t="s">
+        <v>908</v>
+      </c>
+      <c r="C194" s="81">
+        <v>3000</v>
+      </c>
       <c r="D194" s="80"/>
       <c r="E194" s="80"/>
       <c r="F194" s="91"/>
       <c r="G194" s="91"/>
-      <c r="H194" s="92"/>
-      <c r="I194" s="80"/>
-    </row>
-    <row r="195" spans="1:9">
-      <c r="A195" s="75"/>
-      <c r="B195" s="76"/>
-      <c r="C195" s="77"/>
-      <c r="D195" s="76"/>
-      <c r="E195" s="76"/>
+      <c r="H194" s="92" t="s">
+        <v>913</v>
+      </c>
+      <c r="I194" s="80" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="195" spans="1:9" ht="42">
+      <c r="A195" s="75">
+        <v>46155</v>
+      </c>
+      <c r="B195" s="76" t="s">
+        <v>914</v>
+      </c>
+      <c r="C195" s="77">
+        <v>5400</v>
+      </c>
+      <c r="D195" s="76" t="s">
+        <v>142</v>
+      </c>
+      <c r="E195" s="76" t="s">
+        <v>50</v>
+      </c>
       <c r="F195" s="76"/>
       <c r="G195" s="76"/>
-      <c r="H195" s="78"/>
-      <c r="I195" s="76"/>
-    </row>
-    <row r="196" spans="1:9">
-      <c r="A196" s="79"/>
-      <c r="B196" s="80"/>
-      <c r="C196" s="81"/>
-      <c r="D196" s="80"/>
-      <c r="E196" s="80"/>
+      <c r="H195" s="78" t="s">
+        <v>924</v>
+      </c>
+      <c r="I195" s="76" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="196" spans="1:9" ht="42">
+      <c r="A196" s="79">
+        <v>46155</v>
+      </c>
+      <c r="B196" s="80" t="s">
+        <v>915</v>
+      </c>
+      <c r="C196" s="81">
+        <v>5750</v>
+      </c>
+      <c r="D196" s="80" t="s">
+        <v>142</v>
+      </c>
+      <c r="E196" s="80" t="s">
+        <v>50</v>
+      </c>
       <c r="F196" s="91"/>
       <c r="G196" s="91"/>
-      <c r="H196" s="92"/>
-      <c r="I196" s="80"/>
-    </row>
-    <row r="197" spans="1:9">
-      <c r="A197" s="75"/>
-      <c r="B197" s="76"/>
-      <c r="C197" s="77"/>
-      <c r="D197" s="76"/>
-      <c r="E197" s="76"/>
+      <c r="H196" s="92" t="s">
+        <v>916</v>
+      </c>
+      <c r="I196" s="80" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="197" spans="1:9" ht="42">
+      <c r="A197" s="75">
+        <v>46155</v>
+      </c>
+      <c r="B197" s="76" t="s">
+        <v>175</v>
+      </c>
+      <c r="C197" s="77">
+        <v>4000</v>
+      </c>
+      <c r="D197" s="76" t="s">
+        <v>142</v>
+      </c>
+      <c r="E197" s="76" t="s">
+        <v>50</v>
+      </c>
       <c r="F197" s="76"/>
       <c r="G197" s="76"/>
-      <c r="H197" s="78"/>
-      <c r="I197" s="76"/>
+      <c r="H197" s="78" t="s">
+        <v>931</v>
+      </c>
+      <c r="I197" s="76" t="s">
+        <v>140</v>
+      </c>
     </row>
     <row r="198" spans="1:9">
       <c r="A198" s="79"/>
@@ -22373,10 +22580,10 @@
         <v>799</v>
       </c>
       <c r="F52" s="49">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G52" s="49">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H52" s="48">
         <f t="shared" si="3"/>
@@ -22388,24 +22595,24 @@
       </c>
       <c r="J52" s="48">
         <f t="shared" si="4"/>
-        <v>1200</v>
+        <v>2400</v>
       </c>
       <c r="K52" s="48">
         <f t="shared" si="5"/>
-        <v>3600</v>
+        <v>2400</v>
       </c>
       <c r="L52" s="48" t="s">
-        <v>289</v>
+        <v>928</v>
       </c>
       <c r="M52" s="48"/>
       <c r="N52" s="48" t="s">
         <v>451</v>
       </c>
       <c r="O52" s="48" t="s">
+        <v>929</v>
+      </c>
+      <c r="P52" s="48" t="s">
         <v>461</v>
-      </c>
-      <c r="P52" s="48" t="s">
-        <v>462</v>
       </c>
       <c r="Q52" s="48"/>
       <c r="R52" s="48"/>
@@ -22414,7 +22621,7 @@
     </row>
     <row r="53" spans="1:246" ht="15" customHeight="1">
       <c r="A53" s="42" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="B53" s="42" t="s">
         <v>288</v>
@@ -22451,7 +22658,7 @@
         <v>1941</v>
       </c>
       <c r="L53" s="42" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="M53" s="42"/>
       <c r="N53" s="42" t="s">
@@ -22461,7 +22668,7 @@
         <v>221</v>
       </c>
       <c r="P53" s="42" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="Q53" s="42"/>
       <c r="R53" s="42"/>
@@ -22470,10 +22677,10 @@
     </row>
     <row r="54" spans="1:246" s="57" customFormat="1" ht="15" customHeight="1">
       <c r="A54" s="48" t="s">
+        <v>465</v>
+      </c>
+      <c r="B54" s="54" t="s">
         <v>466</v>
-      </c>
-      <c r="B54" s="54" t="s">
-        <v>467</v>
       </c>
       <c r="C54" s="54" t="s">
         <v>96</v>
@@ -22515,10 +22722,10 @@
         <v>199</v>
       </c>
       <c r="P54" s="54" t="s">
+        <v>467</v>
+      </c>
+      <c r="Q54" s="48" t="s">
         <v>468</v>
-      </c>
-      <c r="Q54" s="48" t="s">
-        <v>469</v>
       </c>
       <c r="R54" s="54"/>
       <c r="S54" s="54"/>
@@ -22752,10 +22959,10 @@
     </row>
     <row r="55" spans="1:246" ht="15" customHeight="1">
       <c r="A55" s="42" t="s">
+        <v>469</v>
+      </c>
+      <c r="B55" s="42" t="s">
         <v>470</v>
-      </c>
-      <c r="B55" s="42" t="s">
-        <v>471</v>
       </c>
       <c r="C55" s="42" t="s">
         <v>96</v>
@@ -22789,7 +22996,7 @@
         <v>995</v>
       </c>
       <c r="L55" s="42" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="M55" s="42" t="s">
         <v>49</v>
@@ -22808,7 +23015,7 @@
     </row>
     <row r="56" spans="1:246" ht="15" customHeight="1">
       <c r="A56" s="48" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="B56" s="48" t="s">
         <v>381</v>
@@ -22854,7 +23061,7 @@
         <v>366</v>
       </c>
       <c r="O56" s="48" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="P56" s="48"/>
       <c r="Q56" s="48"/>
@@ -22864,10 +23071,10 @@
     </row>
     <row r="57" spans="1:246" ht="15" customHeight="1">
       <c r="A57" s="42" t="s">
+        <v>474</v>
+      </c>
+      <c r="B57" s="42" t="s">
         <v>475</v>
-      </c>
-      <c r="B57" s="42" t="s">
-        <v>476</v>
       </c>
       <c r="C57" s="42" t="s">
         <v>96</v>
@@ -22906,7 +23113,7 @@
         <v>334</v>
       </c>
       <c r="O57" s="42" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="P57" s="42"/>
       <c r="Q57" s="42"/>
@@ -22916,10 +23123,10 @@
     </row>
     <row r="58" spans="1:246" ht="15" customHeight="1">
       <c r="A58" s="48" t="s">
+        <v>477</v>
+      </c>
+      <c r="B58" s="48" t="s">
         <v>478</v>
-      </c>
-      <c r="B58" s="48" t="s">
-        <v>479</v>
       </c>
       <c r="C58" s="48" t="s">
         <v>96</v>
@@ -22958,7 +23165,7 @@
         <v>334</v>
       </c>
       <c r="O58" s="48" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="P58" s="48"/>
       <c r="Q58" s="48"/>
@@ -22968,7 +23175,7 @@
     </row>
     <row r="59" spans="1:246" ht="15" customHeight="1">
       <c r="A59" s="42" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="B59" s="42" t="s">
         <v>458</v>
@@ -23005,17 +23212,17 @@
         <v>2290</v>
       </c>
       <c r="L59" s="42" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="M59" s="42"/>
       <c r="N59" s="42" t="s">
         <v>451</v>
       </c>
       <c r="O59" s="42" t="s">
+        <v>482</v>
+      </c>
+      <c r="P59" s="42" t="s">
         <v>483</v>
-      </c>
-      <c r="P59" s="42" t="s">
-        <v>484</v>
       </c>
       <c r="Q59" s="42"/>
       <c r="R59" s="42"/>
@@ -23024,10 +23231,10 @@
     </row>
     <row r="60" spans="1:246" ht="15" customHeight="1">
       <c r="A60" s="48" t="s">
+        <v>484</v>
+      </c>
+      <c r="B60" s="48" t="s">
         <v>485</v>
-      </c>
-      <c r="B60" s="48" t="s">
-        <v>486</v>
       </c>
       <c r="C60" s="48" t="s">
         <v>96</v>
@@ -23061,7 +23268,7 @@
         <v>1080</v>
       </c>
       <c r="L60" s="48" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="M60" s="48" t="s">
         <v>49</v>
@@ -23071,7 +23278,7 @@
       </c>
       <c r="O60" s="48"/>
       <c r="P60" s="48" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="Q60" s="48"/>
       <c r="R60" s="48"/>
@@ -23080,7 +23287,7 @@
     </row>
     <row r="61" spans="1:246" ht="45" customHeight="1">
       <c r="A61" s="42" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="B61" s="42" t="s">
         <v>437</v>
@@ -23117,20 +23324,20 @@
         <v>4384</v>
       </c>
       <c r="L61" s="42" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="M61" s="42"/>
       <c r="N61" s="42" t="s">
         <v>451</v>
       </c>
       <c r="O61" s="42" t="s">
+        <v>490</v>
+      </c>
+      <c r="P61" s="42" t="s">
         <v>491</v>
       </c>
-      <c r="P61" s="42" t="s">
+      <c r="Q61" s="42" t="s">
         <v>492</v>
-      </c>
-      <c r="Q61" s="42" t="s">
-        <v>493</v>
       </c>
       <c r="R61" s="42"/>
       <c r="S61" s="42"/>
@@ -23138,7 +23345,7 @@
     </row>
     <row r="62" spans="1:246" ht="15" customHeight="1">
       <c r="A62" s="48" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="B62" s="48" t="s">
         <v>109</v>
@@ -23175,7 +23382,7 @@
         <v>562</v>
       </c>
       <c r="L62" s="48" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="M62" s="48"/>
       <c r="N62" s="48" t="s">
@@ -23190,7 +23397,7 @@
     </row>
     <row r="63" spans="1:246" ht="15" customHeight="1">
       <c r="A63" s="42" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="B63" s="42" t="s">
         <v>372</v>
@@ -23242,7 +23449,7 @@
     </row>
     <row r="64" spans="1:246" ht="15" customHeight="1">
       <c r="A64" s="48" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="B64" s="48" t="s">
         <v>372</v>
@@ -23294,10 +23501,10 @@
     </row>
     <row r="65" spans="1:20" ht="15" customHeight="1">
       <c r="A65" s="42" t="s">
+        <v>497</v>
+      </c>
+      <c r="B65" s="42" t="s">
         <v>498</v>
-      </c>
-      <c r="B65" s="42" t="s">
-        <v>499</v>
       </c>
       <c r="C65" s="42" t="s">
         <v>95</v>
@@ -23331,7 +23538,7 @@
         <v>0</v>
       </c>
       <c r="L65" s="42" t="s">
-        <v>834</v>
+        <v>821</v>
       </c>
       <c r="M65" s="42"/>
       <c r="N65" s="42" t="s">
@@ -23346,10 +23553,10 @@
     </row>
     <row r="66" spans="1:20" ht="15" customHeight="1">
       <c r="A66" s="48" t="s">
+        <v>499</v>
+      </c>
+      <c r="B66" s="48" t="s">
         <v>500</v>
-      </c>
-      <c r="B66" s="48" t="s">
-        <v>501</v>
       </c>
       <c r="C66" s="48" t="s">
         <v>95</v>
@@ -23383,7 +23590,7 @@
         <v>1558</v>
       </c>
       <c r="L66" s="48" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="M66" s="48"/>
       <c r="N66" s="48" t="s">
@@ -23398,10 +23605,10 @@
     </row>
     <row r="67" spans="1:20" ht="15" customHeight="1">
       <c r="A67" s="42" t="s">
+        <v>502</v>
+      </c>
+      <c r="B67" s="42" t="s">
         <v>503</v>
-      </c>
-      <c r="B67" s="42" t="s">
-        <v>504</v>
       </c>
       <c r="C67" s="42" t="s">
         <v>95</v>
@@ -23448,10 +23655,10 @@
     </row>
     <row r="68" spans="1:20" ht="15" customHeight="1">
       <c r="A68" s="48" t="s">
+        <v>504</v>
+      </c>
+      <c r="B68" s="48" t="s">
         <v>505</v>
-      </c>
-      <c r="B68" s="48" t="s">
-        <v>506</v>
       </c>
       <c r="C68" s="48" t="s">
         <v>95</v>
@@ -23485,7 +23692,7 @@
         <v>685</v>
       </c>
       <c r="L68" s="48" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="M68" s="48"/>
       <c r="N68" s="48" t="s">
@@ -23493,7 +23700,7 @@
       </c>
       <c r="O68" s="48"/>
       <c r="P68" s="48" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="Q68" s="48"/>
       <c r="R68" s="48"/>
@@ -23502,10 +23709,10 @@
     </row>
     <row r="69" spans="1:20" ht="15" customHeight="1">
       <c r="A69" s="42" t="s">
+        <v>508</v>
+      </c>
+      <c r="B69" s="42" t="s">
         <v>509</v>
-      </c>
-      <c r="B69" s="42" t="s">
-        <v>510</v>
       </c>
       <c r="C69" s="42" t="s">
         <v>96</v>
@@ -23544,7 +23751,7 @@
         <v>334</v>
       </c>
       <c r="O69" s="42" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="P69" s="42"/>
       <c r="Q69" s="42"/>
@@ -23554,10 +23761,10 @@
     </row>
     <row r="70" spans="1:20" ht="15" customHeight="1">
       <c r="A70" s="48" t="s">
+        <v>511</v>
+      </c>
+      <c r="B70" s="48" t="s">
         <v>512</v>
-      </c>
-      <c r="B70" s="48" t="s">
-        <v>513</v>
       </c>
       <c r="C70" s="48" t="s">
         <v>95</v>
@@ -23591,7 +23798,7 @@
         <v>0</v>
       </c>
       <c r="L70" s="48" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="M70" s="48"/>
       <c r="N70" s="48" t="s">
@@ -23606,10 +23813,10 @@
     </row>
     <row r="71" spans="1:20" ht="15" customHeight="1">
       <c r="A71" s="42" t="s">
+        <v>514</v>
+      </c>
+      <c r="B71" s="42" t="s">
         <v>515</v>
-      </c>
-      <c r="B71" s="42" t="s">
-        <v>516</v>
       </c>
       <c r="C71" s="42" t="s">
         <v>95</v>
@@ -23643,7 +23850,7 @@
         <v>0</v>
       </c>
       <c r="L71" s="42" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="M71" s="42" t="s">
         <v>49</v>
@@ -23653,7 +23860,7 @@
       </c>
       <c r="O71" s="42"/>
       <c r="P71" s="42" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="Q71" s="42"/>
       <c r="R71" s="42"/>
@@ -23662,10 +23869,10 @@
     </row>
     <row r="72" spans="1:20" ht="15" customHeight="1">
       <c r="A72" s="48" t="s">
+        <v>518</v>
+      </c>
+      <c r="B72" s="48" t="s">
         <v>519</v>
-      </c>
-      <c r="B72" s="48" t="s">
-        <v>520</v>
       </c>
       <c r="C72" s="48" t="s">
         <v>95</v>
@@ -23714,10 +23921,10 @@
     </row>
     <row r="73" spans="1:20" ht="15" customHeight="1">
       <c r="A73" s="42" t="s">
+        <v>520</v>
+      </c>
+      <c r="B73" s="42" t="s">
         <v>521</v>
-      </c>
-      <c r="B73" s="42" t="s">
-        <v>522</v>
       </c>
       <c r="C73" s="42" t="s">
         <v>96</v>
@@ -23766,10 +23973,10 @@
     </row>
     <row r="74" spans="1:20" ht="15" customHeight="1">
       <c r="A74" s="48" t="s">
+        <v>522</v>
+      </c>
+      <c r="B74" s="48" t="s">
         <v>523</v>
-      </c>
-      <c r="B74" s="48" t="s">
-        <v>524</v>
       </c>
       <c r="C74" s="48" t="s">
         <v>95</v>
@@ -23820,7 +24027,7 @@
     </row>
     <row r="75" spans="1:20" ht="15" customHeight="1">
       <c r="A75" s="42" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="B75" s="42" t="s">
         <v>415</v>
@@ -23874,10 +24081,10 @@
     </row>
     <row r="76" spans="1:20" ht="15" customHeight="1">
       <c r="A76" s="48" t="s">
+        <v>525</v>
+      </c>
+      <c r="B76" s="48" t="s">
         <v>526</v>
-      </c>
-      <c r="B76" s="48" t="s">
-        <v>527</v>
       </c>
       <c r="C76" s="48" t="s">
         <v>95</v>
@@ -23928,10 +24135,10 @@
     </row>
     <row r="77" spans="1:20" ht="15" customHeight="1">
       <c r="A77" s="42" t="s">
+        <v>527</v>
+      </c>
+      <c r="B77" s="42" t="s">
         <v>528</v>
-      </c>
-      <c r="B77" s="42" t="s">
-        <v>529</v>
       </c>
       <c r="C77" s="42" t="s">
         <v>96</v>
@@ -23965,14 +24172,14 @@
         <v>1990</v>
       </c>
       <c r="L77" s="42" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="M77" s="42"/>
       <c r="N77" s="42" t="s">
         <v>451</v>
       </c>
       <c r="O77" s="42" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="P77" s="42"/>
       <c r="Q77" s="42"/>
@@ -23982,10 +24189,10 @@
     </row>
     <row r="78" spans="1:20" ht="15" customHeight="1">
       <c r="A78" s="48" t="s">
+        <v>531</v>
+      </c>
+      <c r="B78" s="48" t="s">
         <v>532</v>
-      </c>
-      <c r="B78" s="48" t="s">
-        <v>533</v>
       </c>
       <c r="C78" s="48" t="s">
         <v>96</v>
@@ -24019,14 +24226,14 @@
         <v>2150</v>
       </c>
       <c r="L78" s="48" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="M78" s="48"/>
       <c r="N78" s="48" t="s">
         <v>451</v>
       </c>
       <c r="O78" s="48" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="P78" s="48"/>
       <c r="Q78" s="48"/>
@@ -24036,10 +24243,10 @@
     </row>
     <row r="79" spans="1:20" ht="15" customHeight="1">
       <c r="A79" s="42" t="s">
+        <v>535</v>
+      </c>
+      <c r="B79" s="42" t="s">
         <v>536</v>
-      </c>
-      <c r="B79" s="42" t="s">
-        <v>537</v>
       </c>
       <c r="C79" s="42" t="s">
         <v>96</v>
@@ -24073,14 +24280,14 @@
         <v>0</v>
       </c>
       <c r="L79" s="42" t="s">
-        <v>836</v>
+        <v>823</v>
       </c>
       <c r="M79" s="42"/>
       <c r="N79" s="42" t="s">
+        <v>537</v>
+      </c>
+      <c r="O79" s="42" t="s">
         <v>538</v>
-      </c>
-      <c r="O79" s="42" t="s">
-        <v>539</v>
       </c>
       <c r="P79" s="42"/>
       <c r="Q79" s="42"/>
@@ -24090,10 +24297,10 @@
     </row>
     <row r="80" spans="1:20" ht="15" customHeight="1">
       <c r="A80" s="48" t="s">
+        <v>539</v>
+      </c>
+      <c r="B80" s="48" t="s">
         <v>540</v>
-      </c>
-      <c r="B80" s="48" t="s">
-        <v>541</v>
       </c>
       <c r="C80" s="48" t="s">
         <v>96</v>
@@ -24105,10 +24312,10 @@
         <v>1700</v>
       </c>
       <c r="F80" s="49">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G80" s="49">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H80" s="48">
         <f t="shared" si="6"/>
@@ -24120,21 +24327,21 @@
       </c>
       <c r="J80" s="48">
         <f t="shared" si="7"/>
-        <v>2460</v>
+        <v>3690</v>
       </c>
       <c r="K80" s="48">
         <f t="shared" si="8"/>
-        <v>2460</v>
+        <v>1230</v>
       </c>
       <c r="L80" s="48" t="s">
-        <v>542</v>
+        <v>891</v>
       </c>
       <c r="M80" s="48"/>
       <c r="N80" s="48" t="s">
         <v>451</v>
       </c>
       <c r="O80" s="48" t="s">
-        <v>543</v>
+        <v>892</v>
       </c>
       <c r="P80" s="48"/>
       <c r="Q80" s="48"/>
@@ -24144,10 +24351,10 @@
     </row>
     <row r="81" spans="1:20" ht="30" customHeight="1">
       <c r="A81" s="42" t="s">
-        <v>544</v>
+        <v>541</v>
       </c>
       <c r="B81" s="42" t="s">
-        <v>545</v>
+        <v>542</v>
       </c>
       <c r="C81" s="42" t="s">
         <v>96</v>
@@ -24181,7 +24388,7 @@
         <v>0</v>
       </c>
       <c r="L81" s="42" t="s">
-        <v>546</v>
+        <v>543</v>
       </c>
       <c r="M81" s="42"/>
       <c r="N81" s="42" t="s">
@@ -24196,10 +24403,10 @@
     </row>
     <row r="82" spans="1:20" ht="15" customHeight="1">
       <c r="A82" s="48" t="s">
-        <v>547</v>
+        <v>544</v>
       </c>
       <c r="B82" s="48" t="s">
-        <v>548</v>
+        <v>545</v>
       </c>
       <c r="C82" s="48" t="s">
         <v>96</v>
@@ -24233,7 +24440,7 @@
         <v>0</v>
       </c>
       <c r="L82" s="48" t="s">
-        <v>549</v>
+        <v>546</v>
       </c>
       <c r="M82" s="48"/>
       <c r="N82" s="48" t="s">
@@ -24248,10 +24455,10 @@
     </row>
     <row r="83" spans="1:20" ht="30" customHeight="1">
       <c r="A83" s="42" t="s">
-        <v>550</v>
+        <v>547</v>
       </c>
       <c r="B83" s="42" t="s">
-        <v>551</v>
+        <v>548</v>
       </c>
       <c r="C83" s="42" t="s">
         <v>96</v>
@@ -24285,14 +24492,14 @@
         <v>0</v>
       </c>
       <c r="L83" s="42" t="s">
-        <v>552</v>
+        <v>549</v>
       </c>
       <c r="M83" s="42"/>
       <c r="N83" s="42" t="s">
         <v>366</v>
       </c>
       <c r="O83" s="42" t="s">
-        <v>553</v>
+        <v>550</v>
       </c>
       <c r="P83" s="42"/>
       <c r="Q83" s="42"/>
@@ -24302,10 +24509,10 @@
     </row>
     <row r="84" spans="1:20" ht="15" customHeight="1">
       <c r="A84" s="48" t="s">
-        <v>554</v>
+        <v>551</v>
       </c>
       <c r="B84" s="48" t="s">
-        <v>555</v>
+        <v>552</v>
       </c>
       <c r="C84" s="48" t="s">
         <v>96</v>
@@ -24339,14 +24546,14 @@
         <v>900</v>
       </c>
       <c r="L84" s="48" t="s">
-        <v>556</v>
+        <v>553</v>
       </c>
       <c r="M84" s="48"/>
       <c r="N84" s="48" t="s">
         <v>451</v>
       </c>
       <c r="O84" s="48" t="s">
-        <v>557</v>
+        <v>554</v>
       </c>
       <c r="P84" s="48"/>
       <c r="Q84" s="48"/>
@@ -24356,10 +24563,10 @@
     </row>
     <row r="85" spans="1:20" ht="15" customHeight="1">
       <c r="A85" s="42" t="s">
-        <v>558</v>
+        <v>555</v>
       </c>
       <c r="B85" s="42" t="s">
-        <v>559</v>
+        <v>556</v>
       </c>
       <c r="C85" s="42" t="s">
         <v>96</v>
@@ -24393,7 +24600,7 @@
         <v>895</v>
       </c>
       <c r="L85" s="42" t="s">
-        <v>827</v>
+        <v>814</v>
       </c>
       <c r="M85" s="42"/>
       <c r="N85" s="42" t="s">
@@ -24408,10 +24615,10 @@
     </row>
     <row r="86" spans="1:20" ht="15" customHeight="1">
       <c r="A86" s="48" t="s">
-        <v>560</v>
+        <v>557</v>
       </c>
       <c r="B86" s="48" t="s">
-        <v>561</v>
+        <v>558</v>
       </c>
       <c r="C86" s="48" t="s">
         <v>96</v>
@@ -24445,14 +24652,14 @@
         <v>2090</v>
       </c>
       <c r="L86" s="48" t="s">
-        <v>562</v>
+        <v>559</v>
       </c>
       <c r="M86" s="48"/>
       <c r="N86" s="48" t="s">
         <v>451</v>
       </c>
       <c r="O86" s="48" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="P86" s="48"/>
       <c r="Q86" s="48"/>
@@ -24462,10 +24669,10 @@
     </row>
     <row r="87" spans="1:20" ht="15" customHeight="1">
       <c r="A87" s="42" t="s">
-        <v>563</v>
+        <v>560</v>
       </c>
       <c r="B87" s="42" t="s">
-        <v>564</v>
+        <v>561</v>
       </c>
       <c r="C87" s="42" t="s">
         <v>96</v>
@@ -24501,10 +24708,10 @@
       <c r="L87" s="42"/>
       <c r="M87" s="42"/>
       <c r="N87" s="42" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="O87" s="42" t="s">
-        <v>565</v>
+        <v>562</v>
       </c>
       <c r="P87" s="42"/>
       <c r="Q87" s="42"/>
@@ -24514,10 +24721,10 @@
     </row>
     <row r="88" spans="1:20" ht="30" customHeight="1">
       <c r="A88" s="48" t="s">
-        <v>566</v>
+        <v>563</v>
       </c>
       <c r="B88" s="48" t="s">
-        <v>567</v>
+        <v>564</v>
       </c>
       <c r="C88" s="48" t="s">
         <v>96</v>
@@ -24551,14 +24758,14 @@
         <v>795</v>
       </c>
       <c r="L88" s="48" t="s">
-        <v>568</v>
+        <v>565</v>
       </c>
       <c r="M88" s="48"/>
       <c r="N88" s="48" t="s">
         <v>451</v>
       </c>
       <c r="O88" s="48" t="s">
-        <v>569</v>
+        <v>566</v>
       </c>
       <c r="P88" s="48"/>
       <c r="Q88" s="48"/>
@@ -24568,10 +24775,10 @@
     </row>
     <row r="89" spans="1:20" ht="15" customHeight="1">
       <c r="A89" s="42" t="s">
-        <v>570</v>
+        <v>567</v>
       </c>
       <c r="B89" s="42" t="s">
-        <v>571</v>
+        <v>568</v>
       </c>
       <c r="C89" s="42" t="s">
         <v>95</v>
@@ -24605,7 +24812,7 @@
         <v>0</v>
       </c>
       <c r="L89" s="42" t="s">
-        <v>572</v>
+        <v>569</v>
       </c>
       <c r="M89" s="42"/>
       <c r="N89" s="42" t="s">
@@ -24620,10 +24827,10 @@
     </row>
     <row r="90" spans="1:20" ht="15" customHeight="1">
       <c r="A90" s="48" t="s">
-        <v>573</v>
+        <v>570</v>
       </c>
       <c r="B90" s="48" t="s">
-        <v>574</v>
+        <v>571</v>
       </c>
       <c r="C90" s="48" t="s">
         <v>95</v>
@@ -24672,13 +24879,13 @@
     </row>
     <row r="91" spans="1:20" ht="15" customHeight="1">
       <c r="A91" s="42" t="s">
-        <v>575</v>
+        <v>572</v>
       </c>
       <c r="B91" s="42" t="s">
-        <v>576</v>
+        <v>573</v>
       </c>
       <c r="C91" s="42" t="s">
-        <v>577</v>
+        <v>574</v>
       </c>
       <c r="D91" s="51">
         <v>389</v>
@@ -24709,7 +24916,7 @@
         <v>0</v>
       </c>
       <c r="L91" s="42" t="s">
-        <v>856</v>
+        <v>840</v>
       </c>
       <c r="M91" s="42"/>
       <c r="N91" s="42" t="s">
@@ -24724,13 +24931,13 @@
     </row>
     <row r="92" spans="1:20" ht="15" customHeight="1">
       <c r="A92" s="48" t="s">
-        <v>578</v>
+        <v>575</v>
       </c>
       <c r="B92" s="48" t="s">
-        <v>579</v>
+        <v>576</v>
       </c>
       <c r="C92" s="48" t="s">
-        <v>577</v>
+        <v>574</v>
       </c>
       <c r="D92" s="49">
         <v>489</v>
@@ -24761,7 +24968,7 @@
         <v>0</v>
       </c>
       <c r="L92" s="48" t="s">
-        <v>580</v>
+        <v>577</v>
       </c>
       <c r="M92" s="48"/>
       <c r="N92" s="48" t="s">
@@ -24776,10 +24983,10 @@
     </row>
     <row r="93" spans="1:20" ht="15" customHeight="1">
       <c r="A93" s="42" t="s">
-        <v>581</v>
+        <v>578</v>
       </c>
       <c r="B93" s="42" t="s">
-        <v>582</v>
+        <v>579</v>
       </c>
       <c r="C93" s="42" t="s">
         <v>97</v>
@@ -24791,10 +24998,10 @@
         <v>650</v>
       </c>
       <c r="F93" s="51">
+        <v>2</v>
+      </c>
+      <c r="G93" s="51">
         <v>1</v>
-      </c>
-      <c r="G93" s="51">
-        <v>2</v>
       </c>
       <c r="H93" s="42">
         <f t="shared" si="6"/>
@@ -24806,21 +25013,21 @@
       </c>
       <c r="J93" s="42">
         <f t="shared" si="7"/>
-        <v>472</v>
+        <v>944</v>
       </c>
       <c r="K93" s="42">
         <f t="shared" si="8"/>
-        <v>944</v>
+        <v>472</v>
       </c>
       <c r="L93" s="42" t="s">
-        <v>816</v>
+        <v>910</v>
       </c>
       <c r="M93" s="42"/>
       <c r="N93" s="48" t="s">
         <v>451</v>
       </c>
       <c r="O93" s="42" t="s">
-        <v>817</v>
+        <v>806</v>
       </c>
       <c r="P93" s="42"/>
       <c r="Q93" s="42"/>
@@ -24830,10 +25037,10 @@
     </row>
     <row r="94" spans="1:20" ht="15" customHeight="1">
       <c r="A94" s="48" t="s">
-        <v>583</v>
+        <v>580</v>
       </c>
       <c r="B94" s="48" t="s">
-        <v>584</v>
+        <v>581</v>
       </c>
       <c r="C94" s="48" t="s">
         <v>95</v>
@@ -24882,10 +25089,10 @@
     </row>
     <row r="95" spans="1:20" ht="15" customHeight="1">
       <c r="A95" s="42" t="s">
-        <v>585</v>
+        <v>582</v>
       </c>
       <c r="B95" s="42" t="s">
-        <v>586</v>
+        <v>583</v>
       </c>
       <c r="C95" s="42" t="s">
         <v>95</v>
@@ -24919,7 +25126,7 @@
         <v>0</v>
       </c>
       <c r="L95" s="42" t="s">
-        <v>587</v>
+        <v>584</v>
       </c>
       <c r="M95" s="42"/>
       <c r="N95" s="42" t="s">
@@ -24934,10 +25141,10 @@
     </row>
     <row r="96" spans="1:20" ht="15" customHeight="1">
       <c r="A96" s="48" t="s">
-        <v>588</v>
+        <v>585</v>
       </c>
       <c r="B96" s="48" t="s">
-        <v>589</v>
+        <v>586</v>
       </c>
       <c r="C96" s="48" t="s">
         <v>95</v>
@@ -24973,7 +25180,7 @@
       <c r="L96" s="48"/>
       <c r="M96" s="48"/>
       <c r="N96" s="48" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="O96" s="48"/>
       <c r="P96" s="48"/>
@@ -24984,10 +25191,10 @@
     </row>
     <row r="97" spans="1:20" ht="15" customHeight="1">
       <c r="A97" s="42" t="s">
-        <v>590</v>
+        <v>587</v>
       </c>
       <c r="B97" s="42" t="s">
-        <v>591</v>
+        <v>588</v>
       </c>
       <c r="C97" s="42" t="s">
         <v>95</v>
@@ -25036,10 +25243,10 @@
     </row>
     <row r="98" spans="1:20" ht="15" customHeight="1">
       <c r="A98" s="48" t="s">
-        <v>592</v>
+        <v>589</v>
       </c>
       <c r="B98" s="48" t="s">
-        <v>593</v>
+        <v>590</v>
       </c>
       <c r="C98" s="48" t="s">
         <v>96</v>
@@ -25090,10 +25297,10 @@
     </row>
     <row r="99" spans="1:20" ht="15" customHeight="1">
       <c r="A99" s="42" t="s">
-        <v>594</v>
+        <v>591</v>
       </c>
       <c r="B99" s="42" t="s">
-        <v>595</v>
+        <v>592</v>
       </c>
       <c r="C99" s="42" t="s">
         <v>96</v>
@@ -25144,10 +25351,10 @@
     </row>
     <row r="100" spans="1:20" ht="15" customHeight="1">
       <c r="A100" s="48" t="s">
-        <v>596</v>
+        <v>593</v>
       </c>
       <c r="B100" s="48" t="s">
-        <v>597</v>
+        <v>594</v>
       </c>
       <c r="C100" s="48" t="s">
         <v>96</v>
@@ -25198,10 +25405,10 @@
     </row>
     <row r="101" spans="1:20" ht="15" customHeight="1">
       <c r="A101" s="42" t="s">
-        <v>598</v>
+        <v>595</v>
       </c>
       <c r="B101" s="42" t="s">
-        <v>599</v>
+        <v>596</v>
       </c>
       <c r="C101" s="42" t="s">
         <v>96</v>
@@ -25252,10 +25459,10 @@
     </row>
     <row r="102" spans="1:20" ht="15" customHeight="1">
       <c r="A102" s="48" t="s">
-        <v>600</v>
+        <v>597</v>
       </c>
       <c r="B102" s="48" t="s">
-        <v>601</v>
+        <v>598</v>
       </c>
       <c r="C102" s="48" t="s">
         <v>96</v>
@@ -25306,10 +25513,10 @@
     </row>
     <row r="103" spans="1:20" ht="15" customHeight="1">
       <c r="A103" s="42" t="s">
-        <v>602</v>
+        <v>599</v>
       </c>
       <c r="B103" s="42" t="s">
-        <v>603</v>
+        <v>600</v>
       </c>
       <c r="C103" s="42" t="s">
         <v>96</v>
@@ -25360,10 +25567,10 @@
     </row>
     <row r="104" spans="1:20" ht="15" customHeight="1">
       <c r="A104" s="48" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
       <c r="B104" s="48" t="s">
-        <v>605</v>
+        <v>602</v>
       </c>
       <c r="C104" s="48" t="s">
         <v>96</v>
@@ -25414,10 +25621,10 @@
     </row>
     <row r="105" spans="1:20" ht="15" customHeight="1">
       <c r="A105" s="42" t="s">
-        <v>606</v>
+        <v>603</v>
       </c>
       <c r="B105" s="42" t="s">
-        <v>607</v>
+        <v>604</v>
       </c>
       <c r="C105" s="42" t="s">
         <v>96</v>
@@ -25468,10 +25675,10 @@
     </row>
     <row r="106" spans="1:20" ht="15" customHeight="1">
       <c r="A106" s="48" t="s">
-        <v>608</v>
+        <v>605</v>
       </c>
       <c r="B106" s="48" t="s">
-        <v>609</v>
+        <v>606</v>
       </c>
       <c r="C106" s="48" t="s">
         <v>96</v>
@@ -25483,10 +25690,10 @@
         <v>1600</v>
       </c>
       <c r="F106" s="49">
+        <v>1</v>
+      </c>
+      <c r="G106" s="49">
         <v>0</v>
-      </c>
-      <c r="G106" s="49">
-        <v>1</v>
       </c>
       <c r="H106" s="48">
         <f t="shared" si="9"/>
@@ -25498,16 +25705,18 @@
       </c>
       <c r="J106" s="48">
         <f t="shared" si="10"/>
-        <v>0</v>
+        <v>976</v>
       </c>
       <c r="K106" s="48">
         <f t="shared" si="11"/>
-        <v>976</v>
-      </c>
-      <c r="L106" s="48"/>
+        <v>0</v>
+      </c>
+      <c r="L106" s="48" t="s">
+        <v>915</v>
+      </c>
       <c r="M106" s="48"/>
       <c r="N106" s="48" t="s">
-        <v>334</v>
+        <v>366</v>
       </c>
       <c r="O106" s="48" t="s">
         <v>199</v>
@@ -25520,10 +25729,10 @@
     </row>
     <row r="107" spans="1:20" ht="15" customHeight="1">
       <c r="A107" s="42" t="s">
-        <v>610</v>
+        <v>607</v>
       </c>
       <c r="B107" s="42" t="s">
-        <v>611</v>
+        <v>608</v>
       </c>
       <c r="C107" s="42" t="s">
         <v>96</v>
@@ -25574,10 +25783,10 @@
     </row>
     <row r="108" spans="1:20" ht="15" customHeight="1">
       <c r="A108" s="48" t="s">
-        <v>612</v>
+        <v>609</v>
       </c>
       <c r="B108" s="48" t="s">
-        <v>613</v>
+        <v>610</v>
       </c>
       <c r="C108" s="48" t="s">
         <v>96</v>
@@ -25628,10 +25837,10 @@
     </row>
     <row r="109" spans="1:20" ht="15" customHeight="1">
       <c r="A109" s="42" t="s">
-        <v>614</v>
+        <v>611</v>
       </c>
       <c r="B109" s="42" t="s">
-        <v>615</v>
+        <v>612</v>
       </c>
       <c r="C109" s="42" t="s">
         <v>96</v>
@@ -25682,10 +25891,10 @@
     </row>
     <row r="110" spans="1:20" ht="15" customHeight="1">
       <c r="A110" s="48" t="s">
-        <v>616</v>
+        <v>613</v>
       </c>
       <c r="B110" s="48" t="s">
-        <v>617</v>
+        <v>614</v>
       </c>
       <c r="C110" s="48" t="s">
         <v>96</v>
@@ -25736,10 +25945,10 @@
     </row>
     <row r="111" spans="1:20" ht="15" customHeight="1">
       <c r="A111" s="42" t="s">
-        <v>618</v>
+        <v>615</v>
       </c>
       <c r="B111" s="42" t="s">
-        <v>619</v>
+        <v>616</v>
       </c>
       <c r="C111" s="42" t="s">
         <v>96</v>
@@ -25790,10 +25999,10 @@
     </row>
     <row r="112" spans="1:20" ht="15" customHeight="1">
       <c r="A112" s="48" t="s">
-        <v>620</v>
+        <v>617</v>
       </c>
       <c r="B112" s="48" t="s">
-        <v>621</v>
+        <v>618</v>
       </c>
       <c r="C112" s="48" t="s">
         <v>96</v>
@@ -25829,7 +26038,7 @@
       <c r="L112" s="48"/>
       <c r="M112" s="48"/>
       <c r="N112" s="48" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="O112" s="48" t="s">
         <v>199</v>
@@ -25842,10 +26051,10 @@
     </row>
     <row r="113" spans="1:246" ht="15" customHeight="1">
       <c r="A113" s="42" t="s">
-        <v>622</v>
+        <v>619</v>
       </c>
       <c r="B113" s="42" t="s">
-        <v>623</v>
+        <v>620</v>
       </c>
       <c r="C113" s="42" t="s">
         <v>96</v>
@@ -25896,10 +26105,10 @@
     </row>
     <row r="114" spans="1:246" ht="15" customHeight="1">
       <c r="A114" s="48" t="s">
-        <v>624</v>
+        <v>621</v>
       </c>
       <c r="B114" s="48" t="s">
-        <v>625</v>
+        <v>622</v>
       </c>
       <c r="C114" s="48" t="s">
         <v>95</v>
@@ -25948,10 +26157,10 @@
     </row>
     <row r="115" spans="1:246" ht="30" customHeight="1">
       <c r="A115" s="42" t="s">
-        <v>626</v>
+        <v>623</v>
       </c>
       <c r="B115" s="42" t="s">
-        <v>627</v>
+        <v>624</v>
       </c>
       <c r="C115" s="42" t="s">
         <v>95</v>
@@ -25985,7 +26194,7 @@
         <v>0</v>
       </c>
       <c r="L115" s="42" t="s">
-        <v>628</v>
+        <v>625</v>
       </c>
       <c r="M115" s="42"/>
       <c r="N115" s="42" t="s">
@@ -26000,10 +26209,10 @@
     </row>
     <row r="116" spans="1:246" ht="150" customHeight="1">
       <c r="A116" s="48" t="s">
-        <v>629</v>
+        <v>626</v>
       </c>
       <c r="B116" s="48" t="s">
-        <v>630</v>
+        <v>627</v>
       </c>
       <c r="C116" s="48" t="s">
         <v>95</v>
@@ -26037,7 +26246,7 @@
         <v>0</v>
       </c>
       <c r="L116" s="48" t="s">
-        <v>631</v>
+        <v>628</v>
       </c>
       <c r="M116" s="48"/>
       <c r="N116" s="48" t="s">
@@ -26052,10 +26261,10 @@
     </row>
     <row r="117" spans="1:246" ht="15" customHeight="1">
       <c r="A117" s="42" t="s">
-        <v>632</v>
+        <v>629</v>
       </c>
       <c r="B117" s="42" t="s">
-        <v>633</v>
+        <v>630</v>
       </c>
       <c r="C117" s="42" t="s">
         <v>95</v>
@@ -26104,10 +26313,10 @@
     </row>
     <row r="118" spans="1:246" ht="15" customHeight="1">
       <c r="A118" s="48" t="s">
-        <v>634</v>
+        <v>631</v>
       </c>
       <c r="B118" s="48" t="s">
-        <v>635</v>
+        <v>632</v>
       </c>
       <c r="C118" s="48" t="s">
         <v>95</v>
@@ -26141,7 +26350,7 @@
         <v>2095.8000000000002</v>
       </c>
       <c r="L118" s="48" t="s">
-        <v>636</v>
+        <v>633</v>
       </c>
       <c r="M118" s="48"/>
       <c r="N118" s="48" t="s">
@@ -26149,7 +26358,7 @@
       </c>
       <c r="O118" s="48"/>
       <c r="P118" s="48" t="s">
-        <v>637</v>
+        <v>634</v>
       </c>
       <c r="Q118" s="48"/>
       <c r="R118" s="48"/>
@@ -26158,10 +26367,10 @@
     </row>
     <row r="119" spans="1:246" ht="15" customHeight="1">
       <c r="A119" s="42" t="s">
-        <v>638</v>
+        <v>635</v>
       </c>
       <c r="B119" s="42" t="s">
-        <v>639</v>
+        <v>636</v>
       </c>
       <c r="C119" s="42" t="s">
         <v>95</v>
@@ -26210,10 +26419,10 @@
     </row>
     <row r="120" spans="1:246" ht="105">
       <c r="A120" s="48" t="s">
-        <v>640</v>
+        <v>637</v>
       </c>
       <c r="B120" s="48" t="s">
-        <v>641</v>
+        <v>638</v>
       </c>
       <c r="C120" s="48" t="s">
         <v>95</v>
@@ -26225,10 +26434,10 @@
         <v>699</v>
       </c>
       <c r="F120" s="49">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G120" s="49">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="H120" s="48">
         <f t="shared" si="9"/>
@@ -26240,14 +26449,14 @@
       </c>
       <c r="J120" s="48">
         <f t="shared" si="10"/>
-        <v>7541.1599999999935</v>
+        <v>7960.1133333333264</v>
       </c>
       <c r="K120" s="48">
         <f t="shared" si="11"/>
-        <v>12987.553333333322</v>
+        <v>12568.599999999989</v>
       </c>
       <c r="L120" s="94" t="s">
-        <v>899</v>
+        <v>932</v>
       </c>
       <c r="M120" s="48" t="s">
         <v>49</v>
@@ -26257,7 +26466,7 @@
       </c>
       <c r="O120" s="48"/>
       <c r="P120" s="48" t="s">
-        <v>898</v>
+        <v>933</v>
       </c>
       <c r="Q120" s="48"/>
       <c r="R120" s="48"/>
@@ -26266,10 +26475,10 @@
     </row>
     <row r="121" spans="1:246" ht="15" customHeight="1">
       <c r="A121" s="42" t="s">
-        <v>642</v>
+        <v>639</v>
       </c>
       <c r="B121" s="42" t="s">
-        <v>643</v>
+        <v>640</v>
       </c>
       <c r="C121" s="42" t="s">
         <v>95</v>
@@ -26303,7 +26512,7 @@
         <v>0</v>
       </c>
       <c r="L121" s="42" t="s">
-        <v>644</v>
+        <v>641</v>
       </c>
       <c r="M121" s="42"/>
       <c r="N121" s="42" t="s">
@@ -26311,7 +26520,7 @@
       </c>
       <c r="O121" s="42"/>
       <c r="P121" s="42" t="s">
-        <v>645</v>
+        <v>642</v>
       </c>
       <c r="Q121" s="42"/>
       <c r="R121" s="42"/>
@@ -26320,10 +26529,10 @@
     </row>
     <row r="122" spans="1:246" ht="15" customHeight="1">
       <c r="A122" s="48" t="s">
-        <v>646</v>
+        <v>643</v>
       </c>
       <c r="B122" s="48" t="s">
-        <v>647</v>
+        <v>644</v>
       </c>
       <c r="C122" s="48" t="s">
         <v>96</v>
@@ -26335,10 +26544,10 @@
         <v>1600</v>
       </c>
       <c r="F122" s="49">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G122" s="49">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H122" s="48">
         <f t="shared" si="9"/>
@@ -26350,22 +26559,20 @@
       </c>
       <c r="J122" s="48">
         <f t="shared" si="10"/>
-        <v>1175</v>
+        <v>0</v>
       </c>
       <c r="K122" s="48">
         <f t="shared" si="11"/>
-        <v>3525</v>
+        <v>4700</v>
       </c>
       <c r="L122" s="48" t="s">
-        <v>648</v>
+        <v>885</v>
       </c>
       <c r="M122" s="48"/>
       <c r="N122" s="48" t="s">
-        <v>451</v>
-      </c>
-      <c r="O122" s="48" t="s">
-        <v>649</v>
-      </c>
+        <v>366</v>
+      </c>
+      <c r="O122" s="48"/>
       <c r="P122" s="48"/>
       <c r="Q122" s="48"/>
       <c r="R122" s="48"/>
@@ -26374,10 +26581,10 @@
     </row>
     <row r="123" spans="1:246" s="53" customFormat="1" ht="75" customHeight="1">
       <c r="A123" s="59" t="s">
-        <v>650</v>
+        <v>646</v>
       </c>
       <c r="B123" s="59" t="s">
-        <v>651</v>
+        <v>647</v>
       </c>
       <c r="C123" s="59" t="s">
         <v>95</v>
@@ -26411,7 +26618,7 @@
         <v>891.44</v>
       </c>
       <c r="L123" s="59" t="s">
-        <v>652</v>
+        <v>648</v>
       </c>
       <c r="M123" s="59"/>
       <c r="N123" s="59" t="s">
@@ -26652,10 +26859,10 @@
     </row>
     <row r="124" spans="1:246" s="64" customFormat="1" ht="30" customHeight="1">
       <c r="A124" s="61" t="s">
-        <v>653</v>
+        <v>649</v>
       </c>
       <c r="B124" s="61" t="s">
-        <v>654</v>
+        <v>650</v>
       </c>
       <c r="C124" s="61" t="s">
         <v>95</v>
@@ -26689,7 +26896,7 @@
         <v>0</v>
       </c>
       <c r="L124" s="61" t="s">
-        <v>655</v>
+        <v>651</v>
       </c>
       <c r="M124" s="61"/>
       <c r="N124" s="61" t="s">
@@ -26697,7 +26904,7 @@
       </c>
       <c r="O124" s="61"/>
       <c r="P124" s="61" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="Q124" s="61"/>
       <c r="R124" s="61"/>
@@ -26932,10 +27139,10 @@
     </row>
     <row r="125" spans="1:246" s="53" customFormat="1" ht="15" customHeight="1">
       <c r="A125" s="59" t="s">
-        <v>656</v>
+        <v>652</v>
       </c>
       <c r="B125" s="59" t="s">
-        <v>657</v>
+        <v>653</v>
       </c>
       <c r="C125" s="59" t="s">
         <v>95</v>
@@ -26969,7 +27176,7 @@
         <v>0</v>
       </c>
       <c r="L125" s="59" t="s">
-        <v>658</v>
+        <v>654</v>
       </c>
       <c r="M125" s="59"/>
       <c r="N125" s="59" t="s">
@@ -26977,7 +27184,7 @@
       </c>
       <c r="O125" s="59"/>
       <c r="P125" s="59" t="s">
-        <v>659</v>
+        <v>655</v>
       </c>
       <c r="Q125" s="59"/>
       <c r="R125" s="59"/>
@@ -27212,10 +27419,10 @@
     </row>
     <row r="126" spans="1:246" ht="15" customHeight="1">
       <c r="A126" s="61" t="s">
-        <v>660</v>
+        <v>656</v>
       </c>
       <c r="B126" s="48" t="s">
-        <v>661</v>
+        <v>657</v>
       </c>
       <c r="C126" s="48" t="s">
         <v>96</v>
@@ -27249,14 +27456,14 @@
         <v>0</v>
       </c>
       <c r="L126" s="48" t="s">
-        <v>662</v>
+        <v>658</v>
       </c>
       <c r="M126" s="48"/>
       <c r="N126" s="48" t="s">
         <v>366</v>
       </c>
       <c r="O126" s="48" t="s">
-        <v>663</v>
+        <v>659</v>
       </c>
       <c r="P126" s="48"/>
       <c r="Q126" s="48"/>
@@ -27266,10 +27473,10 @@
     </row>
     <row r="127" spans="1:246" ht="15" customHeight="1">
       <c r="A127" s="59" t="s">
-        <v>664</v>
+        <v>660</v>
       </c>
       <c r="B127" s="42" t="s">
-        <v>665</v>
+        <v>661</v>
       </c>
       <c r="C127" s="42" t="s">
         <v>96</v>
@@ -27320,10 +27527,10 @@
     </row>
     <row r="128" spans="1:246" ht="15" customHeight="1">
       <c r="A128" s="61" t="s">
-        <v>666</v>
+        <v>662</v>
       </c>
       <c r="B128" s="48" t="s">
-        <v>667</v>
+        <v>663</v>
       </c>
       <c r="C128" s="48" t="s">
         <v>95</v>
@@ -27359,7 +27566,7 @@
       <c r="L128" s="48"/>
       <c r="M128" s="48"/>
       <c r="N128" s="48" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="O128" s="48"/>
       <c r="P128" s="48"/>
@@ -27370,10 +27577,10 @@
     </row>
     <row r="129" spans="1:20" ht="15" customHeight="1">
       <c r="A129" s="59" t="s">
-        <v>668</v>
+        <v>664</v>
       </c>
       <c r="B129" s="42" t="s">
-        <v>669</v>
+        <v>665</v>
       </c>
       <c r="C129" s="42" t="s">
         <v>95</v>
@@ -27407,7 +27614,7 @@
         <v>0</v>
       </c>
       <c r="L129" s="42" t="s">
-        <v>670</v>
+        <v>666</v>
       </c>
       <c r="M129" s="42"/>
       <c r="N129" s="42" t="s">
@@ -27422,10 +27629,10 @@
     </row>
     <row r="130" spans="1:20" ht="15" customHeight="1">
       <c r="A130" s="61" t="s">
-        <v>671</v>
+        <v>667</v>
       </c>
       <c r="B130" s="48" t="s">
-        <v>672</v>
+        <v>668</v>
       </c>
       <c r="C130" s="48" t="s">
         <v>95</v>
@@ -27459,7 +27666,7 @@
         <v>0</v>
       </c>
       <c r="L130" s="48" t="s">
-        <v>673</v>
+        <v>669</v>
       </c>
       <c r="M130" s="48"/>
       <c r="N130" s="48" t="s">
@@ -27474,10 +27681,10 @@
     </row>
     <row r="131" spans="1:20" ht="15" customHeight="1">
       <c r="A131" s="59" t="s">
-        <v>674</v>
+        <v>670</v>
       </c>
       <c r="B131" s="42" t="s">
-        <v>675</v>
+        <v>671</v>
       </c>
       <c r="C131" s="42" t="s">
         <v>95</v>
@@ -27513,7 +27720,7 @@
       <c r="L131" s="42"/>
       <c r="M131" s="42"/>
       <c r="N131" s="42" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="O131" s="42"/>
       <c r="P131" s="42"/>
@@ -27524,10 +27731,10 @@
     </row>
     <row r="132" spans="1:20" ht="15" customHeight="1">
       <c r="A132" s="61" t="s">
-        <v>676</v>
+        <v>672</v>
       </c>
       <c r="B132" s="48" t="s">
-        <v>677</v>
+        <v>673</v>
       </c>
       <c r="C132" s="48" t="s">
         <v>95</v>
@@ -27561,7 +27768,7 @@
         <v>0</v>
       </c>
       <c r="L132" s="48" t="s">
-        <v>678</v>
+        <v>674</v>
       </c>
       <c r="M132" s="48"/>
       <c r="N132" s="48" t="s">
@@ -27576,10 +27783,10 @@
     </row>
     <row r="133" spans="1:20" ht="15" customHeight="1">
       <c r="A133" s="59" t="s">
-        <v>679</v>
+        <v>675</v>
       </c>
       <c r="B133" s="42" t="s">
-        <v>680</v>
+        <v>676</v>
       </c>
       <c r="C133" s="42" t="s">
         <v>95</v>
@@ -27615,7 +27822,7 @@
       <c r="L133" s="42"/>
       <c r="M133" s="42"/>
       <c r="N133" s="42" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="O133" s="42"/>
       <c r="P133" s="42"/>
@@ -27626,10 +27833,10 @@
     </row>
     <row r="134" spans="1:20" ht="15" customHeight="1">
       <c r="A134" s="61" t="s">
-        <v>681</v>
+        <v>677</v>
       </c>
       <c r="B134" s="48" t="s">
-        <v>682</v>
+        <v>678</v>
       </c>
       <c r="C134" s="48" t="s">
         <v>95</v>
@@ -27665,7 +27872,7 @@
       <c r="L134" s="48"/>
       <c r="M134" s="48"/>
       <c r="N134" s="48" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="O134" s="48"/>
       <c r="P134" s="48"/>
@@ -27676,10 +27883,10 @@
     </row>
     <row r="135" spans="1:20" ht="15" customHeight="1">
       <c r="A135" s="59" t="s">
-        <v>683</v>
+        <v>679</v>
       </c>
       <c r="B135" s="42" t="s">
-        <v>684</v>
+        <v>680</v>
       </c>
       <c r="C135" s="42" t="s">
         <v>95</v>
@@ -27713,7 +27920,7 @@
         <v>0</v>
       </c>
       <c r="L135" s="42" t="s">
-        <v>685</v>
+        <v>681</v>
       </c>
       <c r="M135" s="42"/>
       <c r="N135" s="42" t="s">
@@ -27728,10 +27935,10 @@
     </row>
     <row r="136" spans="1:20" ht="15" customHeight="1">
       <c r="A136" s="61" t="s">
-        <v>686</v>
+        <v>682</v>
       </c>
       <c r="B136" s="48" t="s">
-        <v>687</v>
+        <v>683</v>
       </c>
       <c r="C136" s="48" t="s">
         <v>95</v>
@@ -27765,7 +27972,7 @@
         <v>0</v>
       </c>
       <c r="L136" s="48" t="s">
-        <v>830</v>
+        <v>817</v>
       </c>
       <c r="M136" s="48"/>
       <c r="N136" s="48" t="s">
@@ -27773,7 +27980,7 @@
       </c>
       <c r="O136" s="48"/>
       <c r="P136" s="48" t="s">
-        <v>688</v>
+        <v>684</v>
       </c>
       <c r="Q136" s="48"/>
       <c r="R136" s="48"/>
@@ -27782,10 +27989,10 @@
     </row>
     <row r="137" spans="1:20" ht="15" customHeight="1">
       <c r="A137" s="59" t="s">
-        <v>689</v>
+        <v>685</v>
       </c>
       <c r="B137" s="42" t="s">
-        <v>690</v>
+        <v>686</v>
       </c>
       <c r="C137" s="42" t="s">
         <v>95</v>
@@ -27834,10 +28041,10 @@
     </row>
     <row r="138" spans="1:20" ht="15" customHeight="1">
       <c r="A138" s="61" t="s">
-        <v>691</v>
+        <v>687</v>
       </c>
       <c r="B138" s="48" t="s">
-        <v>692</v>
+        <v>688</v>
       </c>
       <c r="C138" s="48" t="s">
         <v>95</v>
@@ -27871,7 +28078,7 @@
         <v>0</v>
       </c>
       <c r="L138" s="48" t="s">
-        <v>829</v>
+        <v>816</v>
       </c>
       <c r="M138" s="48"/>
       <c r="N138" s="48" t="s">
@@ -27886,10 +28093,10 @@
     </row>
     <row r="139" spans="1:20" ht="15" customHeight="1">
       <c r="A139" s="59" t="s">
-        <v>693</v>
+        <v>689</v>
       </c>
       <c r="B139" s="42" t="s">
-        <v>694</v>
+        <v>690</v>
       </c>
       <c r="C139" s="42" t="s">
         <v>95</v>
@@ -27938,10 +28145,10 @@
     </row>
     <row r="140" spans="1:20" ht="15" customHeight="1">
       <c r="A140" s="61" t="s">
-        <v>695</v>
+        <v>691</v>
       </c>
       <c r="B140" s="48" t="s">
-        <v>696</v>
+        <v>692</v>
       </c>
       <c r="C140" s="48" t="s">
         <v>95</v>
@@ -27975,7 +28182,7 @@
         <v>699</v>
       </c>
       <c r="L140" s="48" t="s">
-        <v>697</v>
+        <v>693</v>
       </c>
       <c r="M140" s="48"/>
       <c r="N140" s="48" t="s">
@@ -27990,10 +28197,10 @@
     </row>
     <row r="141" spans="1:20" ht="15" customHeight="1">
       <c r="A141" s="59" t="s">
-        <v>698</v>
+        <v>694</v>
       </c>
       <c r="B141" s="42" t="s">
-        <v>699</v>
+        <v>695</v>
       </c>
       <c r="C141" s="42" t="s">
         <v>95</v>
@@ -28029,7 +28236,7 @@
       <c r="L141" s="42"/>
       <c r="M141" s="42"/>
       <c r="N141" s="42" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="O141" s="42"/>
       <c r="P141" s="42"/>
@@ -28040,10 +28247,10 @@
     </row>
     <row r="142" spans="1:20" ht="15" customHeight="1">
       <c r="A142" s="48" t="s">
-        <v>700</v>
+        <v>696</v>
       </c>
       <c r="B142" s="48" t="s">
-        <v>701</v>
+        <v>697</v>
       </c>
       <c r="C142" s="48" t="s">
         <v>95</v>
@@ -28077,7 +28284,7 @@
         <v>600</v>
       </c>
       <c r="L142" s="48" t="s">
-        <v>702</v>
+        <v>698</v>
       </c>
       <c r="M142" s="48"/>
       <c r="N142" s="48" t="s">
@@ -28094,10 +28301,10 @@
     </row>
     <row r="143" spans="1:20" ht="15" customHeight="1">
       <c r="A143" s="42" t="s">
-        <v>703</v>
+        <v>699</v>
       </c>
       <c r="B143" s="42" t="s">
-        <v>704</v>
+        <v>700</v>
       </c>
       <c r="C143" s="42" t="s">
         <v>95</v>
@@ -28133,7 +28340,7 @@
       <c r="L143" s="42"/>
       <c r="M143" s="42"/>
       <c r="N143" s="42" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="O143" s="42"/>
       <c r="P143" s="42"/>
@@ -28144,10 +28351,10 @@
     </row>
     <row r="144" spans="1:20" ht="15" customHeight="1">
       <c r="A144" s="48" t="s">
-        <v>705</v>
+        <v>701</v>
       </c>
       <c r="B144" s="48" t="s">
-        <v>706</v>
+        <v>702</v>
       </c>
       <c r="C144" s="48" t="s">
         <v>95</v>
@@ -28183,7 +28390,7 @@
       <c r="L144" s="48"/>
       <c r="M144" s="48"/>
       <c r="N144" s="48" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="O144" s="48"/>
       <c r="P144" s="48"/>
@@ -28194,7 +28401,7 @@
     </row>
     <row r="145" spans="1:20" ht="15" customHeight="1">
       <c r="A145" s="42" t="s">
-        <v>707</v>
+        <v>703</v>
       </c>
       <c r="B145" s="42" t="s">
         <v>294</v>
@@ -28246,10 +28453,10 @@
     </row>
     <row r="146" spans="1:20" ht="15" customHeight="1">
       <c r="A146" s="48" t="s">
-        <v>708</v>
+        <v>704</v>
       </c>
       <c r="B146" s="48" t="s">
-        <v>709</v>
+        <v>705</v>
       </c>
       <c r="C146" s="48" t="s">
         <v>95</v>
@@ -28261,10 +28468,10 @@
         <v>1200</v>
       </c>
       <c r="F146" s="62">
+        <v>2</v>
+      </c>
+      <c r="G146" s="62">
         <v>1</v>
-      </c>
-      <c r="G146" s="62">
-        <v>2</v>
       </c>
       <c r="H146" s="61">
         <f t="shared" si="12"/>
@@ -28276,21 +28483,23 @@
       </c>
       <c r="J146" s="61">
         <f t="shared" si="13"/>
-        <v>761</v>
+        <v>1522</v>
       </c>
       <c r="K146" s="61">
         <f t="shared" si="14"/>
-        <v>1522</v>
+        <v>761</v>
       </c>
       <c r="L146" s="48" t="s">
-        <v>710</v>
+        <v>905</v>
       </c>
       <c r="M146" s="48"/>
       <c r="N146" s="48" t="s">
         <v>451</v>
       </c>
       <c r="O146" s="48"/>
-      <c r="P146" s="48"/>
+      <c r="P146" s="48" t="s">
+        <v>906</v>
+      </c>
       <c r="Q146" s="48"/>
       <c r="R146" s="48"/>
       <c r="S146" s="48"/>
@@ -28298,10 +28507,10 @@
     </row>
     <row r="147" spans="1:20" ht="64" customHeight="1">
       <c r="A147" s="42" t="s">
-        <v>711</v>
+        <v>706</v>
       </c>
       <c r="B147" s="42" t="s">
-        <v>712</v>
+        <v>707</v>
       </c>
       <c r="C147" s="42" t="s">
         <v>95</v>
@@ -28335,7 +28544,7 @@
         <v>4314</v>
       </c>
       <c r="L147" s="42" t="s">
-        <v>907</v>
+        <v>882</v>
       </c>
       <c r="M147" s="42"/>
       <c r="N147" s="42" t="s">
@@ -28343,7 +28552,7 @@
       </c>
       <c r="O147" s="42"/>
       <c r="P147" s="42" t="s">
-        <v>906</v>
+        <v>881</v>
       </c>
       <c r="Q147" s="42"/>
       <c r="R147" s="42"/>
@@ -28352,10 +28561,10 @@
     </row>
     <row r="148" spans="1:20" ht="15" customHeight="1">
       <c r="A148" s="48" t="s">
-        <v>713</v>
+        <v>708</v>
       </c>
       <c r="B148" s="48" t="s">
-        <v>714</v>
+        <v>709</v>
       </c>
       <c r="C148" s="48" t="s">
         <v>95</v>
@@ -28389,7 +28598,7 @@
         <v>502</v>
       </c>
       <c r="L148" s="48" t="s">
-        <v>715</v>
+        <v>710</v>
       </c>
       <c r="M148" s="48"/>
       <c r="N148" s="48" t="s">
@@ -28404,10 +28613,10 @@
     </row>
     <row r="149" spans="1:20" ht="15" customHeight="1">
       <c r="A149" s="42" t="s">
-        <v>716</v>
+        <v>711</v>
       </c>
       <c r="B149" s="42" t="s">
-        <v>717</v>
+        <v>712</v>
       </c>
       <c r="C149" s="42" t="s">
         <v>95</v>
@@ -28441,7 +28650,7 @@
         <v>1024</v>
       </c>
       <c r="L149" s="42" t="s">
-        <v>718</v>
+        <v>930</v>
       </c>
       <c r="M149" s="42"/>
       <c r="N149" s="42" t="s">
@@ -28456,10 +28665,10 @@
     </row>
     <row r="150" spans="1:20" ht="15" customHeight="1">
       <c r="A150" s="48" t="s">
-        <v>719</v>
+        <v>713</v>
       </c>
       <c r="B150" s="48" t="s">
-        <v>720</v>
+        <v>714</v>
       </c>
       <c r="C150" s="48" t="s">
         <v>95</v>
@@ -28495,7 +28704,7 @@
       <c r="L150" s="48"/>
       <c r="M150" s="48"/>
       <c r="N150" s="48" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="O150" s="48"/>
       <c r="P150" s="48"/>
@@ -28506,10 +28715,10 @@
     </row>
     <row r="151" spans="1:20" ht="15" customHeight="1">
       <c r="A151" s="42" t="s">
-        <v>721</v>
+        <v>715</v>
       </c>
       <c r="B151" s="42" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="C151" s="42" t="s">
         <v>96</v>
@@ -28543,7 +28752,7 @@
         <v>645</v>
       </c>
       <c r="L151" s="42" t="s">
-        <v>822</v>
+        <v>811</v>
       </c>
       <c r="M151" s="42"/>
       <c r="N151" s="42" t="s">
@@ -28553,7 +28762,7 @@
         <v>208</v>
       </c>
       <c r="P151" s="42" t="s">
-        <v>723</v>
+        <v>717</v>
       </c>
       <c r="Q151" s="42"/>
       <c r="R151" s="42"/>
@@ -28562,10 +28771,10 @@
     </row>
     <row r="152" spans="1:20" ht="15" customHeight="1">
       <c r="A152" s="48" t="s">
-        <v>724</v>
+        <v>718</v>
       </c>
       <c r="B152" s="48" t="s">
-        <v>725</v>
+        <v>719</v>
       </c>
       <c r="C152" s="48" t="s">
         <v>97</v>
@@ -28599,17 +28808,17 @@
         <v>885</v>
       </c>
       <c r="L152" s="48" t="s">
-        <v>726</v>
+        <v>720</v>
       </c>
       <c r="M152" s="48"/>
       <c r="N152" s="48" t="s">
         <v>451</v>
       </c>
       <c r="O152" s="48" t="s">
-        <v>727</v>
+        <v>721</v>
       </c>
       <c r="P152" s="48" t="s">
-        <v>728</v>
+        <v>722</v>
       </c>
       <c r="Q152" s="48"/>
       <c r="R152" s="48"/>
@@ -28618,10 +28827,10 @@
     </row>
     <row r="153" spans="1:20" ht="15" customHeight="1">
       <c r="A153" s="42" t="s">
-        <v>729</v>
+        <v>723</v>
       </c>
       <c r="B153" s="42" t="s">
-        <v>730</v>
+        <v>724</v>
       </c>
       <c r="C153" s="42" t="s">
         <v>95</v>
@@ -28655,7 +28864,7 @@
         <v>891.5</v>
       </c>
       <c r="L153" s="42" t="s">
-        <v>731</v>
+        <v>725</v>
       </c>
       <c r="M153" s="42"/>
       <c r="N153" s="42" t="s">
@@ -28663,7 +28872,7 @@
       </c>
       <c r="O153" s="42"/>
       <c r="P153" s="42" t="s">
-        <v>732</v>
+        <v>726</v>
       </c>
       <c r="Q153" s="42"/>
       <c r="R153" s="42"/>
@@ -28672,10 +28881,10 @@
     </row>
     <row r="154" spans="1:20" ht="15" customHeight="1">
       <c r="A154" s="48" t="s">
-        <v>733</v>
+        <v>727</v>
       </c>
       <c r="B154" s="48" t="s">
-        <v>734</v>
+        <v>728</v>
       </c>
       <c r="C154" s="48" t="s">
         <v>96</v>
@@ -28687,10 +28896,10 @@
         <v>1450</v>
       </c>
       <c r="F154" s="62">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G154" s="62">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H154" s="61">
         <f t="shared" si="12"/>
@@ -28702,19 +28911,21 @@
       </c>
       <c r="J154" s="61">
         <f t="shared" si="13"/>
-        <v>0</v>
+        <v>949</v>
       </c>
       <c r="K154" s="61">
         <f t="shared" si="14"/>
-        <v>2847</v>
-      </c>
-      <c r="L154" s="48"/>
+        <v>1898</v>
+      </c>
+      <c r="L154" s="48" t="s">
+        <v>925</v>
+      </c>
       <c r="M154" s="48"/>
       <c r="N154" s="48" t="s">
-        <v>538</v>
+        <v>451</v>
       </c>
       <c r="O154" s="48" t="s">
-        <v>735</v>
+        <v>926</v>
       </c>
       <c r="P154" s="48"/>
       <c r="Q154" s="48"/>
@@ -28724,10 +28935,10 @@
     </row>
     <row r="155" spans="1:20" ht="15" customHeight="1">
       <c r="A155" s="42" t="s">
-        <v>736</v>
+        <v>730</v>
       </c>
       <c r="B155" s="42" t="s">
-        <v>737</v>
+        <v>731</v>
       </c>
       <c r="C155" s="42" t="s">
         <v>96</v>
@@ -28763,10 +28974,10 @@
       <c r="L155" s="42"/>
       <c r="M155" s="42"/>
       <c r="N155" s="42" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="O155" s="42" t="s">
-        <v>735</v>
+        <v>729</v>
       </c>
       <c r="P155" s="42"/>
       <c r="Q155" s="42"/>
@@ -28776,10 +28987,10 @@
     </row>
     <row r="156" spans="1:20" ht="15" customHeight="1">
       <c r="A156" s="48" t="s">
-        <v>738</v>
+        <v>732</v>
       </c>
       <c r="B156" s="48" t="s">
-        <v>739</v>
+        <v>733</v>
       </c>
       <c r="C156" s="48" t="s">
         <v>96</v>
@@ -28791,10 +29002,10 @@
         <v>1550</v>
       </c>
       <c r="F156" s="62">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G156" s="62">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H156" s="61">
         <f t="shared" si="12"/>
@@ -28806,19 +29017,21 @@
       </c>
       <c r="J156" s="61">
         <f t="shared" si="13"/>
-        <v>0</v>
+        <v>950</v>
       </c>
       <c r="K156" s="61">
         <f t="shared" si="14"/>
-        <v>3800</v>
-      </c>
-      <c r="L156" s="48"/>
+        <v>2850</v>
+      </c>
+      <c r="L156" s="48" t="s">
+        <v>923</v>
+      </c>
       <c r="M156" s="48"/>
       <c r="N156" s="48" t="s">
-        <v>538</v>
+        <v>451</v>
       </c>
       <c r="O156" s="48" t="s">
-        <v>740</v>
+        <v>729</v>
       </c>
       <c r="P156" s="48"/>
       <c r="Q156" s="48"/>
@@ -28828,10 +29041,10 @@
     </row>
     <row r="157" spans="1:20" ht="15" customHeight="1">
       <c r="A157" s="42" t="s">
-        <v>741</v>
+        <v>734</v>
       </c>
       <c r="B157" s="42" t="s">
-        <v>742</v>
+        <v>735</v>
       </c>
       <c r="C157" s="42" t="s">
         <v>96</v>
@@ -28865,14 +29078,14 @@
         <v>1575</v>
       </c>
       <c r="L157" s="42" t="s">
-        <v>743</v>
+        <v>736</v>
       </c>
       <c r="M157" s="42"/>
       <c r="N157" s="42" t="s">
         <v>451</v>
       </c>
       <c r="O157" s="42" t="s">
-        <v>649</v>
+        <v>645</v>
       </c>
       <c r="P157" s="42"/>
       <c r="Q157" s="42"/>
@@ -28882,10 +29095,10 @@
     </row>
     <row r="158" spans="1:20" ht="15" customHeight="1">
       <c r="A158" s="48" t="s">
-        <v>744</v>
+        <v>737</v>
       </c>
       <c r="B158" s="48" t="s">
-        <v>745</v>
+        <v>738</v>
       </c>
       <c r="C158" s="48" t="s">
         <v>96</v>
@@ -28919,14 +29132,14 @@
         <v>3356</v>
       </c>
       <c r="L158" s="48" t="s">
-        <v>825</v>
+        <v>812</v>
       </c>
       <c r="M158" s="48"/>
       <c r="N158" s="48" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="O158" s="48" t="s">
-        <v>826</v>
+        <v>813</v>
       </c>
       <c r="P158" s="48"/>
       <c r="Q158" s="48"/>
@@ -28936,10 +29149,10 @@
     </row>
     <row r="159" spans="1:20" ht="15" customHeight="1">
       <c r="A159" s="42" t="s">
-        <v>746</v>
+        <v>739</v>
       </c>
       <c r="B159" s="42" t="s">
-        <v>747</v>
+        <v>740</v>
       </c>
       <c r="C159" s="42" t="s">
         <v>96</v>
@@ -28951,10 +29164,10 @@
         <v>1450</v>
       </c>
       <c r="F159" s="60">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G159" s="60">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H159" s="59">
         <f t="shared" si="12"/>
@@ -28966,21 +29179,21 @@
       </c>
       <c r="J159" s="59">
         <f t="shared" si="13"/>
-        <v>839</v>
+        <v>1678</v>
       </c>
       <c r="K159" s="59">
         <f t="shared" si="14"/>
-        <v>3356</v>
+        <v>2517</v>
       </c>
       <c r="L159" s="42" t="s">
-        <v>823</v>
+        <v>921</v>
       </c>
       <c r="M159" s="42"/>
       <c r="N159" s="42" t="s">
-        <v>538</v>
+        <v>451</v>
       </c>
       <c r="O159" s="42" t="s">
-        <v>824</v>
+        <v>922</v>
       </c>
       <c r="P159" s="42"/>
       <c r="Q159" s="42"/>
@@ -28990,10 +29203,10 @@
     </row>
     <row r="160" spans="1:20" ht="15" customHeight="1">
       <c r="A160" s="48" t="s">
-        <v>748</v>
+        <v>741</v>
       </c>
       <c r="B160" s="48" t="s">
-        <v>749</v>
+        <v>742</v>
       </c>
       <c r="C160" s="48" t="s">
         <v>95</v>
@@ -29042,10 +29255,10 @@
     </row>
     <row r="161" spans="1:20" ht="15" customHeight="1">
       <c r="A161" s="42" t="s">
-        <v>750</v>
+        <v>743</v>
       </c>
       <c r="B161" s="42" t="s">
-        <v>751</v>
+        <v>744</v>
       </c>
       <c r="C161" s="42" t="s">
         <v>95</v>
@@ -29094,10 +29307,10 @@
     </row>
     <row r="162" spans="1:20" ht="15" customHeight="1">
       <c r="A162" s="48" t="s">
-        <v>752</v>
+        <v>745</v>
       </c>
       <c r="B162" s="48" t="s">
-        <v>753</v>
+        <v>887</v>
       </c>
       <c r="C162" s="48" t="s">
         <v>95</v>
@@ -29106,7 +29319,7 @@
         <v>533</v>
       </c>
       <c r="E162" s="49">
-        <v>750</v>
+        <v>600</v>
       </c>
       <c r="F162" s="62">
         <v>0</v>
@@ -29130,10 +29343,12 @@
         <f t="shared" ref="K162:K175" si="17">IF(LEN(G162)=0,0,G162)*I162</f>
         <v>533</v>
       </c>
-      <c r="L162" s="48"/>
+      <c r="L162" s="48" t="s">
+        <v>153</v>
+      </c>
       <c r="M162" s="48"/>
       <c r="N162" s="48" t="s">
-        <v>538</v>
+        <v>366</v>
       </c>
       <c r="O162" s="48"/>
       <c r="P162" s="48"/>
@@ -29144,10 +29359,10 @@
     </row>
     <row r="163" spans="1:20" ht="15" customHeight="1">
       <c r="A163" s="42" t="s">
-        <v>754</v>
+        <v>746</v>
       </c>
       <c r="B163" s="42" t="s">
-        <v>755</v>
+        <v>888</v>
       </c>
       <c r="C163" s="42" t="s">
         <v>95</v>
@@ -29156,7 +29371,7 @@
         <v>441</v>
       </c>
       <c r="E163" s="51">
-        <v>750</v>
+        <v>600</v>
       </c>
       <c r="F163" s="60">
         <v>0</v>
@@ -29183,7 +29398,7 @@
       <c r="L163" s="42"/>
       <c r="M163" s="42"/>
       <c r="N163" s="42" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="O163" s="42"/>
       <c r="P163" s="42"/>
@@ -29194,10 +29409,10 @@
     </row>
     <row r="164" spans="1:20" ht="60" customHeight="1">
       <c r="A164" s="48" t="s">
-        <v>756</v>
+        <v>747</v>
       </c>
       <c r="B164" s="48" t="s">
-        <v>757</v>
+        <v>748</v>
       </c>
       <c r="C164" s="48" t="s">
         <v>95</v>
@@ -29209,10 +29424,10 @@
         <v>1499</v>
       </c>
       <c r="F164" s="62">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G164" s="62">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="H164" s="61">
         <f t="shared" si="15"/>
@@ -29224,20 +29439,22 @@
       </c>
       <c r="J164" s="61">
         <f t="shared" si="16"/>
-        <v>0</v>
+        <v>3039</v>
       </c>
       <c r="K164" s="61">
         <f t="shared" si="17"/>
-        <v>5065</v>
-      </c>
-      <c r="L164" s="48"/>
+        <v>2026</v>
+      </c>
+      <c r="L164" s="48" t="s">
+        <v>918</v>
+      </c>
       <c r="M164" s="48"/>
       <c r="N164" s="48" t="s">
-        <v>538</v>
+        <v>451</v>
       </c>
       <c r="O164" s="48"/>
       <c r="P164" s="48" t="s">
-        <v>758</v>
+        <v>920</v>
       </c>
       <c r="Q164" s="48"/>
       <c r="R164" s="48"/>
@@ -29246,10 +29463,10 @@
     </row>
     <row r="165" spans="1:20" ht="15" customHeight="1">
       <c r="A165" s="42" t="s">
-        <v>759</v>
+        <v>749</v>
       </c>
       <c r="B165" s="42" t="s">
-        <v>760</v>
+        <v>750</v>
       </c>
       <c r="C165" s="42" t="s">
         <v>95</v>
@@ -29291,7 +29508,7 @@
       </c>
       <c r="O165" s="42"/>
       <c r="P165" s="42" t="s">
-        <v>761</v>
+        <v>751</v>
       </c>
       <c r="Q165" s="42"/>
       <c r="R165" s="42"/>
@@ -29300,10 +29517,10 @@
     </row>
     <row r="166" spans="1:20" ht="15" customHeight="1">
       <c r="A166" s="48" t="s">
-        <v>762</v>
+        <v>752</v>
       </c>
       <c r="B166" s="48" t="s">
-        <v>763</v>
+        <v>753</v>
       </c>
       <c r="C166" s="48" t="s">
         <v>95</v>
@@ -29339,11 +29556,11 @@
       <c r="L166" s="48"/>
       <c r="M166" s="48"/>
       <c r="N166" s="48" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="O166" s="48"/>
       <c r="P166" s="48" t="s">
-        <v>764</v>
+        <v>754</v>
       </c>
       <c r="Q166" s="48"/>
       <c r="R166" s="48"/>
@@ -29352,10 +29569,10 @@
     </row>
     <row r="167" spans="1:20" ht="15" customHeight="1">
       <c r="A167" s="42" t="s">
-        <v>765</v>
+        <v>755</v>
       </c>
       <c r="B167" s="42" t="s">
-        <v>766</v>
+        <v>756</v>
       </c>
       <c r="C167" s="42" t="s">
         <v>95</v>
@@ -29389,7 +29606,7 @@
         <v>2220</v>
       </c>
       <c r="L167" s="42" t="s">
-        <v>767</v>
+        <v>757</v>
       </c>
       <c r="M167" s="42"/>
       <c r="N167" s="42" t="s">
@@ -29397,7 +29614,7 @@
       </c>
       <c r="O167" s="42"/>
       <c r="P167" s="42" t="s">
-        <v>768</v>
+        <v>758</v>
       </c>
       <c r="Q167" s="42"/>
       <c r="R167" s="42"/>
@@ -29406,10 +29623,10 @@
     </row>
     <row r="168" spans="1:20" ht="15" customHeight="1">
       <c r="A168" s="48" t="s">
-        <v>769</v>
+        <v>759</v>
       </c>
       <c r="B168" s="48" t="s">
-        <v>770</v>
+        <v>760</v>
       </c>
       <c r="C168" s="48" t="s">
         <v>95</v>
@@ -29443,7 +29660,7 @@
         <v>1216</v>
       </c>
       <c r="L168" s="48" t="s">
-        <v>857</v>
+        <v>841</v>
       </c>
       <c r="M168" s="48"/>
       <c r="N168" s="48" t="s">
@@ -29451,7 +29668,7 @@
       </c>
       <c r="O168" s="48"/>
       <c r="P168" s="48" t="s">
-        <v>858</v>
+        <v>842</v>
       </c>
       <c r="Q168" s="48"/>
       <c r="R168" s="48"/>
@@ -29460,10 +29677,10 @@
     </row>
     <row r="169" spans="1:20" ht="15" customHeight="1">
       <c r="A169" s="42" t="s">
-        <v>771</v>
+        <v>761</v>
       </c>
       <c r="B169" s="42" t="s">
-        <v>772</v>
+        <v>762</v>
       </c>
       <c r="C169" s="42" t="s">
         <v>95</v>
@@ -29499,11 +29716,11 @@
       <c r="L169" s="42"/>
       <c r="M169" s="42"/>
       <c r="N169" s="42" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="O169" s="42"/>
       <c r="P169" s="42" t="s">
-        <v>773</v>
+        <v>763</v>
       </c>
       <c r="Q169" s="42"/>
       <c r="R169" s="42"/>
@@ -29512,10 +29729,10 @@
     </row>
     <row r="170" spans="1:20" ht="30" customHeight="1">
       <c r="A170" s="48" t="s">
-        <v>774</v>
+        <v>764</v>
       </c>
       <c r="B170" s="48" t="s">
-        <v>775</v>
+        <v>765</v>
       </c>
       <c r="C170" s="48" t="s">
         <v>95</v>
@@ -29549,7 +29766,7 @@
         <v>0</v>
       </c>
       <c r="L170" s="48" t="s">
-        <v>815</v>
+        <v>805</v>
       </c>
       <c r="M170" s="48"/>
       <c r="N170" s="48" t="s">
@@ -29557,7 +29774,7 @@
       </c>
       <c r="O170" s="48"/>
       <c r="P170" s="48" t="s">
-        <v>776</v>
+        <v>766</v>
       </c>
       <c r="Q170" s="48"/>
       <c r="R170" s="48"/>
@@ -29566,10 +29783,10 @@
     </row>
     <row r="171" spans="1:20" ht="32" customHeight="1">
       <c r="A171" s="42" t="s">
-        <v>777</v>
+        <v>767</v>
       </c>
       <c r="B171" s="48" t="s">
-        <v>778</v>
+        <v>768</v>
       </c>
       <c r="C171" s="42" t="s">
         <v>95</v>
@@ -29603,7 +29820,7 @@
         <v>0</v>
       </c>
       <c r="L171" s="42" t="s">
-        <v>855</v>
+        <v>839</v>
       </c>
       <c r="M171" s="42"/>
       <c r="N171" s="42" t="s">
@@ -29618,10 +29835,10 @@
     </row>
     <row r="172" spans="1:20" ht="15" customHeight="1">
       <c r="A172" s="48" t="s">
-        <v>779</v>
+        <v>769</v>
       </c>
       <c r="B172" s="48" t="s">
-        <v>780</v>
+        <v>770</v>
       </c>
       <c r="C172" s="48" t="s">
         <v>95</v>
@@ -29636,11 +29853,11 @@
         <v>0</v>
       </c>
       <c r="G172" s="62">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H172" s="61">
         <f t="shared" si="15"/>
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I172" s="61">
         <f>IF(D172&lt;&gt;"",D172,IFERROR(E172/(IFERROR(SUM(Sales!C:C),0))*(IFERROR(SUM(Purchases!C:C),0)),0))</f>
@@ -29652,12 +29869,12 @@
       </c>
       <c r="K172" s="61">
         <f t="shared" si="17"/>
-        <v>1047</v>
+        <v>4188</v>
       </c>
       <c r="L172" s="48"/>
       <c r="M172" s="48"/>
       <c r="N172" s="48" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="O172" s="48"/>
       <c r="P172" s="48"/>
@@ -29668,10 +29885,10 @@
     </row>
     <row r="173" spans="1:20" ht="15" customHeight="1">
       <c r="A173" s="42" t="s">
-        <v>781</v>
+        <v>771</v>
       </c>
       <c r="B173" s="42" t="s">
-        <v>782</v>
+        <v>772</v>
       </c>
       <c r="C173" s="42" t="s">
         <v>95</v>
@@ -29683,14 +29900,14 @@
         <v>1250</v>
       </c>
       <c r="F173" s="60">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G173" s="60">
         <v>1</v>
       </c>
       <c r="H173" s="59">
         <f t="shared" si="15"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I173" s="59">
         <f>IF(D173&lt;&gt;"",D173,IFERROR(E173/(IFERROR(SUM(Sales!C:C),0))*(IFERROR(SUM(Purchases!C:C),0)),0))</f>
@@ -29698,16 +29915,18 @@
       </c>
       <c r="J173" s="59">
         <f t="shared" si="16"/>
-        <v>0</v>
+        <v>803.26</v>
       </c>
       <c r="K173" s="59">
         <f t="shared" si="17"/>
         <v>803.26</v>
       </c>
-      <c r="L173" s="42"/>
+      <c r="L173" s="42" t="s">
+        <v>914</v>
+      </c>
       <c r="M173" s="42"/>
       <c r="N173" s="42" t="s">
-        <v>538</v>
+        <v>451</v>
       </c>
       <c r="O173" s="42"/>
       <c r="P173" s="42"/>
@@ -29718,10 +29937,10 @@
     </row>
     <row r="174" spans="1:20" ht="15" customHeight="1">
       <c r="A174" s="48" t="s">
-        <v>783</v>
+        <v>773</v>
       </c>
       <c r="B174" s="48" t="s">
-        <v>784</v>
+        <v>774</v>
       </c>
       <c r="C174" s="48" t="s">
         <v>95</v>
@@ -29733,10 +29952,10 @@
         <v>1250</v>
       </c>
       <c r="F174" s="62">
+        <v>1</v>
+      </c>
+      <c r="G174" s="62">
         <v>0</v>
-      </c>
-      <c r="G174" s="62">
-        <v>1</v>
       </c>
       <c r="H174" s="61">
         <f t="shared" si="15"/>
@@ -29748,16 +29967,18 @@
       </c>
       <c r="J174" s="61">
         <f t="shared" si="16"/>
-        <v>0</v>
+        <v>791.7</v>
       </c>
       <c r="K174" s="61">
         <f t="shared" si="17"/>
-        <v>791.7</v>
-      </c>
-      <c r="L174" s="48"/>
+        <v>0</v>
+      </c>
+      <c r="L174" s="48" t="s">
+        <v>893</v>
+      </c>
       <c r="M174" s="48"/>
       <c r="N174" s="48" t="s">
-        <v>538</v>
+        <v>366</v>
       </c>
       <c r="O174" s="48"/>
       <c r="P174" s="48"/>
@@ -29768,10 +29989,10 @@
     </row>
     <row r="175" spans="1:20" ht="90" customHeight="1">
       <c r="A175" s="42" t="s">
-        <v>785</v>
+        <v>775</v>
       </c>
       <c r="B175" s="42" t="s">
-        <v>786</v>
+        <v>776</v>
       </c>
       <c r="C175" s="42" t="s">
         <v>95</v>
@@ -29783,14 +30004,14 @@
         <v>1250</v>
       </c>
       <c r="F175" s="60">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G175" s="60">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="H175" s="59">
         <f t="shared" si="15"/>
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="I175" s="59">
         <f>IF(D175&lt;&gt;"",D175,IFERROR(E175/(IFERROR(SUM(Sales!C:C),0))*(IFERROR(SUM(Purchases!C:C),0)),0))</f>
@@ -29798,14 +30019,14 @@
       </c>
       <c r="J175" s="59">
         <f t="shared" si="16"/>
-        <v>698.25</v>
+        <v>1396.5</v>
       </c>
       <c r="K175" s="59">
         <f t="shared" si="17"/>
-        <v>6284.25</v>
+        <v>4887.75</v>
       </c>
       <c r="L175" s="42" t="s">
-        <v>860</v>
+        <v>911</v>
       </c>
       <c r="M175" s="42"/>
       <c r="N175" s="42" t="s">
@@ -29813,7 +30034,7 @@
       </c>
       <c r="O175" s="42"/>
       <c r="P175" s="42" t="s">
-        <v>859</v>
+        <v>912</v>
       </c>
       <c r="Q175" s="42"/>
       <c r="R175" s="42"/>
@@ -29822,10 +30043,10 @@
     </row>
     <row r="176" spans="1:20" ht="15">
       <c r="A176" s="48" t="s">
-        <v>866</v>
+        <v>847</v>
       </c>
       <c r="B176" s="48" t="s">
-        <v>892</v>
+        <v>869</v>
       </c>
       <c r="C176" s="48" t="s">
         <v>95</v>
@@ -29837,10 +30058,10 @@
         <v>1350</v>
       </c>
       <c r="F176" s="62">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G176" s="62">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H176" s="61">
         <f t="shared" ref="H176:H180" si="18">F176+IF(LEN(G176)=0,0,G176)</f>
@@ -29852,20 +30073,22 @@
       </c>
       <c r="J176" s="61">
         <f t="shared" ref="J176:J180" si="19">F176*I176</f>
-        <v>0</v>
+        <v>1816</v>
       </c>
       <c r="K176" s="61">
         <f t="shared" ref="K176:K180" si="20">IF(LEN(G176)=0,0,G176)*I176</f>
-        <v>3632</v>
-      </c>
-      <c r="L176" s="48"/>
+        <v>1816</v>
+      </c>
+      <c r="L176" s="48" t="s">
+        <v>917</v>
+      </c>
       <c r="M176" s="48"/>
       <c r="N176" s="48" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="O176" s="48"/>
       <c r="P176" s="48" t="s">
-        <v>865</v>
+        <v>919</v>
       </c>
       <c r="Q176" s="48"/>
       <c r="R176" s="48"/>
@@ -29874,10 +30097,10 @@
     </row>
     <row r="177" spans="1:20" ht="15">
       <c r="A177" s="42" t="s">
-        <v>868</v>
+        <v>848</v>
       </c>
       <c r="B177" s="42" t="s">
-        <v>893</v>
+        <v>870</v>
       </c>
       <c r="C177" s="42" t="s">
         <v>95</v>
@@ -29889,10 +30112,10 @@
         <v>1350</v>
       </c>
       <c r="F177" s="60">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G177" s="60">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="H177" s="59">
         <f t="shared" si="18"/>
@@ -29904,20 +30127,22 @@
       </c>
       <c r="J177" s="59">
         <f t="shared" si="19"/>
-        <v>0</v>
+        <v>2718</v>
       </c>
       <c r="K177" s="59">
         <f t="shared" si="20"/>
-        <v>4530</v>
-      </c>
-      <c r="L177" s="42"/>
+        <v>1812</v>
+      </c>
+      <c r="L177" s="42" t="s">
+        <v>896</v>
+      </c>
       <c r="M177" s="42"/>
       <c r="N177" s="42" t="s">
-        <v>538</v>
+        <v>451</v>
       </c>
       <c r="O177" s="42"/>
       <c r="P177" s="42" t="s">
-        <v>867</v>
+        <v>897</v>
       </c>
       <c r="Q177" s="42"/>
       <c r="R177" s="42"/>
@@ -29926,10 +30151,10 @@
     </row>
     <row r="178" spans="1:20" ht="15">
       <c r="A178" s="48" t="s">
-        <v>869</v>
+        <v>849</v>
       </c>
       <c r="B178" s="48" t="s">
-        <v>894</v>
+        <v>871</v>
       </c>
       <c r="C178" s="48" t="s">
         <v>95</v>
@@ -29941,10 +30166,10 @@
         <v>1400</v>
       </c>
       <c r="F178" s="62">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G178" s="62">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H178" s="61">
         <f t="shared" si="18"/>
@@ -29956,32 +30181,34 @@
       </c>
       <c r="J178" s="61">
         <f t="shared" si="19"/>
-        <v>0</v>
+        <v>938</v>
       </c>
       <c r="K178" s="61">
         <f t="shared" si="20"/>
-        <v>1876</v>
-      </c>
-      <c r="L178" s="48"/>
+        <v>938</v>
+      </c>
+      <c r="L178" s="48" t="s">
+        <v>899</v>
+      </c>
       <c r="M178" s="48"/>
       <c r="N178" s="48" t="s">
-        <v>538</v>
+        <v>451</v>
       </c>
       <c r="O178" s="48"/>
       <c r="P178" s="48" t="s">
-        <v>880</v>
+        <v>898</v>
       </c>
       <c r="Q178" s="48"/>
       <c r="R178" s="48"/>
       <c r="S178" s="48"/>
       <c r="T178" s="48"/>
     </row>
-    <row r="179" spans="1:20" ht="15">
+    <row r="179" spans="1:20" ht="30">
       <c r="A179" s="42" t="s">
-        <v>870</v>
+        <v>850</v>
       </c>
       <c r="B179" s="42" t="s">
-        <v>895</v>
+        <v>872</v>
       </c>
       <c r="C179" s="42" t="s">
         <v>95</v>
@@ -29993,10 +30220,10 @@
         <v>1350</v>
       </c>
       <c r="F179" s="60">
+        <v>3</v>
+      </c>
+      <c r="G179" s="60">
         <v>0</v>
-      </c>
-      <c r="G179" s="60">
-        <v>3</v>
       </c>
       <c r="H179" s="59">
         <f t="shared" si="18"/>
@@ -30008,20 +30235,22 @@
       </c>
       <c r="J179" s="59">
         <f t="shared" si="19"/>
-        <v>0</v>
+        <v>2757</v>
       </c>
       <c r="K179" s="59">
         <f t="shared" si="20"/>
-        <v>2757</v>
-      </c>
-      <c r="L179" s="42"/>
+        <v>0</v>
+      </c>
+      <c r="L179" s="42" t="s">
+        <v>927</v>
+      </c>
       <c r="M179" s="42"/>
       <c r="N179" s="42" t="s">
-        <v>538</v>
+        <v>366</v>
       </c>
       <c r="O179" s="42"/>
       <c r="P179" s="42" t="s">
-        <v>881</v>
+        <v>909</v>
       </c>
       <c r="Q179" s="42"/>
       <c r="R179" s="42"/>
@@ -30030,10 +30259,10 @@
     </row>
     <row r="180" spans="1:20" ht="15">
       <c r="A180" s="48" t="s">
-        <v>871</v>
+        <v>851</v>
       </c>
       <c r="B180" s="48" t="s">
-        <v>891</v>
+        <v>868</v>
       </c>
       <c r="C180" s="48" t="s">
         <v>95</v>
@@ -30045,10 +30274,10 @@
         <v>1380</v>
       </c>
       <c r="F180" s="62">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G180" s="62">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H180" s="61">
         <f t="shared" si="18"/>
@@ -30060,20 +30289,22 @@
       </c>
       <c r="J180" s="61">
         <f t="shared" si="19"/>
-        <v>0</v>
+        <v>919</v>
       </c>
       <c r="K180" s="61">
         <f t="shared" si="20"/>
-        <v>2757</v>
-      </c>
-      <c r="L180" s="48"/>
+        <v>1838</v>
+      </c>
+      <c r="L180" s="48" t="s">
+        <v>901</v>
+      </c>
       <c r="M180" s="48"/>
       <c r="N180" s="48" t="s">
-        <v>538</v>
+        <v>451</v>
       </c>
       <c r="O180" s="48"/>
       <c r="P180" s="48" t="s">
-        <v>890</v>
+        <v>902</v>
       </c>
       <c r="Q180" s="48"/>
       <c r="R180" s="48"/>
@@ -30082,7 +30313,7 @@
     </row>
     <row r="181" spans="1:20" ht="15">
       <c r="A181" s="42" t="s">
-        <v>872</v>
+        <v>852</v>
       </c>
       <c r="B181" s="42"/>
       <c r="C181" s="42"/>
@@ -30106,7 +30337,7 @@
     </row>
     <row r="182" spans="1:20" ht="15">
       <c r="A182" s="48" t="s">
-        <v>873</v>
+        <v>853</v>
       </c>
       <c r="B182" s="48"/>
       <c r="C182" s="48"/>
@@ -30130,7 +30361,7 @@
     </row>
     <row r="183" spans="1:20" ht="15">
       <c r="A183" s="42" t="s">
-        <v>874</v>
+        <v>854</v>
       </c>
       <c r="B183" s="42"/>
       <c r="C183" s="42"/>
@@ -30154,7 +30385,7 @@
     </row>
     <row r="184" spans="1:20" ht="15">
       <c r="A184" s="48" t="s">
-        <v>875</v>
+        <v>855</v>
       </c>
       <c r="B184" s="48"/>
       <c r="C184" s="48"/>
@@ -30178,7 +30409,7 @@
     </row>
     <row r="185" spans="1:20" ht="15">
       <c r="A185" s="42" t="s">
-        <v>876</v>
+        <v>856</v>
       </c>
       <c r="B185" s="42"/>
       <c r="C185" s="42"/>
@@ -30202,7 +30433,7 @@
     </row>
     <row r="186" spans="1:20" ht="15">
       <c r="A186" s="48" t="s">
-        <v>877</v>
+        <v>857</v>
       </c>
       <c r="B186" s="48"/>
       <c r="C186" s="48"/>
@@ -30226,7 +30457,7 @@
     </row>
     <row r="187" spans="1:20" ht="15">
       <c r="A187" s="42" t="s">
-        <v>878</v>
+        <v>858</v>
       </c>
       <c r="B187" s="42"/>
       <c r="C187" s="42"/>
@@ -30250,7 +30481,7 @@
     </row>
     <row r="188" spans="1:20" ht="15">
       <c r="A188" s="48" t="s">
-        <v>879</v>
+        <v>859</v>
       </c>
       <c r="B188" s="48"/>
       <c r="C188" s="48"/>
@@ -34325,7 +34556,7 @@
   <sheetData>
     <row r="1" spans="1:8" ht="15" customHeight="1">
       <c r="A1" s="96" t="s">
-        <v>787</v>
+        <v>777</v>
       </c>
       <c r="B1" s="96"/>
     </row>
@@ -34334,7 +34565,7 @@
         <v>42</v>
       </c>
       <c r="B2" s="8" t="s">
-        <v>788</v>
+        <v>778</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="13.5" customHeight="1">
@@ -34366,25 +34597,25 @@
         <v>42</v>
       </c>
       <c r="B7" s="67" t="s">
-        <v>789</v>
+        <v>779</v>
       </c>
       <c r="C7" s="67" t="s">
-        <v>790</v>
+        <v>780</v>
       </c>
       <c r="D7" s="67" t="s">
-        <v>791</v>
+        <v>781</v>
       </c>
       <c r="E7" s="67" t="s">
-        <v>792</v>
+        <v>782</v>
       </c>
       <c r="F7" s="67" t="s">
-        <v>793</v>
+        <v>783</v>
       </c>
       <c r="G7" s="67" t="s">
-        <v>794</v>
+        <v>784</v>
       </c>
       <c r="H7" s="67" t="s">
-        <v>795</v>
+        <v>785</v>
       </c>
     </row>
     <row r="8" spans="1:8" ht="13.5" customHeight="1">
@@ -34397,11 +34628,11 @@
       </c>
       <c r="C8" s="9">
         <f>SUM($B$8:$B$10)/3</f>
-        <v>116764.33333333333</v>
+        <v>118079</v>
       </c>
       <c r="D8" s="9">
         <f>B8-C8</f>
-        <v>37495.666666666672</v>
+        <v>36181</v>
       </c>
       <c r="E8" s="9">
         <f>IF(Summary!$B$6&gt;0, Summary!$B$6*VLOOKUP($A8,$A$3:$B$5,2,FALSE()),0)</f>
@@ -34409,7 +34640,7 @@
       </c>
       <c r="F8" s="9">
         <f>D8+E8</f>
-        <v>37495.666666666672</v>
+        <v>36181</v>
       </c>
       <c r="G8" s="9">
         <f>IFERROR(SUMIFS($E$13:$E$499,$D$13:$D$499,$A8,$B$13:$B$499,"Contribution"),0)+IFERROR(SUMIFS($E$13:$E$499,$D$13:$D$499,$A8,$B$13:$B$499,"Profit"),0)-IFERROR(SUMIFS($E$13:$E$499,$C$13:$C$499,$A8,$B$13:$B$499,"Contribution"),0)-IFERROR(SUMIFS($E$13:$E$499,$C$13:$C$499,$A8,$B$13:$B$499,"Profit"),0)</f>
@@ -34417,7 +34648,7 @@
       </c>
       <c r="H8" s="69">
         <f>F8-G8</f>
-        <v>19192.326666666671</v>
+        <v>17877.66</v>
       </c>
     </row>
     <row r="9" spans="1:8" ht="13.5" customHeight="1">
@@ -34426,15 +34657,15 @@
       </c>
       <c r="B9" s="11">
         <f>IFERROR(SUMIF(Purchases!$B:$B,$A9,Purchases!$C:$C),0)</f>
-        <v>163433</v>
+        <v>167377</v>
       </c>
       <c r="C9" s="11">
         <f>SUM($B$8:$B$10)/3</f>
-        <v>116764.33333333333</v>
+        <v>118079</v>
       </c>
       <c r="D9" s="11">
         <f>B9-C9</f>
-        <v>46668.666666666672</v>
+        <v>49298</v>
       </c>
       <c r="E9" s="11">
         <f>IF(Summary!$B$6&gt;0, Summary!$B$6*VLOOKUP($A9,$A$3:$B$5,2,FALSE()),0)</f>
@@ -34442,7 +34673,7 @@
       </c>
       <c r="F9" s="11">
         <f>D9+E9</f>
-        <v>46668.666666666672</v>
+        <v>49298</v>
       </c>
       <c r="G9" s="11">
         <f>IFERROR(SUMIFS($E$13:$E$499,$D$13:$D$499,$A9,$B$13:$B$499,"Contribution"),0)+IFERROR(SUMIFS($E$13:$E$499,$D$13:$D$499,$A9,$B$13:$B$499,"Profit"),0)-IFERROR(SUMIFS($E$13:$E$499,$C$13:$C$499,$A9,$B$13:$B$499,"Contribution"),0)-IFERROR(SUMIFS($E$13:$E$499,$C$13:$C$499,$A9,$B$13:$B$499,"Profit"),0)</f>
@@ -34450,7 +34681,7 @@
       </c>
       <c r="H9" s="70">
         <f>F9-G9</f>
-        <v>5029.3366666666698</v>
+        <v>7658.6699999999983</v>
       </c>
     </row>
     <row r="10" spans="1:8" ht="13.5" customHeight="1">
@@ -34463,11 +34694,11 @@
       </c>
       <c r="C10" s="9">
         <f>SUM($B$8:$B$10)/3</f>
-        <v>116764.33333333333</v>
+        <v>118079</v>
       </c>
       <c r="D10" s="9">
         <f>B10-C10</f>
-        <v>-84164.333333333328</v>
+        <v>-85479</v>
       </c>
       <c r="E10" s="9">
         <f>IF(Summary!$B$6&gt;0, Summary!$B$6*VLOOKUP($A10,$A$3:$B$5,2,FALSE()),0)</f>
@@ -34475,7 +34706,7 @@
       </c>
       <c r="F10" s="9">
         <f>D10+E10</f>
-        <v>-84164.333333333328</v>
+        <v>-85479</v>
       </c>
       <c r="G10" s="9">
         <f>IFERROR(SUMIFS($E$13:$E$499,$D$13:$D$499,$A10,$B$13:$B$499,"Contribution"),0)+IFERROR(SUMIFS($E$13:$E$499,$D$13:$D$499,$A10,$B$13:$B$499,"Profit"),0)-IFERROR(SUMIFS($E$13:$E$499,$C$13:$C$499,$A10,$B$13:$B$499,"Contribution"),0)-IFERROR(SUMIFS($E$13:$E$499,$C$13:$C$499,$A10,$B$13:$B$499,"Profit"),0)</f>
@@ -34483,12 +34714,12 @@
       </c>
       <c r="H10" s="69">
         <f>F10-G10</f>
-        <v>-24221.66333333333</v>
+        <v>-25536.33</v>
       </c>
     </row>
     <row r="12" spans="1:8" s="71" customFormat="1" ht="15.75" customHeight="1">
       <c r="A12" s="97" t="s">
-        <v>796</v>
+        <v>786</v>
       </c>
       <c r="B12" s="97"/>
       <c r="C12" s="97"/>
@@ -34501,13 +34732,13 @@
         <v>98</v>
       </c>
       <c r="B13" s="67" t="s">
-        <v>797</v>
+        <v>787</v>
       </c>
       <c r="C13" s="67" t="s">
-        <v>798</v>
+        <v>788</v>
       </c>
       <c r="D13" s="67" t="s">
-        <v>799</v>
+        <v>789</v>
       </c>
       <c r="E13" s="67" t="s">
         <v>99</v>
@@ -34521,7 +34752,7 @@
         <v>45952</v>
       </c>
       <c r="B14" s="9" t="s">
-        <v>800</v>
+        <v>790</v>
       </c>
       <c r="C14" s="9" t="s">
         <v>51</v>
@@ -34539,7 +34770,7 @@
         <v>45952</v>
       </c>
       <c r="B15" s="11" t="s">
-        <v>800</v>
+        <v>790</v>
       </c>
       <c r="C15" s="11" t="s">
         <v>51</v>
@@ -34593,7 +34824,7 @@
         <v>45970</v>
       </c>
       <c r="B18" s="9" t="s">
-        <v>800</v>
+        <v>790</v>
       </c>
       <c r="C18" s="9" t="s">
         <v>50</v>
@@ -34611,7 +34842,7 @@
         <v>45970</v>
       </c>
       <c r="B19" s="11" t="s">
-        <v>800</v>
+        <v>790</v>
       </c>
       <c r="C19" s="11" t="s">
         <v>50</v>
@@ -34629,7 +34860,7 @@
         <v>45973</v>
       </c>
       <c r="B20" s="9" t="s">
-        <v>800</v>
+        <v>790</v>
       </c>
       <c r="C20" s="9" t="s">
         <v>50</v>
@@ -34647,7 +34878,7 @@
         <v>45973</v>
       </c>
       <c r="B21" s="11" t="s">
-        <v>800</v>
+        <v>790</v>
       </c>
       <c r="C21" s="11" t="s">
         <v>49</v>
@@ -34665,7 +34896,7 @@
         <v>46058</v>
       </c>
       <c r="B22" s="9" t="s">
-        <v>800</v>
+        <v>790</v>
       </c>
       <c r="C22" s="9" t="s">
         <v>51</v>
@@ -34701,7 +34932,7 @@
         <v>46059</v>
       </c>
       <c r="B24" s="9" t="s">
-        <v>800</v>
+        <v>790</v>
       </c>
       <c r="C24" s="9" t="s">
         <v>49</v>
@@ -34737,7 +34968,7 @@
         <v>46093</v>
       </c>
       <c r="B26" s="9" t="s">
-        <v>800</v>
+        <v>790</v>
       </c>
       <c r="C26" s="9" t="s">
         <v>50</v>
@@ -34755,7 +34986,7 @@
         <v>46093</v>
       </c>
       <c r="B27" s="11" t="s">
-        <v>800</v>
+        <v>790</v>
       </c>
       <c r="C27" s="11" t="s">
         <v>51</v>
@@ -34838,7 +35069,7 @@
     </row>
     <row r="58" spans="2:2" ht="13.5" customHeight="1">
       <c r="B58" s="6" t="s">
-        <v>801</v>
+        <v>791</v>
       </c>
     </row>
   </sheetData>
@@ -34868,7 +35099,7 @@
   <sheetData>
     <row r="1" spans="1:7" ht="13.5" customHeight="1">
       <c r="A1" s="74" t="s">
-        <v>802</v>
+        <v>792</v>
       </c>
     </row>
     <row r="3" spans="1:7" s="68" customFormat="1" ht="13.5" customHeight="1">
@@ -34876,22 +35107,22 @@
         <v>42</v>
       </c>
       <c r="B3" s="67" t="s">
-        <v>803</v>
+        <v>793</v>
       </c>
       <c r="C3" s="67" t="s">
-        <v>788</v>
+        <v>778</v>
       </c>
       <c r="D3" s="67" t="s">
-        <v>804</v>
+        <v>794</v>
       </c>
       <c r="E3" s="67" t="s">
-        <v>805</v>
+        <v>795</v>
       </c>
       <c r="F3" s="67" t="s">
-        <v>806</v>
+        <v>796</v>
       </c>
       <c r="G3" s="67" t="s">
-        <v>807</v>
+        <v>797</v>
       </c>
     </row>
     <row r="4" spans="1:7" ht="13.5" customHeight="1">
@@ -34900,7 +35131,7 @@
       </c>
       <c r="B4" s="9">
         <f>IFERROR(SUMIFS(Sales!$C:$C,Sales!$E:$E,$A4,Sales!$I:$I,"Completed"),0)</f>
-        <v>271719</v>
+        <v>274469</v>
       </c>
       <c r="C4" s="9">
         <f>VLOOKUP($A4,PartnerShares!$A$3:$B$5,2,FALSE())</f>
@@ -34908,11 +35139,11 @@
       </c>
       <c r="D4" s="9">
         <f>Summary!$B$4*C4</f>
-        <v>97575.511199999994</v>
+        <v>109144.49119999999</v>
       </c>
       <c r="E4" s="9">
         <f>B4-D4</f>
-        <v>174143.48879999999</v>
+        <v>165324.50880000001</v>
       </c>
       <c r="F4" s="9">
         <f>IFERROR(SUMIFS(PartnerShares!$E$13:$E$499,PartnerShares!$D$13:$D$499,$A4,PartnerShares!$B$13:$B$499,"Cash"),0)-IFERROR(SUMIFS(PartnerShares!$E$13:$E$499,PartnerShares!$C$13:$C$499,$A4,PartnerShares!$B$13:$B$499,"Cash"),0)</f>
@@ -34920,7 +35151,7 @@
       </c>
       <c r="G4" s="69">
         <f>E4+F4</f>
-        <v>36833.462799999979</v>
+        <v>28014.482799999998</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="13.5" customHeight="1">
@@ -34929,7 +35160,7 @@
       </c>
       <c r="B5" s="11">
         <f>IFERROR(SUMIFS(Sales!$C:$C,Sales!$E:$E,$A5,Sales!$I:$I,"Completed"),0)</f>
-        <v>8419</v>
+        <v>40369</v>
       </c>
       <c r="C5" s="11">
         <f>VLOOKUP($A5,PartnerShares!$A$3:$B$5,2,FALSE())</f>
@@ -34937,11 +35168,11 @@
       </c>
       <c r="D5" s="11">
         <f>Summary!$B$4*C5</f>
-        <v>97516.977599999998</v>
+        <v>109079.01759999999</v>
       </c>
       <c r="E5" s="11">
         <f>B5-D5</f>
-        <v>-89097.977599999998</v>
+        <v>-68710.017599999992</v>
       </c>
       <c r="F5" s="11">
         <f>IFERROR(SUMIFS(PartnerShares!$E$13:$E$499,PartnerShares!$D$13:$D$499,$A5,PartnerShares!$B$13:$B$499,"Cash"),0)-IFERROR(SUMIFS(PartnerShares!$E$13:$E$499,PartnerShares!$C$13:$C$499,$A5,PartnerShares!$B$13:$B$499,"Cash"),0)</f>
@@ -34949,7 +35180,7 @@
       </c>
       <c r="G5" s="70">
         <f>E5+F5</f>
-        <v>-17510.935599999997</v>
+        <v>2877.0244000000093</v>
       </c>
     </row>
     <row r="6" spans="1:7" ht="13.5" customHeight="1">
@@ -34966,11 +35197,11 @@
       </c>
       <c r="D6" s="9">
         <f>Summary!$B$4*C6</f>
-        <v>97575.511199999994</v>
+        <v>109144.49119999999</v>
       </c>
       <c r="E6" s="9">
         <f>B6-D6</f>
-        <v>-85045.511199999994</v>
+        <v>-96614.491199999989</v>
       </c>
       <c r="F6" s="9">
         <f>IFERROR(SUMIFS(PartnerShares!$E$13:$E$499,PartnerShares!$D$13:$D$499,$A6,PartnerShares!$B$13:$B$499,"Cash"),0)-IFERROR(SUMIFS(PartnerShares!$E$13:$E$499,PartnerShares!$C$13:$C$499,$A6,PartnerShares!$B$13:$B$499,"Cash"),0)</f>
@@ -34978,7 +35209,7 @@
       </c>
       <c r="G6" s="69">
         <f>E6+F6</f>
-        <v>-19322.527199999982</v>
+        <v>-30891.507199999978</v>
       </c>
     </row>
     <row r="9" spans="1:7" ht="13.5" customHeight="1">
@@ -34988,27 +35219,27 @@
     </row>
     <row r="10" spans="1:7" ht="13.5" customHeight="1">
       <c r="A10" s="6" t="s">
-        <v>808</v>
+        <v>798</v>
       </c>
     </row>
     <row r="11" spans="1:7" ht="13.5" customHeight="1">
       <c r="A11" s="6" t="s">
-        <v>809</v>
+        <v>799</v>
       </c>
     </row>
     <row r="12" spans="1:7" ht="13.5" customHeight="1">
       <c r="A12" s="6" t="s">
-        <v>810</v>
+        <v>800</v>
       </c>
     </row>
     <row r="13" spans="1:7" ht="13.5" customHeight="1">
       <c r="A13" s="6" t="s">
-        <v>811</v>
+        <v>801</v>
       </c>
     </row>
     <row r="14" spans="1:7" ht="13.5" customHeight="1">
       <c r="A14" s="6" t="s">
-        <v>812</v>
+        <v>802</v>
       </c>
     </row>
   </sheetData>

--- a/docs/Chiraath-Summary-May26.xlsx
+++ b/docs/Chiraath-Summary-May26.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/anooppremachandran/Desktop/CHIRAATH/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{36418D76-F2BE-F34B-9E50-45C2A6F9F74D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A3EED658-39E2-244C-ABE4-BA99D9EB7BFA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="18000" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="18000" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Notes" sheetId="1" r:id="rId1"/>
@@ -46,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2323" uniqueCount="933">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2340" uniqueCount="940">
   <si>
     <t>Notes:</t>
   </si>
@@ -1714,9 +1714,6 @@
   </si>
   <si>
     <t>CHR-61</t>
-  </si>
-  <si>
-    <t>Resmi(Tvm) - 500</t>
   </si>
   <si>
     <t>CHR-62</t>
@@ -2184,15 +2181,6 @@
     <t>Chanderi Printed Silk Saree</t>
   </si>
   <si>
-    <t>First Set: Aruna - violet, Resmi - navy blue, Malini - Rani Pink
-Second Set: Sreelekha - Black, Dona - navy Blue, Jayalakshmi - Pink, Jyothimol - Navy Blue, Amrutha - Maroon, Athira - Black, Jini - Maroon, Gopika - Black, Aji Roy - Black, Aji Roy - Mustard, Lili Kutty - Maroon, Sindhu - Black, Asha - Green, Soorya - Rani Pink, Asha Latha - Offwhite, Susmi - Off white</t>
-  </si>
-  <si>
-    <t xml:space="preserve">
-New batch: Blue (2), mustard yellow (1), navy blue (3), Green (2), Rani pink (2), Maroon (3), off white (2), Orange (2)
-New batch2: Black(7), White(5), Rani Pink(1)</t>
-  </si>
-  <si>
     <t>CHR-120</t>
   </si>
   <si>
@@ -2727,9 +2715,6 @@
     <t>Tissue Silk Saree Collection</t>
   </si>
   <si>
-    <t>Lipcy - Green</t>
-  </si>
-  <si>
     <t>Light brown</t>
   </si>
   <si>
@@ -2751,12 +2736,6 @@
     <t>Matka Silk Saree Collection</t>
   </si>
   <si>
-    <t>Lipcy - Red/Green</t>
-  </si>
-  <si>
-    <t>royal blue/rani pink, parrot green/red</t>
-  </si>
-  <si>
     <t>CHR-180</t>
   </si>
   <si>
@@ -2866,6 +2845,48 @@
   </si>
   <si>
     <t>Salwar maroon single piece M (CHR-78) - 500 advance, 300 pending</t>
+  </si>
+  <si>
+    <t xml:space="preserve">
+New batch: Blue (2), mustard yellow (1), navy blue (3), Green (2), Rani pink (2), Maroon (2), off white (2), Orange (1)
+New batch2: Black(7), White(5), Rani Pink(1)</t>
+  </si>
+  <si>
+    <t>First Set: Aruna - violet, Resmi - navy blue, Malini - Rani Pink
+Second Set: Sreelekha - Black, Dona - navy Blue, Jayalakshmi - Pink, Jyothimol - Navy Blue, Amrutha - Maroon, Athira - Black, Jini - Maroon, Gopika - Black, Aji Roy - Black, Aji Roy - Mustard, Lili Kutty - Maroon, Sindhu - Black, Asha - Green, Soorya - Rani Pink, Asha Latha - Offwhite, Susmi - Off white, Revathi - Maroon &amp; Orange</t>
+  </si>
+  <si>
+    <t>Lipcy - Red/Green, Revathi - Parrot Green/Red</t>
+  </si>
+  <si>
+    <t>royal blue/rani pink</t>
+  </si>
+  <si>
+    <t>Revathi</t>
+  </si>
+  <si>
+    <t>Resmi(Tvm) - 500, Revathi</t>
+  </si>
+  <si>
+    <t>Kerala Saree Temple Design, Pink Cottton Saree (CHR-61), Chanderi Silk Saree (Orange &amp; Maroon-CHR-119), Matka Saree (Green/Pink -CHR-179)</t>
+  </si>
+  <si>
+    <t>Siji</t>
+  </si>
+  <si>
+    <t>Anju Sanjeev</t>
+  </si>
+  <si>
+    <t>Jomi</t>
+  </si>
+  <si>
+    <t>Saritha</t>
+  </si>
+  <si>
+    <t>Tussar Silk Saree (CHR-177)</t>
+  </si>
+  <si>
+    <t>Lipcy - Green, Siji -Dusty Rose</t>
   </si>
 </sst>
 </file>
@@ -3778,7 +3799,7 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="3"/>
                 <c:pt idx="0">
-                  <c:v>182</c:v>
+                  <c:v>184</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>86</c:v>
@@ -3881,7 +3902,7 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="3"/>
                 <c:pt idx="0">
-                  <c:v>93</c:v>
+                  <c:v>91</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>59</c:v>
@@ -4214,7 +4235,7 @@
                   <c:v>61609</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>61548.609999999993</c:v>
+                  <c:v>59958.609999999993</c:v>
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>1357</c:v>
@@ -4701,7 +4722,7 @@
                   <c:v>55936</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>39339</c:v>
+                  <c:v>45939</c:v>
                 </c:pt>
                 <c:pt idx="5">
                   <c:v>0</c:v>
@@ -5141,7 +5162,7 @@
                   <c:v>-15066</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>34890</c:v>
+                  <c:v>41490</c:v>
                 </c:pt>
                 <c:pt idx="5">
                   <c:v>0</c:v>
@@ -5611,10 +5632,10 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="2"/>
                 <c:pt idx="0">
-                  <c:v>271</c:v>
+                  <c:v>273</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>156</c:v>
+                  <c:v>154</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6801,7 +6822,7 @@
       </c>
       <c r="B4" s="10">
         <f>SUMIFS(Sales!C:C, Sales!I:I, "Completed")</f>
-        <v>329218</v>
+        <v>334418</v>
       </c>
       <c r="E4" s="9" t="str">
         <f>PartnerShares!A3</f>
@@ -6818,7 +6839,7 @@
       </c>
       <c r="B5" s="12">
         <f>SUM(Sales!C:C)</f>
-        <v>342087</v>
+        <v>348687</v>
       </c>
       <c r="E5" s="11" t="str">
         <f>PartnerShares!A4</f>
@@ -6835,7 +6856,7 @@
       </c>
       <c r="B6" s="10">
         <f>B4-B3</f>
-        <v>-25524</v>
+        <v>-20324</v>
       </c>
       <c r="E6" s="9" t="str">
         <f>PartnerShares!A5</f>
@@ -7051,11 +7072,11 @@
       </c>
       <c r="C26" s="10">
         <f>'Cash Pool'!D4</f>
-        <v>109761.2812</v>
+        <v>111494.96119999999</v>
       </c>
       <c r="D26" s="10">
         <f>'Cash Pool'!E4</f>
-        <v>166557.7188</v>
+        <v>164824.03880000001</v>
       </c>
       <c r="E26" s="10">
         <f>'Cash Pool'!F4</f>
@@ -7063,11 +7084,11 @@
       </c>
       <c r="F26" s="13">
         <f>'Cash Pool'!G4</f>
-        <v>29247.69279999999</v>
+        <v>27514.012799999997</v>
       </c>
       <c r="G26" s="17" t="str">
         <f>IF(ROUND(F26,0)&gt;0,"Pay ₹"&amp;TEXT(ABS(F26),"#,##0"),IF(ROUND(F26,0)&lt;0,"Receive ₹"&amp;TEXT(ABS(F26),"#,##0"),"✓ Settled"))</f>
-        <v>Pay ₹29,248</v>
+        <v>Pay ₹27,514</v>
       </c>
     </row>
     <row r="27" spans="1:7" ht="13.5" customHeight="1">
@@ -7077,15 +7098,15 @@
       </c>
       <c r="B27" s="12">
         <f>'Cash Pool'!B5</f>
-        <v>40369</v>
+        <v>45569</v>
       </c>
       <c r="C27" s="12">
         <f>'Cash Pool'!D5</f>
-        <v>109695.4376</v>
+        <v>111428.0776</v>
       </c>
       <c r="D27" s="12">
         <f>'Cash Pool'!E5</f>
-        <v>-69326.437600000005</v>
+        <v>-65859.077600000004</v>
       </c>
       <c r="E27" s="12">
         <f>'Cash Pool'!F5</f>
@@ -7093,11 +7114,11 @@
       </c>
       <c r="F27" s="14">
         <f>'Cash Pool'!G5</f>
-        <v>2260.6043999999965</v>
+        <v>5727.9643999999971</v>
       </c>
       <c r="G27" s="18" t="str">
         <f>IF(ROUND(F27,0)&gt;0,"Pay ₹"&amp;TEXT(ABS(F27),"#,##0"),IF(ROUND(F27,0)&lt;0,"Receive ₹"&amp;TEXT(ABS(F27),"#,##0"),"✓ Settled"))</f>
-        <v>Pay ₹2,261</v>
+        <v>Pay ₹5,728</v>
       </c>
     </row>
     <row r="28" spans="1:7" ht="13.5" customHeight="1">
@@ -7111,11 +7132,11 @@
       </c>
       <c r="C28" s="10">
         <f>'Cash Pool'!D6</f>
-        <v>109761.2812</v>
+        <v>111494.96119999999</v>
       </c>
       <c r="D28" s="10">
         <f>'Cash Pool'!E6</f>
-        <v>-97231.281199999998</v>
+        <v>-98964.961199999991</v>
       </c>
       <c r="E28" s="10">
         <f>'Cash Pool'!F6</f>
@@ -7123,11 +7144,11 @@
       </c>
       <c r="F28" s="13">
         <f>'Cash Pool'!G6</f>
-        <v>-31508.297199999986</v>
+        <v>-33241.977199999979</v>
       </c>
       <c r="G28" s="16" t="str">
         <f>IF(ROUND(F28,0)&gt;0,"Pay ₹"&amp;TEXT(ABS(F28),"#,##0"),IF(ROUND(F28,0)&lt;0,"Receive ₹"&amp;TEXT(ABS(F28),"#,##0"),"✓ Settled"))</f>
-        <v>Receive ₹31,508</v>
+        <v>Receive ₹33,242</v>
       </c>
     </row>
     <row r="32" spans="1:7" ht="15.75" customHeight="1">
@@ -7239,7 +7260,7 @@
       </c>
       <c r="B3" s="20">
         <f ca="1">TODAY()</f>
-        <v>46167</v>
+        <v>46173</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="15" customHeight="1">
@@ -7255,7 +7276,7 @@
       </c>
       <c r="E5" s="21">
         <f>Summary!B4</f>
-        <v>329218</v>
+        <v>334418</v>
       </c>
     </row>
     <row r="6" spans="1:8" ht="15" customHeight="1">
@@ -7264,14 +7285,14 @@
       </c>
       <c r="B6" s="21">
         <f>Summary!B6</f>
-        <v>-25524</v>
+        <v>-20324</v>
       </c>
       <c r="D6" s="19" t="s">
         <v>71</v>
       </c>
       <c r="E6" s="21">
         <f>SUMIFS(INVENTORY!K:K, INVENTORY!N:N, "&lt;&gt;Sold Out")</f>
-        <v>115210.80999999998</v>
+        <v>111744.80999999998</v>
       </c>
     </row>
     <row r="7" spans="1:8" ht="15.75" customHeight="1">
@@ -7323,7 +7344,7 @@
       </c>
       <c r="G10" s="21">
         <f>SUM(INVENTORY!F:F)</f>
-        <v>271</v>
+        <v>273</v>
       </c>
     </row>
     <row r="11" spans="1:8" ht="15" customHeight="1">
@@ -7347,7 +7368,7 @@
       </c>
       <c r="G11" s="27">
         <f>SUM(INVENTORY!G:G)</f>
-        <v>156</v>
+        <v>154</v>
       </c>
     </row>
     <row r="12" spans="1:8" ht="15" customHeight="1">
@@ -7394,11 +7415,11 @@
       </c>
       <c r="C14" s="21">
         <f>IFERROR(SUMPRODUCT((TEXT(Sales!$A$2:$A$996,"MMM")=$A14)*(YEAR(Sales!$A$2:$A$996)=$B$7)*Sales!$C$2:$C$996),0)</f>
-        <v>39339</v>
+        <v>45939</v>
       </c>
       <c r="D14" s="21">
         <f t="shared" si="0"/>
-        <v>34890</v>
+        <v>41490</v>
       </c>
     </row>
     <row r="15" spans="1:8" ht="15" customHeight="1">
@@ -7543,11 +7564,11 @@
       </c>
       <c r="G47" s="30">
         <f>SUMIF(INVENTORY!C:C, F47, INVENTORY!F:F)</f>
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="H47" s="30">
         <f>SUMIF(INVENTORY!C:C, F47, INVENTORY!G:G)</f>
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="J47" s="30" t="s">
         <v>96</v>
@@ -7574,7 +7595,7 @@
       </c>
       <c r="K48" s="31">
         <f t="array" ref="K48">SUMPRODUCT((INVENTORY!$C$2:$C$477=J48)*(INVENTORY!$D$2:$D$477)*(INVENTORY!$G$2:$G$477))</f>
-        <v>61548.609999999993</v>
+        <v>59958.609999999993</v>
       </c>
     </row>
     <row r="49" spans="5:12" ht="15" customHeight="1">
@@ -14609,7 +14630,7 @@
       <c r="F149" s="49"/>
       <c r="G149" s="49"/>
       <c r="H149" s="51" t="s">
-        <v>931</v>
+        <v>925</v>
       </c>
       <c r="I149" s="49" t="s">
         <v>142</v>
@@ -14882,7 +14903,7 @@
       <c r="F160" s="56"/>
       <c r="G160" s="56"/>
       <c r="H160" s="57" t="s">
-        <v>930</v>
+        <v>924</v>
       </c>
       <c r="I160" s="53" t="s">
         <v>341</v>
@@ -15074,7 +15095,7 @@
       <c r="F168" s="49"/>
       <c r="G168" s="49"/>
       <c r="H168" s="51" t="s">
-        <v>932</v>
+        <v>926</v>
       </c>
       <c r="I168" s="49" t="s">
         <v>341</v>
@@ -15797,60 +15818,100 @@
         <v>142</v>
       </c>
     </row>
-    <row r="198" spans="1:9">
-      <c r="A198" s="52"/>
-      <c r="B198" s="53"/>
-      <c r="C198" s="54"/>
-      <c r="D198" s="53"/>
-      <c r="E198" s="53"/>
+    <row r="198" spans="1:9" ht="42">
+      <c r="A198" s="52">
+        <v>46168</v>
+      </c>
+      <c r="B198" s="53" t="s">
+        <v>931</v>
+      </c>
+      <c r="C198" s="54">
+        <v>5200</v>
+      </c>
+      <c r="D198" s="53" t="s">
+        <v>144</v>
+      </c>
+      <c r="E198" s="53" t="s">
+        <v>50</v>
+      </c>
       <c r="F198" s="56"/>
       <c r="G198" s="56"/>
-      <c r="H198" s="57"/>
-      <c r="I198" s="53"/>
-    </row>
-    <row r="199" spans="1:9">
-      <c r="A199" s="48"/>
-      <c r="B199" s="49"/>
-      <c r="C199" s="50"/>
-      <c r="D199" s="49"/>
-      <c r="E199" s="49"/>
+      <c r="H198" s="57" t="s">
+        <v>933</v>
+      </c>
+      <c r="I198" s="53" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="199" spans="1:9" ht="14">
+      <c r="A199" s="48">
+        <v>46172</v>
+      </c>
+      <c r="B199" s="49" t="s">
+        <v>934</v>
+      </c>
+      <c r="C199" s="50">
+        <v>1400</v>
+      </c>
+      <c r="D199" s="49" t="s">
+        <v>144</v>
+      </c>
+      <c r="E199" s="49" t="s">
+        <v>50</v>
+      </c>
       <c r="F199" s="49"/>
       <c r="G199" s="49"/>
-      <c r="H199" s="51"/>
-      <c r="I199" s="49"/>
+      <c r="H199" s="51" t="s">
+        <v>938</v>
+      </c>
+      <c r="I199" s="49" t="s">
+        <v>341</v>
+      </c>
     </row>
     <row r="200" spans="1:9">
       <c r="A200" s="52"/>
-      <c r="B200" s="53"/>
+      <c r="B200" s="53" t="s">
+        <v>935</v>
+      </c>
       <c r="C200" s="54"/>
       <c r="D200" s="53"/>
       <c r="E200" s="53"/>
       <c r="F200" s="56"/>
       <c r="G200" s="56"/>
       <c r="H200" s="57"/>
-      <c r="I200" s="53"/>
+      <c r="I200" s="53" t="s">
+        <v>341</v>
+      </c>
     </row>
     <row r="201" spans="1:9">
       <c r="A201" s="48"/>
-      <c r="B201" s="49"/>
+      <c r="B201" s="49" t="s">
+        <v>936</v>
+      </c>
       <c r="C201" s="50"/>
       <c r="D201" s="49"/>
       <c r="E201" s="49"/>
       <c r="F201" s="49"/>
       <c r="G201" s="49"/>
       <c r="H201" s="51"/>
-      <c r="I201" s="49"/>
+      <c r="I201" s="49" t="s">
+        <v>341</v>
+      </c>
     </row>
     <row r="202" spans="1:9">
       <c r="A202" s="52"/>
-      <c r="B202" s="53"/>
+      <c r="B202" s="53" t="s">
+        <v>937</v>
+      </c>
       <c r="C202" s="54"/>
       <c r="D202" s="53"/>
       <c r="E202" s="53"/>
       <c r="F202" s="56"/>
       <c r="G202" s="56"/>
       <c r="H202" s="57"/>
-      <c r="I202" s="53"/>
+      <c r="I202" s="53" t="s">
+        <v>341</v>
+      </c>
     </row>
     <row r="203" spans="1:9">
       <c r="A203" s="48"/>
@@ -23257,10 +23318,10 @@
         <v>750</v>
       </c>
       <c r="F62" s="67">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G62" s="67">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H62" s="66">
         <f t="shared" si="3"/>
@@ -23272,18 +23333,18 @@
       </c>
       <c r="J62" s="66">
         <f t="shared" si="4"/>
-        <v>562</v>
+        <v>1124</v>
       </c>
       <c r="K62" s="66">
         <f t="shared" si="5"/>
-        <v>562</v>
+        <v>0</v>
       </c>
       <c r="L62" s="66" t="s">
-        <v>556</v>
+        <v>932</v>
       </c>
       <c r="M62" s="66"/>
       <c r="N62" s="66" t="s">
-        <v>511</v>
+        <v>426</v>
       </c>
       <c r="O62" s="66"/>
       <c r="P62" s="66"/>
@@ -23294,7 +23355,7 @@
     </row>
     <row r="63" spans="1:246" ht="15" customHeight="1">
       <c r="A63" s="69" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="B63" s="69" t="s">
         <v>432</v>
@@ -23346,7 +23407,7 @@
     </row>
     <row r="64" spans="1:246" ht="15" customHeight="1">
       <c r="A64" s="66" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="B64" s="66" t="s">
         <v>432</v>
@@ -23398,10 +23459,10 @@
     </row>
     <row r="65" spans="1:20" ht="15" customHeight="1">
       <c r="A65" s="69" t="s">
+        <v>558</v>
+      </c>
+      <c r="B65" s="69" t="s">
         <v>559</v>
-      </c>
-      <c r="B65" s="69" t="s">
-        <v>560</v>
       </c>
       <c r="C65" s="69" t="s">
         <v>95</v>
@@ -23435,7 +23496,7 @@
         <v>0</v>
       </c>
       <c r="L65" s="69" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="M65" s="69"/>
       <c r="N65" s="69" t="s">
@@ -23450,10 +23511,10 @@
     </row>
     <row r="66" spans="1:20" ht="15" customHeight="1">
       <c r="A66" s="66" t="s">
+        <v>561</v>
+      </c>
+      <c r="B66" s="66" t="s">
         <v>562</v>
-      </c>
-      <c r="B66" s="66" t="s">
-        <v>563</v>
       </c>
       <c r="C66" s="66" t="s">
         <v>95</v>
@@ -23487,7 +23548,7 @@
         <v>1558</v>
       </c>
       <c r="L66" s="66" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="M66" s="66"/>
       <c r="N66" s="66" t="s">
@@ -23502,10 +23563,10 @@
     </row>
     <row r="67" spans="1:20" ht="15" customHeight="1">
       <c r="A67" s="69" t="s">
+        <v>564</v>
+      </c>
+      <c r="B67" s="69" t="s">
         <v>565</v>
-      </c>
-      <c r="B67" s="69" t="s">
-        <v>566</v>
       </c>
       <c r="C67" s="69" t="s">
         <v>95</v>
@@ -23552,10 +23613,10 @@
     </row>
     <row r="68" spans="1:20" ht="15" customHeight="1">
       <c r="A68" s="66" t="s">
+        <v>566</v>
+      </c>
+      <c r="B68" s="66" t="s">
         <v>567</v>
-      </c>
-      <c r="B68" s="66" t="s">
-        <v>568</v>
       </c>
       <c r="C68" s="66" t="s">
         <v>95</v>
@@ -23589,7 +23650,7 @@
         <v>685</v>
       </c>
       <c r="L68" s="66" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="M68" s="66"/>
       <c r="N68" s="66" t="s">
@@ -23597,7 +23658,7 @@
       </c>
       <c r="O68" s="66"/>
       <c r="P68" s="66" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="Q68" s="66"/>
       <c r="R68" s="66"/>
@@ -23606,10 +23667,10 @@
     </row>
     <row r="69" spans="1:20" ht="15" customHeight="1">
       <c r="A69" s="69" t="s">
+        <v>570</v>
+      </c>
+      <c r="B69" s="69" t="s">
         <v>571</v>
-      </c>
-      <c r="B69" s="69" t="s">
-        <v>572</v>
       </c>
       <c r="C69" s="69" t="s">
         <v>96</v>
@@ -23648,7 +23709,7 @@
         <v>341</v>
       </c>
       <c r="O69" s="69" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="P69" s="69"/>
       <c r="Q69" s="69"/>
@@ -23658,10 +23719,10 @@
     </row>
     <row r="70" spans="1:20" ht="15" customHeight="1">
       <c r="A70" s="66" t="s">
+        <v>573</v>
+      </c>
+      <c r="B70" s="66" t="s">
         <v>574</v>
-      </c>
-      <c r="B70" s="66" t="s">
-        <v>575</v>
       </c>
       <c r="C70" s="66" t="s">
         <v>95</v>
@@ -23695,7 +23756,7 @@
         <v>0</v>
       </c>
       <c r="L70" s="66" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="M70" s="66"/>
       <c r="N70" s="66" t="s">
@@ -23710,10 +23771,10 @@
     </row>
     <row r="71" spans="1:20" ht="15" customHeight="1">
       <c r="A71" s="69" t="s">
+        <v>576</v>
+      </c>
+      <c r="B71" s="69" t="s">
         <v>577</v>
-      </c>
-      <c r="B71" s="69" t="s">
-        <v>578</v>
       </c>
       <c r="C71" s="69" t="s">
         <v>95</v>
@@ -23747,7 +23808,7 @@
         <v>0</v>
       </c>
       <c r="L71" s="69" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="M71" s="69" t="s">
         <v>49</v>
@@ -23757,7 +23818,7 @@
       </c>
       <c r="O71" s="69"/>
       <c r="P71" s="69" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="Q71" s="69"/>
       <c r="R71" s="69"/>
@@ -23766,10 +23827,10 @@
     </row>
     <row r="72" spans="1:20" ht="15" customHeight="1">
       <c r="A72" s="66" t="s">
+        <v>580</v>
+      </c>
+      <c r="B72" s="66" t="s">
         <v>581</v>
-      </c>
-      <c r="B72" s="66" t="s">
-        <v>582</v>
       </c>
       <c r="C72" s="66" t="s">
         <v>95</v>
@@ -23818,10 +23879,10 @@
     </row>
     <row r="73" spans="1:20" ht="15" customHeight="1">
       <c r="A73" s="69" t="s">
+        <v>582</v>
+      </c>
+      <c r="B73" s="69" t="s">
         <v>583</v>
-      </c>
-      <c r="B73" s="69" t="s">
-        <v>584</v>
       </c>
       <c r="C73" s="69" t="s">
         <v>96</v>
@@ -23870,10 +23931,10 @@
     </row>
     <row r="74" spans="1:20" ht="15" customHeight="1">
       <c r="A74" s="66" t="s">
+        <v>584</v>
+      </c>
+      <c r="B74" s="66" t="s">
         <v>585</v>
-      </c>
-      <c r="B74" s="66" t="s">
-        <v>586</v>
       </c>
       <c r="C74" s="66" t="s">
         <v>95</v>
@@ -23924,7 +23985,7 @@
     </row>
     <row r="75" spans="1:20" ht="15" customHeight="1">
       <c r="A75" s="69" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="B75" s="69" t="s">
         <v>475</v>
@@ -23978,10 +24039,10 @@
     </row>
     <row r="76" spans="1:20" ht="15" customHeight="1">
       <c r="A76" s="66" t="s">
+        <v>587</v>
+      </c>
+      <c r="B76" s="66" t="s">
         <v>588</v>
-      </c>
-      <c r="B76" s="66" t="s">
-        <v>589</v>
       </c>
       <c r="C76" s="66" t="s">
         <v>95</v>
@@ -24032,10 +24093,10 @@
     </row>
     <row r="77" spans="1:20" ht="15" customHeight="1">
       <c r="A77" s="69" t="s">
+        <v>589</v>
+      </c>
+      <c r="B77" s="69" t="s">
         <v>590</v>
-      </c>
-      <c r="B77" s="69" t="s">
-        <v>591</v>
       </c>
       <c r="C77" s="69" t="s">
         <v>96</v>
@@ -24069,14 +24130,14 @@
         <v>1990</v>
       </c>
       <c r="L77" s="69" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="M77" s="69"/>
       <c r="N77" s="69" t="s">
         <v>511</v>
       </c>
       <c r="O77" s="69" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="P77" s="69"/>
       <c r="Q77" s="69"/>
@@ -24086,10 +24147,10 @@
     </row>
     <row r="78" spans="1:20" ht="15" customHeight="1">
       <c r="A78" s="66" t="s">
+        <v>593</v>
+      </c>
+      <c r="B78" s="66" t="s">
         <v>594</v>
-      </c>
-      <c r="B78" s="66" t="s">
-        <v>595</v>
       </c>
       <c r="C78" s="66" t="s">
         <v>96</v>
@@ -24123,14 +24184,14 @@
         <v>2150</v>
       </c>
       <c r="L78" s="66" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="M78" s="66"/>
       <c r="N78" s="66" t="s">
         <v>511</v>
       </c>
       <c r="O78" s="66" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="P78" s="66"/>
       <c r="Q78" s="66"/>
@@ -24140,10 +24201,10 @@
     </row>
     <row r="79" spans="1:20" ht="15" customHeight="1">
       <c r="A79" s="69" t="s">
+        <v>597</v>
+      </c>
+      <c r="B79" s="69" t="s">
         <v>598</v>
-      </c>
-      <c r="B79" s="69" t="s">
-        <v>599</v>
       </c>
       <c r="C79" s="69" t="s">
         <v>96</v>
@@ -24177,14 +24238,14 @@
         <v>0</v>
       </c>
       <c r="L79" s="69" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="M79" s="69"/>
       <c r="N79" s="69" t="s">
+        <v>600</v>
+      </c>
+      <c r="O79" s="69" t="s">
         <v>601</v>
-      </c>
-      <c r="O79" s="69" t="s">
-        <v>602</v>
       </c>
       <c r="P79" s="69"/>
       <c r="Q79" s="69"/>
@@ -24194,10 +24255,10 @@
     </row>
     <row r="80" spans="1:20" ht="15" customHeight="1">
       <c r="A80" s="66" t="s">
+        <v>602</v>
+      </c>
+      <c r="B80" s="66" t="s">
         <v>603</v>
-      </c>
-      <c r="B80" s="66" t="s">
-        <v>604</v>
       </c>
       <c r="C80" s="66" t="s">
         <v>96</v>
@@ -24231,14 +24292,14 @@
         <v>1230</v>
       </c>
       <c r="L80" s="66" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="M80" s="66"/>
       <c r="N80" s="66" t="s">
         <v>511</v>
       </c>
       <c r="O80" s="66" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="P80" s="66"/>
       <c r="Q80" s="66"/>
@@ -24248,10 +24309,10 @@
     </row>
     <row r="81" spans="1:20" ht="30" customHeight="1">
       <c r="A81" s="69" t="s">
+        <v>606</v>
+      </c>
+      <c r="B81" s="69" t="s">
         <v>607</v>
-      </c>
-      <c r="B81" s="69" t="s">
-        <v>608</v>
       </c>
       <c r="C81" s="69" t="s">
         <v>96</v>
@@ -24285,7 +24346,7 @@
         <v>0</v>
       </c>
       <c r="L81" s="69" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="M81" s="69"/>
       <c r="N81" s="69" t="s">
@@ -24300,10 +24361,10 @@
     </row>
     <row r="82" spans="1:20" ht="15" customHeight="1">
       <c r="A82" s="66" t="s">
+        <v>609</v>
+      </c>
+      <c r="B82" s="66" t="s">
         <v>610</v>
-      </c>
-      <c r="B82" s="66" t="s">
-        <v>611</v>
       </c>
       <c r="C82" s="66" t="s">
         <v>96</v>
@@ -24337,7 +24398,7 @@
         <v>0</v>
       </c>
       <c r="L82" s="66" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="M82" s="66"/>
       <c r="N82" s="66" t="s">
@@ -24352,10 +24413,10 @@
     </row>
     <row r="83" spans="1:20" ht="30" customHeight="1">
       <c r="A83" s="69" t="s">
+        <v>612</v>
+      </c>
+      <c r="B83" s="69" t="s">
         <v>613</v>
-      </c>
-      <c r="B83" s="69" t="s">
-        <v>614</v>
       </c>
       <c r="C83" s="69" t="s">
         <v>96</v>
@@ -24389,14 +24450,14 @@
         <v>0</v>
       </c>
       <c r="L83" s="69" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="M83" s="69"/>
       <c r="N83" s="69" t="s">
         <v>426</v>
       </c>
       <c r="O83" s="69" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="P83" s="69"/>
       <c r="Q83" s="69"/>
@@ -24406,10 +24467,10 @@
     </row>
     <row r="84" spans="1:20" ht="15" customHeight="1">
       <c r="A84" s="66" t="s">
+        <v>616</v>
+      </c>
+      <c r="B84" s="66" t="s">
         <v>617</v>
-      </c>
-      <c r="B84" s="66" t="s">
-        <v>618</v>
       </c>
       <c r="C84" s="66" t="s">
         <v>96</v>
@@ -24443,14 +24504,14 @@
         <v>900</v>
       </c>
       <c r="L84" s="66" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
       <c r="M84" s="66"/>
       <c r="N84" s="66" t="s">
         <v>511</v>
       </c>
       <c r="O84" s="66" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="P84" s="66"/>
       <c r="Q84" s="66"/>
@@ -24460,10 +24521,10 @@
     </row>
     <row r="85" spans="1:20" ht="15" customHeight="1">
       <c r="A85" s="69" t="s">
+        <v>620</v>
+      </c>
+      <c r="B85" s="69" t="s">
         <v>621</v>
-      </c>
-      <c r="B85" s="69" t="s">
-        <v>622</v>
       </c>
       <c r="C85" s="69" t="s">
         <v>96</v>
@@ -24497,7 +24558,7 @@
         <v>895</v>
       </c>
       <c r="L85" s="69" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="M85" s="69"/>
       <c r="N85" s="69" t="s">
@@ -24512,10 +24573,10 @@
     </row>
     <row r="86" spans="1:20" ht="15" customHeight="1">
       <c r="A86" s="66" t="s">
+        <v>623</v>
+      </c>
+      <c r="B86" s="66" t="s">
         <v>624</v>
-      </c>
-      <c r="B86" s="66" t="s">
-        <v>625</v>
       </c>
       <c r="C86" s="66" t="s">
         <v>96</v>
@@ -24549,14 +24610,14 @@
         <v>2090</v>
       </c>
       <c r="L86" s="66" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="M86" s="66"/>
       <c r="N86" s="66" t="s">
         <v>511</v>
       </c>
       <c r="O86" s="66" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="P86" s="66"/>
       <c r="Q86" s="66"/>
@@ -24566,10 +24627,10 @@
     </row>
     <row r="87" spans="1:20" ht="15" customHeight="1">
       <c r="A87" s="69" t="s">
+        <v>626</v>
+      </c>
+      <c r="B87" s="69" t="s">
         <v>627</v>
-      </c>
-      <c r="B87" s="69" t="s">
-        <v>628</v>
       </c>
       <c r="C87" s="69" t="s">
         <v>96</v>
@@ -24605,10 +24666,10 @@
       <c r="L87" s="69"/>
       <c r="M87" s="69"/>
       <c r="N87" s="69" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="O87" s="69" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="P87" s="69"/>
       <c r="Q87" s="69"/>
@@ -24618,10 +24679,10 @@
     </row>
     <row r="88" spans="1:20" ht="30" customHeight="1">
       <c r="A88" s="66" t="s">
+        <v>629</v>
+      </c>
+      <c r="B88" s="66" t="s">
         <v>630</v>
-      </c>
-      <c r="B88" s="66" t="s">
-        <v>631</v>
       </c>
       <c r="C88" s="66" t="s">
         <v>96</v>
@@ -24655,14 +24716,14 @@
         <v>795</v>
       </c>
       <c r="L88" s="66" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="M88" s="66"/>
       <c r="N88" s="66" t="s">
         <v>511</v>
       </c>
       <c r="O88" s="66" t="s">
-        <v>633</v>
+        <v>632</v>
       </c>
       <c r="P88" s="66"/>
       <c r="Q88" s="66"/>
@@ -24672,10 +24733,10 @@
     </row>
     <row r="89" spans="1:20" ht="15" customHeight="1">
       <c r="A89" s="69" t="s">
+        <v>633</v>
+      </c>
+      <c r="B89" s="69" t="s">
         <v>634</v>
-      </c>
-      <c r="B89" s="69" t="s">
-        <v>635</v>
       </c>
       <c r="C89" s="69" t="s">
         <v>95</v>
@@ -24709,7 +24770,7 @@
         <v>0</v>
       </c>
       <c r="L89" s="69" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="M89" s="69"/>
       <c r="N89" s="69" t="s">
@@ -24724,10 +24785,10 @@
     </row>
     <row r="90" spans="1:20" ht="15" customHeight="1">
       <c r="A90" s="66" t="s">
+        <v>636</v>
+      </c>
+      <c r="B90" s="66" t="s">
         <v>637</v>
-      </c>
-      <c r="B90" s="66" t="s">
-        <v>638</v>
       </c>
       <c r="C90" s="66" t="s">
         <v>95</v>
@@ -24776,13 +24837,13 @@
     </row>
     <row r="91" spans="1:20" ht="15" customHeight="1">
       <c r="A91" s="69" t="s">
+        <v>638</v>
+      </c>
+      <c r="B91" s="69" t="s">
         <v>639</v>
       </c>
-      <c r="B91" s="69" t="s">
+      <c r="C91" s="69" t="s">
         <v>640</v>
-      </c>
-      <c r="C91" s="69" t="s">
-        <v>641</v>
       </c>
       <c r="D91" s="70">
         <v>389</v>
@@ -24813,7 +24874,7 @@
         <v>0</v>
       </c>
       <c r="L91" s="69" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="M91" s="69"/>
       <c r="N91" s="69" t="s">
@@ -24828,13 +24889,13 @@
     </row>
     <row r="92" spans="1:20" ht="15" customHeight="1">
       <c r="A92" s="66" t="s">
+        <v>642</v>
+      </c>
+      <c r="B92" s="66" t="s">
         <v>643</v>
       </c>
-      <c r="B92" s="66" t="s">
-        <v>644</v>
-      </c>
       <c r="C92" s="66" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="D92" s="67">
         <v>489</v>
@@ -24865,7 +24926,7 @@
         <v>0</v>
       </c>
       <c r="L92" s="66" t="s">
-        <v>645</v>
+        <v>644</v>
       </c>
       <c r="M92" s="66"/>
       <c r="N92" s="66" t="s">
@@ -24880,10 +24941,10 @@
     </row>
     <row r="93" spans="1:20" ht="15" customHeight="1">
       <c r="A93" s="69" t="s">
+        <v>645</v>
+      </c>
+      <c r="B93" s="69" t="s">
         <v>646</v>
-      </c>
-      <c r="B93" s="69" t="s">
-        <v>647</v>
       </c>
       <c r="C93" s="69" t="s">
         <v>97</v>
@@ -24917,14 +24978,14 @@
         <v>472</v>
       </c>
       <c r="L93" s="69" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="M93" s="69"/>
       <c r="N93" s="66" t="s">
         <v>511</v>
       </c>
       <c r="O93" s="69" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="P93" s="69"/>
       <c r="Q93" s="69"/>
@@ -24934,10 +24995,10 @@
     </row>
     <row r="94" spans="1:20" ht="15" customHeight="1">
       <c r="A94" s="66" t="s">
+        <v>649</v>
+      </c>
+      <c r="B94" s="66" t="s">
         <v>650</v>
-      </c>
-      <c r="B94" s="66" t="s">
-        <v>651</v>
       </c>
       <c r="C94" s="66" t="s">
         <v>95</v>
@@ -24986,10 +25047,10 @@
     </row>
     <row r="95" spans="1:20" ht="15" customHeight="1">
       <c r="A95" s="69" t="s">
+        <v>651</v>
+      </c>
+      <c r="B95" s="69" t="s">
         <v>652</v>
-      </c>
-      <c r="B95" s="69" t="s">
-        <v>653</v>
       </c>
       <c r="C95" s="69" t="s">
         <v>95</v>
@@ -25023,7 +25084,7 @@
         <v>0</v>
       </c>
       <c r="L95" s="69" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="M95" s="69"/>
       <c r="N95" s="69" t="s">
@@ -25038,10 +25099,10 @@
     </row>
     <row r="96" spans="1:20" ht="15" customHeight="1">
       <c r="A96" s="66" t="s">
+        <v>654</v>
+      </c>
+      <c r="B96" s="66" t="s">
         <v>655</v>
-      </c>
-      <c r="B96" s="66" t="s">
-        <v>656</v>
       </c>
       <c r="C96" s="66" t="s">
         <v>95</v>
@@ -25077,7 +25138,7 @@
       <c r="L96" s="66"/>
       <c r="M96" s="66"/>
       <c r="N96" s="66" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="O96" s="66"/>
       <c r="P96" s="66"/>
@@ -25088,10 +25149,10 @@
     </row>
     <row r="97" spans="1:20" ht="15" customHeight="1">
       <c r="A97" s="69" t="s">
+        <v>656</v>
+      </c>
+      <c r="B97" s="69" t="s">
         <v>657</v>
-      </c>
-      <c r="B97" s="69" t="s">
-        <v>658</v>
       </c>
       <c r="C97" s="69" t="s">
         <v>95</v>
@@ -25140,10 +25201,10 @@
     </row>
     <row r="98" spans="1:20" ht="15" customHeight="1">
       <c r="A98" s="66" t="s">
+        <v>658</v>
+      </c>
+      <c r="B98" s="66" t="s">
         <v>659</v>
-      </c>
-      <c r="B98" s="66" t="s">
-        <v>660</v>
       </c>
       <c r="C98" s="66" t="s">
         <v>96</v>
@@ -25194,10 +25255,10 @@
     </row>
     <row r="99" spans="1:20" ht="15" customHeight="1">
       <c r="A99" s="69" t="s">
+        <v>660</v>
+      </c>
+      <c r="B99" s="69" t="s">
         <v>661</v>
-      </c>
-      <c r="B99" s="69" t="s">
-        <v>662</v>
       </c>
       <c r="C99" s="69" t="s">
         <v>96</v>
@@ -25248,10 +25309,10 @@
     </row>
     <row r="100" spans="1:20" ht="15" customHeight="1">
       <c r="A100" s="66" t="s">
+        <v>662</v>
+      </c>
+      <c r="B100" s="66" t="s">
         <v>663</v>
-      </c>
-      <c r="B100" s="66" t="s">
-        <v>664</v>
       </c>
       <c r="C100" s="66" t="s">
         <v>96</v>
@@ -25302,10 +25363,10 @@
     </row>
     <row r="101" spans="1:20" ht="15" customHeight="1">
       <c r="A101" s="69" t="s">
+        <v>664</v>
+      </c>
+      <c r="B101" s="69" t="s">
         <v>665</v>
-      </c>
-      <c r="B101" s="69" t="s">
-        <v>666</v>
       </c>
       <c r="C101" s="69" t="s">
         <v>96</v>
@@ -25356,10 +25417,10 @@
     </row>
     <row r="102" spans="1:20" ht="15" customHeight="1">
       <c r="A102" s="66" t="s">
+        <v>666</v>
+      </c>
+      <c r="B102" s="66" t="s">
         <v>667</v>
-      </c>
-      <c r="B102" s="66" t="s">
-        <v>668</v>
       </c>
       <c r="C102" s="66" t="s">
         <v>96</v>
@@ -25410,10 +25471,10 @@
     </row>
     <row r="103" spans="1:20" ht="15" customHeight="1">
       <c r="A103" s="69" t="s">
+        <v>668</v>
+      </c>
+      <c r="B103" s="69" t="s">
         <v>669</v>
-      </c>
-      <c r="B103" s="69" t="s">
-        <v>670</v>
       </c>
       <c r="C103" s="69" t="s">
         <v>96</v>
@@ -25464,10 +25525,10 @@
     </row>
     <row r="104" spans="1:20" ht="15" customHeight="1">
       <c r="A104" s="66" t="s">
+        <v>670</v>
+      </c>
+      <c r="B104" s="66" t="s">
         <v>671</v>
-      </c>
-      <c r="B104" s="66" t="s">
-        <v>672</v>
       </c>
       <c r="C104" s="66" t="s">
         <v>96</v>
@@ -25518,10 +25579,10 @@
     </row>
     <row r="105" spans="1:20" ht="15" customHeight="1">
       <c r="A105" s="69" t="s">
+        <v>672</v>
+      </c>
+      <c r="B105" s="69" t="s">
         <v>673</v>
-      </c>
-      <c r="B105" s="69" t="s">
-        <v>674</v>
       </c>
       <c r="C105" s="69" t="s">
         <v>96</v>
@@ -25572,10 +25633,10 @@
     </row>
     <row r="106" spans="1:20" ht="15" customHeight="1">
       <c r="A106" s="66" t="s">
+        <v>674</v>
+      </c>
+      <c r="B106" s="66" t="s">
         <v>675</v>
-      </c>
-      <c r="B106" s="66" t="s">
-        <v>676</v>
       </c>
       <c r="C106" s="66" t="s">
         <v>96</v>
@@ -25626,10 +25687,10 @@
     </row>
     <row r="107" spans="1:20" ht="15" customHeight="1">
       <c r="A107" s="69" t="s">
+        <v>676</v>
+      </c>
+      <c r="B107" s="69" t="s">
         <v>677</v>
-      </c>
-      <c r="B107" s="69" t="s">
-        <v>678</v>
       </c>
       <c r="C107" s="69" t="s">
         <v>96</v>
@@ -25680,10 +25741,10 @@
     </row>
     <row r="108" spans="1:20" ht="15" customHeight="1">
       <c r="A108" s="66" t="s">
+        <v>678</v>
+      </c>
+      <c r="B108" s="66" t="s">
         <v>679</v>
-      </c>
-      <c r="B108" s="66" t="s">
-        <v>680</v>
       </c>
       <c r="C108" s="66" t="s">
         <v>96</v>
@@ -25734,10 +25795,10 @@
     </row>
     <row r="109" spans="1:20" ht="15" customHeight="1">
       <c r="A109" s="69" t="s">
+        <v>680</v>
+      </c>
+      <c r="B109" s="69" t="s">
         <v>681</v>
-      </c>
-      <c r="B109" s="69" t="s">
-        <v>682</v>
       </c>
       <c r="C109" s="69" t="s">
         <v>96</v>
@@ -25788,10 +25849,10 @@
     </row>
     <row r="110" spans="1:20" ht="15" customHeight="1">
       <c r="A110" s="66" t="s">
+        <v>682</v>
+      </c>
+      <c r="B110" s="66" t="s">
         <v>683</v>
-      </c>
-      <c r="B110" s="66" t="s">
-        <v>684</v>
       </c>
       <c r="C110" s="66" t="s">
         <v>96</v>
@@ -25842,10 +25903,10 @@
     </row>
     <row r="111" spans="1:20" ht="15" customHeight="1">
       <c r="A111" s="69" t="s">
+        <v>684</v>
+      </c>
+      <c r="B111" s="69" t="s">
         <v>685</v>
-      </c>
-      <c r="B111" s="69" t="s">
-        <v>686</v>
       </c>
       <c r="C111" s="69" t="s">
         <v>96</v>
@@ -25896,10 +25957,10 @@
     </row>
     <row r="112" spans="1:20" ht="15" customHeight="1">
       <c r="A112" s="66" t="s">
+        <v>686</v>
+      </c>
+      <c r="B112" s="66" t="s">
         <v>687</v>
-      </c>
-      <c r="B112" s="66" t="s">
-        <v>688</v>
       </c>
       <c r="C112" s="66" t="s">
         <v>96</v>
@@ -25935,7 +25996,7 @@
       <c r="L112" s="66"/>
       <c r="M112" s="66"/>
       <c r="N112" s="66" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="O112" s="66" t="s">
         <v>201</v>
@@ -25948,10 +26009,10 @@
     </row>
     <row r="113" spans="1:246" ht="15" customHeight="1">
       <c r="A113" s="69" t="s">
+        <v>688</v>
+      </c>
+      <c r="B113" s="69" t="s">
         <v>689</v>
-      </c>
-      <c r="B113" s="69" t="s">
-        <v>690</v>
       </c>
       <c r="C113" s="69" t="s">
         <v>96</v>
@@ -26002,10 +26063,10 @@
     </row>
     <row r="114" spans="1:246" ht="15" customHeight="1">
       <c r="A114" s="66" t="s">
+        <v>690</v>
+      </c>
+      <c r="B114" s="66" t="s">
         <v>691</v>
-      </c>
-      <c r="B114" s="66" t="s">
-        <v>692</v>
       </c>
       <c r="C114" s="66" t="s">
         <v>95</v>
@@ -26054,10 +26115,10 @@
     </row>
     <row r="115" spans="1:246" ht="30" customHeight="1">
       <c r="A115" s="69" t="s">
+        <v>692</v>
+      </c>
+      <c r="B115" s="69" t="s">
         <v>693</v>
-      </c>
-      <c r="B115" s="69" t="s">
-        <v>694</v>
       </c>
       <c r="C115" s="69" t="s">
         <v>95</v>
@@ -26091,7 +26152,7 @@
         <v>0</v>
       </c>
       <c r="L115" s="69" t="s">
-        <v>695</v>
+        <v>694</v>
       </c>
       <c r="M115" s="69"/>
       <c r="N115" s="69" t="s">
@@ -26106,10 +26167,10 @@
     </row>
     <row r="116" spans="1:246" ht="150" customHeight="1">
       <c r="A116" s="66" t="s">
+        <v>695</v>
+      </c>
+      <c r="B116" s="66" t="s">
         <v>696</v>
-      </c>
-      <c r="B116" s="66" t="s">
-        <v>697</v>
       </c>
       <c r="C116" s="66" t="s">
         <v>95</v>
@@ -26143,7 +26204,7 @@
         <v>0</v>
       </c>
       <c r="L116" s="66" t="s">
-        <v>698</v>
+        <v>697</v>
       </c>
       <c r="M116" s="66"/>
       <c r="N116" s="66" t="s">
@@ -26158,10 +26219,10 @@
     </row>
     <row r="117" spans="1:246" ht="15" customHeight="1">
       <c r="A117" s="69" t="s">
+        <v>698</v>
+      </c>
+      <c r="B117" s="69" t="s">
         <v>699</v>
-      </c>
-      <c r="B117" s="69" t="s">
-        <v>700</v>
       </c>
       <c r="C117" s="69" t="s">
         <v>95</v>
@@ -26210,10 +26271,10 @@
     </row>
     <row r="118" spans="1:246" ht="15" customHeight="1">
       <c r="A118" s="66" t="s">
+        <v>700</v>
+      </c>
+      <c r="B118" s="66" t="s">
         <v>701</v>
-      </c>
-      <c r="B118" s="66" t="s">
-        <v>702</v>
       </c>
       <c r="C118" s="66" t="s">
         <v>95</v>
@@ -26247,7 +26308,7 @@
         <v>2095.8000000000002</v>
       </c>
       <c r="L118" s="66" t="s">
-        <v>703</v>
+        <v>702</v>
       </c>
       <c r="M118" s="66"/>
       <c r="N118" s="66" t="s">
@@ -26255,7 +26316,7 @@
       </c>
       <c r="O118" s="66"/>
       <c r="P118" s="66" t="s">
-        <v>704</v>
+        <v>703</v>
       </c>
       <c r="Q118" s="66"/>
       <c r="R118" s="66"/>
@@ -26264,10 +26325,10 @@
     </row>
     <row r="119" spans="1:246" ht="15" customHeight="1">
       <c r="A119" s="69" t="s">
+        <v>704</v>
+      </c>
+      <c r="B119" s="69" t="s">
         <v>705</v>
-      </c>
-      <c r="B119" s="69" t="s">
-        <v>706</v>
       </c>
       <c r="C119" s="69" t="s">
         <v>95</v>
@@ -26316,10 +26377,10 @@
     </row>
     <row r="120" spans="1:246" ht="105" customHeight="1">
       <c r="A120" s="66" t="s">
+        <v>706</v>
+      </c>
+      <c r="B120" s="66" t="s">
         <v>707</v>
-      </c>
-      <c r="B120" s="66" t="s">
-        <v>708</v>
       </c>
       <c r="C120" s="66" t="s">
         <v>95</v>
@@ -26353,7 +26414,7 @@
         <v>12568.599999999989</v>
       </c>
       <c r="L120" s="66" t="s">
-        <v>709</v>
+        <v>928</v>
       </c>
       <c r="M120" s="66" t="s">
         <v>49</v>
@@ -26363,7 +26424,7 @@
       </c>
       <c r="O120" s="66"/>
       <c r="P120" s="66" t="s">
-        <v>710</v>
+        <v>927</v>
       </c>
       <c r="Q120" s="66"/>
       <c r="R120" s="66"/>
@@ -26372,10 +26433,10 @@
     </row>
     <row r="121" spans="1:246" ht="15" customHeight="1">
       <c r="A121" s="69" t="s">
-        <v>711</v>
+        <v>708</v>
       </c>
       <c r="B121" s="69" t="s">
-        <v>712</v>
+        <v>709</v>
       </c>
       <c r="C121" s="69" t="s">
         <v>95</v>
@@ -26409,7 +26470,7 @@
         <v>0</v>
       </c>
       <c r="L121" s="69" t="s">
-        <v>713</v>
+        <v>710</v>
       </c>
       <c r="M121" s="69"/>
       <c r="N121" s="69" t="s">
@@ -26417,7 +26478,7 @@
       </c>
       <c r="O121" s="69"/>
       <c r="P121" s="69" t="s">
-        <v>714</v>
+        <v>711</v>
       </c>
       <c r="Q121" s="69"/>
       <c r="R121" s="69"/>
@@ -26426,10 +26487,10 @@
     </row>
     <row r="122" spans="1:246" ht="15" customHeight="1">
       <c r="A122" s="66" t="s">
-        <v>715</v>
+        <v>712</v>
       </c>
       <c r="B122" s="66" t="s">
-        <v>716</v>
+        <v>713</v>
       </c>
       <c r="C122" s="66" t="s">
         <v>96</v>
@@ -26463,7 +26524,7 @@
         <v>4700</v>
       </c>
       <c r="L122" s="66" t="s">
-        <v>717</v>
+        <v>714</v>
       </c>
       <c r="M122" s="66"/>
       <c r="N122" s="66" t="s">
@@ -26478,10 +26539,10 @@
     </row>
     <row r="123" spans="1:246" s="72" customFormat="1" ht="75" customHeight="1">
       <c r="A123" s="78" t="s">
-        <v>718</v>
+        <v>715</v>
       </c>
       <c r="B123" s="78" t="s">
-        <v>719</v>
+        <v>716</v>
       </c>
       <c r="C123" s="78" t="s">
         <v>95</v>
@@ -26515,7 +26576,7 @@
         <v>891.44</v>
       </c>
       <c r="L123" s="78" t="s">
-        <v>720</v>
+        <v>717</v>
       </c>
       <c r="M123" s="78"/>
       <c r="N123" s="78" t="s">
@@ -26756,10 +26817,10 @@
     </row>
     <row r="124" spans="1:246" s="83" customFormat="1" ht="30" customHeight="1">
       <c r="A124" s="80" t="s">
-        <v>721</v>
+        <v>718</v>
       </c>
       <c r="B124" s="80" t="s">
-        <v>722</v>
+        <v>719</v>
       </c>
       <c r="C124" s="80" t="s">
         <v>95</v>
@@ -26793,7 +26854,7 @@
         <v>0</v>
       </c>
       <c r="L124" s="80" t="s">
-        <v>723</v>
+        <v>720</v>
       </c>
       <c r="M124" s="80"/>
       <c r="N124" s="80" t="s">
@@ -27036,10 +27097,10 @@
     </row>
     <row r="125" spans="1:246" s="72" customFormat="1" ht="15" customHeight="1">
       <c r="A125" s="78" t="s">
-        <v>724</v>
+        <v>721</v>
       </c>
       <c r="B125" s="78" t="s">
-        <v>725</v>
+        <v>722</v>
       </c>
       <c r="C125" s="78" t="s">
         <v>95</v>
@@ -27073,7 +27134,7 @@
         <v>0</v>
       </c>
       <c r="L125" s="78" t="s">
-        <v>726</v>
+        <v>723</v>
       </c>
       <c r="M125" s="78"/>
       <c r="N125" s="78" t="s">
@@ -27081,7 +27142,7 @@
       </c>
       <c r="O125" s="78"/>
       <c r="P125" s="78" t="s">
-        <v>727</v>
+        <v>724</v>
       </c>
       <c r="Q125" s="78"/>
       <c r="R125" s="78"/>
@@ -27316,10 +27377,10 @@
     </row>
     <row r="126" spans="1:246" ht="15" customHeight="1">
       <c r="A126" s="80" t="s">
-        <v>728</v>
+        <v>725</v>
       </c>
       <c r="B126" s="66" t="s">
-        <v>729</v>
+        <v>726</v>
       </c>
       <c r="C126" s="66" t="s">
         <v>96</v>
@@ -27353,14 +27414,14 @@
         <v>0</v>
       </c>
       <c r="L126" s="66" t="s">
-        <v>730</v>
+        <v>727</v>
       </c>
       <c r="M126" s="66"/>
       <c r="N126" s="66" t="s">
         <v>426</v>
       </c>
       <c r="O126" s="66" t="s">
-        <v>731</v>
+        <v>728</v>
       </c>
       <c r="P126" s="66"/>
       <c r="Q126" s="66"/>
@@ -27370,10 +27431,10 @@
     </row>
     <row r="127" spans="1:246" ht="15" customHeight="1">
       <c r="A127" s="78" t="s">
-        <v>732</v>
+        <v>729</v>
       </c>
       <c r="B127" s="69" t="s">
-        <v>733</v>
+        <v>730</v>
       </c>
       <c r="C127" s="69" t="s">
         <v>96</v>
@@ -27424,10 +27485,10 @@
     </row>
     <row r="128" spans="1:246" ht="15" customHeight="1">
       <c r="A128" s="80" t="s">
-        <v>734</v>
+        <v>731</v>
       </c>
       <c r="B128" s="66" t="s">
-        <v>735</v>
+        <v>732</v>
       </c>
       <c r="C128" s="66" t="s">
         <v>95</v>
@@ -27463,7 +27524,7 @@
       <c r="L128" s="66"/>
       <c r="M128" s="66"/>
       <c r="N128" s="66" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="O128" s="66"/>
       <c r="P128" s="66"/>
@@ -27474,10 +27535,10 @@
     </row>
     <row r="129" spans="1:20" ht="15" customHeight="1">
       <c r="A129" s="78" t="s">
-        <v>736</v>
+        <v>733</v>
       </c>
       <c r="B129" s="69" t="s">
-        <v>737</v>
+        <v>734</v>
       </c>
       <c r="C129" s="69" t="s">
         <v>95</v>
@@ -27511,7 +27572,7 @@
         <v>0</v>
       </c>
       <c r="L129" s="69" t="s">
-        <v>738</v>
+        <v>735</v>
       </c>
       <c r="M129" s="69"/>
       <c r="N129" s="69" t="s">
@@ -27526,10 +27587,10 @@
     </row>
     <row r="130" spans="1:20" ht="15" customHeight="1">
       <c r="A130" s="80" t="s">
-        <v>739</v>
+        <v>736</v>
       </c>
       <c r="B130" s="66" t="s">
-        <v>740</v>
+        <v>737</v>
       </c>
       <c r="C130" s="66" t="s">
         <v>95</v>
@@ -27563,7 +27624,7 @@
         <v>0</v>
       </c>
       <c r="L130" s="66" t="s">
-        <v>741</v>
+        <v>738</v>
       </c>
       <c r="M130" s="66"/>
       <c r="N130" s="66" t="s">
@@ -27578,10 +27639,10 @@
     </row>
     <row r="131" spans="1:20" ht="15" customHeight="1">
       <c r="A131" s="78" t="s">
-        <v>742</v>
+        <v>739</v>
       </c>
       <c r="B131" s="69" t="s">
-        <v>743</v>
+        <v>740</v>
       </c>
       <c r="C131" s="69" t="s">
         <v>95</v>
@@ -27617,7 +27678,7 @@
       <c r="L131" s="69"/>
       <c r="M131" s="69"/>
       <c r="N131" s="69" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="O131" s="69"/>
       <c r="P131" s="69"/>
@@ -27628,10 +27689,10 @@
     </row>
     <row r="132" spans="1:20" ht="15" customHeight="1">
       <c r="A132" s="80" t="s">
-        <v>744</v>
+        <v>741</v>
       </c>
       <c r="B132" s="66" t="s">
-        <v>745</v>
+        <v>742</v>
       </c>
       <c r="C132" s="66" t="s">
         <v>95</v>
@@ -27665,7 +27726,7 @@
         <v>0</v>
       </c>
       <c r="L132" s="66" t="s">
-        <v>746</v>
+        <v>743</v>
       </c>
       <c r="M132" s="66"/>
       <c r="N132" s="66" t="s">
@@ -27680,10 +27741,10 @@
     </row>
     <row r="133" spans="1:20" ht="15" customHeight="1">
       <c r="A133" s="78" t="s">
-        <v>747</v>
+        <v>744</v>
       </c>
       <c r="B133" s="69" t="s">
-        <v>748</v>
+        <v>745</v>
       </c>
       <c r="C133" s="69" t="s">
         <v>95</v>
@@ -27719,7 +27780,7 @@
       <c r="L133" s="69"/>
       <c r="M133" s="69"/>
       <c r="N133" s="69" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="O133" s="69"/>
       <c r="P133" s="69"/>
@@ -27730,10 +27791,10 @@
     </row>
     <row r="134" spans="1:20" ht="15" customHeight="1">
       <c r="A134" s="80" t="s">
-        <v>749</v>
+        <v>746</v>
       </c>
       <c r="B134" s="66" t="s">
-        <v>750</v>
+        <v>747</v>
       </c>
       <c r="C134" s="66" t="s">
         <v>95</v>
@@ -27769,7 +27830,7 @@
       <c r="L134" s="66"/>
       <c r="M134" s="66"/>
       <c r="N134" s="66" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="O134" s="66"/>
       <c r="P134" s="66"/>
@@ -27780,10 +27841,10 @@
     </row>
     <row r="135" spans="1:20" ht="15" customHeight="1">
       <c r="A135" s="78" t="s">
-        <v>751</v>
+        <v>748</v>
       </c>
       <c r="B135" s="69" t="s">
-        <v>752</v>
+        <v>749</v>
       </c>
       <c r="C135" s="69" t="s">
         <v>95</v>
@@ -27817,7 +27878,7 @@
         <v>0</v>
       </c>
       <c r="L135" s="69" t="s">
-        <v>753</v>
+        <v>750</v>
       </c>
       <c r="M135" s="69"/>
       <c r="N135" s="69" t="s">
@@ -27832,10 +27893,10 @@
     </row>
     <row r="136" spans="1:20" ht="15" customHeight="1">
       <c r="A136" s="80" t="s">
-        <v>754</v>
+        <v>751</v>
       </c>
       <c r="B136" s="66" t="s">
-        <v>755</v>
+        <v>752</v>
       </c>
       <c r="C136" s="66" t="s">
         <v>95</v>
@@ -27869,7 +27930,7 @@
         <v>0</v>
       </c>
       <c r="L136" s="66" t="s">
-        <v>756</v>
+        <v>753</v>
       </c>
       <c r="M136" s="66"/>
       <c r="N136" s="66" t="s">
@@ -27877,7 +27938,7 @@
       </c>
       <c r="O136" s="66"/>
       <c r="P136" s="66" t="s">
-        <v>757</v>
+        <v>754</v>
       </c>
       <c r="Q136" s="66"/>
       <c r="R136" s="66"/>
@@ -27886,10 +27947,10 @@
     </row>
     <row r="137" spans="1:20" ht="15" customHeight="1">
       <c r="A137" s="78" t="s">
-        <v>758</v>
+        <v>755</v>
       </c>
       <c r="B137" s="69" t="s">
-        <v>759</v>
+        <v>756</v>
       </c>
       <c r="C137" s="69" t="s">
         <v>95</v>
@@ -27938,10 +27999,10 @@
     </row>
     <row r="138" spans="1:20" ht="15" customHeight="1">
       <c r="A138" s="80" t="s">
-        <v>760</v>
+        <v>757</v>
       </c>
       <c r="B138" s="66" t="s">
-        <v>761</v>
+        <v>758</v>
       </c>
       <c r="C138" s="66" t="s">
         <v>95</v>
@@ -27975,7 +28036,7 @@
         <v>0</v>
       </c>
       <c r="L138" s="66" t="s">
-        <v>762</v>
+        <v>759</v>
       </c>
       <c r="M138" s="66"/>
       <c r="N138" s="66" t="s">
@@ -27990,10 +28051,10 @@
     </row>
     <row r="139" spans="1:20" ht="15" customHeight="1">
       <c r="A139" s="78" t="s">
-        <v>763</v>
+        <v>760</v>
       </c>
       <c r="B139" s="69" t="s">
-        <v>764</v>
+        <v>761</v>
       </c>
       <c r="C139" s="69" t="s">
         <v>95</v>
@@ -28042,10 +28103,10 @@
     </row>
     <row r="140" spans="1:20" ht="15" customHeight="1">
       <c r="A140" s="80" t="s">
-        <v>765</v>
+        <v>762</v>
       </c>
       <c r="B140" s="66" t="s">
-        <v>766</v>
+        <v>763</v>
       </c>
       <c r="C140" s="66" t="s">
         <v>95</v>
@@ -28079,7 +28140,7 @@
         <v>699</v>
       </c>
       <c r="L140" s="66" t="s">
-        <v>767</v>
+        <v>764</v>
       </c>
       <c r="M140" s="66"/>
       <c r="N140" s="66" t="s">
@@ -28094,10 +28155,10 @@
     </row>
     <row r="141" spans="1:20" ht="15" customHeight="1">
       <c r="A141" s="78" t="s">
-        <v>768</v>
+        <v>765</v>
       </c>
       <c r="B141" s="69" t="s">
-        <v>769</v>
+        <v>766</v>
       </c>
       <c r="C141" s="69" t="s">
         <v>95</v>
@@ -28133,7 +28194,7 @@
       <c r="L141" s="69"/>
       <c r="M141" s="69"/>
       <c r="N141" s="69" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="O141" s="69"/>
       <c r="P141" s="69"/>
@@ -28144,10 +28205,10 @@
     </row>
     <row r="142" spans="1:20" ht="15" customHeight="1">
       <c r="A142" s="66" t="s">
-        <v>770</v>
+        <v>767</v>
       </c>
       <c r="B142" s="66" t="s">
-        <v>771</v>
+        <v>768</v>
       </c>
       <c r="C142" s="66" t="s">
         <v>95</v>
@@ -28181,7 +28242,7 @@
         <v>600</v>
       </c>
       <c r="L142" s="66" t="s">
-        <v>772</v>
+        <v>769</v>
       </c>
       <c r="M142" s="66"/>
       <c r="N142" s="66" t="s">
@@ -28198,10 +28259,10 @@
     </row>
     <row r="143" spans="1:20" ht="15" customHeight="1">
       <c r="A143" s="69" t="s">
-        <v>773</v>
+        <v>770</v>
       </c>
       <c r="B143" s="69" t="s">
-        <v>774</v>
+        <v>771</v>
       </c>
       <c r="C143" s="69" t="s">
         <v>95</v>
@@ -28237,7 +28298,7 @@
       <c r="L143" s="69"/>
       <c r="M143" s="69"/>
       <c r="N143" s="69" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="O143" s="69"/>
       <c r="P143" s="69"/>
@@ -28248,10 +28309,10 @@
     </row>
     <row r="144" spans="1:20" ht="15" customHeight="1">
       <c r="A144" s="66" t="s">
-        <v>775</v>
+        <v>772</v>
       </c>
       <c r="B144" s="66" t="s">
-        <v>776</v>
+        <v>773</v>
       </c>
       <c r="C144" s="66" t="s">
         <v>95</v>
@@ -28287,7 +28348,7 @@
       <c r="L144" s="66"/>
       <c r="M144" s="66"/>
       <c r="N144" s="66" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="O144" s="66"/>
       <c r="P144" s="66"/>
@@ -28298,7 +28359,7 @@
     </row>
     <row r="145" spans="1:20" ht="15" customHeight="1">
       <c r="A145" s="69" t="s">
-        <v>777</v>
+        <v>774</v>
       </c>
       <c r="B145" s="69" t="s">
         <v>296</v>
@@ -28350,10 +28411,10 @@
     </row>
     <row r="146" spans="1:20" ht="15" customHeight="1">
       <c r="A146" s="66" t="s">
-        <v>778</v>
+        <v>775</v>
       </c>
       <c r="B146" s="66" t="s">
-        <v>779</v>
+        <v>776</v>
       </c>
       <c r="C146" s="66" t="s">
         <v>95</v>
@@ -28387,7 +28448,7 @@
         <v>761</v>
       </c>
       <c r="L146" s="66" t="s">
-        <v>780</v>
+        <v>777</v>
       </c>
       <c r="M146" s="66"/>
       <c r="N146" s="66" t="s">
@@ -28395,7 +28456,7 @@
       </c>
       <c r="O146" s="66"/>
       <c r="P146" s="66" t="s">
-        <v>781</v>
+        <v>778</v>
       </c>
       <c r="Q146" s="66"/>
       <c r="R146" s="66"/>
@@ -28404,10 +28465,10 @@
     </row>
     <row r="147" spans="1:20" ht="63.75" customHeight="1">
       <c r="A147" s="69" t="s">
-        <v>782</v>
+        <v>779</v>
       </c>
       <c r="B147" s="69" t="s">
-        <v>783</v>
+        <v>780</v>
       </c>
       <c r="C147" s="69" t="s">
         <v>95</v>
@@ -28441,7 +28502,7 @@
         <v>4314</v>
       </c>
       <c r="L147" s="69" t="s">
-        <v>784</v>
+        <v>781</v>
       </c>
       <c r="M147" s="69"/>
       <c r="N147" s="69" t="s">
@@ -28449,7 +28510,7 @@
       </c>
       <c r="O147" s="69"/>
       <c r="P147" s="69" t="s">
-        <v>785</v>
+        <v>782</v>
       </c>
       <c r="Q147" s="69"/>
       <c r="R147" s="69"/>
@@ -28458,10 +28519,10 @@
     </row>
     <row r="148" spans="1:20" ht="15" customHeight="1">
       <c r="A148" s="66" t="s">
-        <v>786</v>
+        <v>783</v>
       </c>
       <c r="B148" s="66" t="s">
-        <v>787</v>
+        <v>784</v>
       </c>
       <c r="C148" s="66" t="s">
         <v>95</v>
@@ -28495,7 +28556,7 @@
         <v>502</v>
       </c>
       <c r="L148" s="66" t="s">
-        <v>788</v>
+        <v>785</v>
       </c>
       <c r="M148" s="66"/>
       <c r="N148" s="66" t="s">
@@ -28510,10 +28571,10 @@
     </row>
     <row r="149" spans="1:20" ht="15" customHeight="1">
       <c r="A149" s="69" t="s">
-        <v>789</v>
+        <v>786</v>
       </c>
       <c r="B149" s="69" t="s">
-        <v>790</v>
+        <v>787</v>
       </c>
       <c r="C149" s="69" t="s">
         <v>95</v>
@@ -28547,7 +28608,7 @@
         <v>1024</v>
       </c>
       <c r="L149" s="69" t="s">
-        <v>791</v>
+        <v>788</v>
       </c>
       <c r="M149" s="69"/>
       <c r="N149" s="69" t="s">
@@ -28562,10 +28623,10 @@
     </row>
     <row r="150" spans="1:20" ht="15" customHeight="1">
       <c r="A150" s="66" t="s">
-        <v>792</v>
+        <v>789</v>
       </c>
       <c r="B150" s="66" t="s">
-        <v>793</v>
+        <v>790</v>
       </c>
       <c r="C150" s="66" t="s">
         <v>95</v>
@@ -28601,7 +28662,7 @@
       <c r="L150" s="66"/>
       <c r="M150" s="66"/>
       <c r="N150" s="66" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="O150" s="66"/>
       <c r="P150" s="66"/>
@@ -28612,10 +28673,10 @@
     </row>
     <row r="151" spans="1:20" ht="15" customHeight="1">
       <c r="A151" s="69" t="s">
-        <v>794</v>
+        <v>791</v>
       </c>
       <c r="B151" s="69" t="s">
-        <v>795</v>
+        <v>792</v>
       </c>
       <c r="C151" s="69" t="s">
         <v>96</v>
@@ -28649,7 +28710,7 @@
         <v>645</v>
       </c>
       <c r="L151" s="69" t="s">
-        <v>796</v>
+        <v>793</v>
       </c>
       <c r="M151" s="69"/>
       <c r="N151" s="69" t="s">
@@ -28659,7 +28720,7 @@
         <v>210</v>
       </c>
       <c r="P151" s="69" t="s">
-        <v>797</v>
+        <v>794</v>
       </c>
       <c r="Q151" s="69"/>
       <c r="R151" s="69"/>
@@ -28668,10 +28729,10 @@
     </row>
     <row r="152" spans="1:20" ht="15" customHeight="1">
       <c r="A152" s="66" t="s">
-        <v>798</v>
+        <v>795</v>
       </c>
       <c r="B152" s="66" t="s">
-        <v>799</v>
+        <v>796</v>
       </c>
       <c r="C152" s="66" t="s">
         <v>97</v>
@@ -28705,17 +28766,17 @@
         <v>885</v>
       </c>
       <c r="L152" s="66" t="s">
-        <v>800</v>
+        <v>797</v>
       </c>
       <c r="M152" s="66"/>
       <c r="N152" s="66" t="s">
         <v>511</v>
       </c>
       <c r="O152" s="66" t="s">
-        <v>801</v>
+        <v>798</v>
       </c>
       <c r="P152" s="66" t="s">
-        <v>802</v>
+        <v>799</v>
       </c>
       <c r="Q152" s="66"/>
       <c r="R152" s="66"/>
@@ -28724,10 +28785,10 @@
     </row>
     <row r="153" spans="1:20" ht="15" customHeight="1">
       <c r="A153" s="69" t="s">
-        <v>803</v>
+        <v>800</v>
       </c>
       <c r="B153" s="69" t="s">
-        <v>804</v>
+        <v>801</v>
       </c>
       <c r="C153" s="69" t="s">
         <v>95</v>
@@ -28761,7 +28822,7 @@
         <v>891.5</v>
       </c>
       <c r="L153" s="69" t="s">
-        <v>805</v>
+        <v>802</v>
       </c>
       <c r="M153" s="69"/>
       <c r="N153" s="69" t="s">
@@ -28769,7 +28830,7 @@
       </c>
       <c r="O153" s="69"/>
       <c r="P153" s="69" t="s">
-        <v>806</v>
+        <v>803</v>
       </c>
       <c r="Q153" s="69"/>
       <c r="R153" s="69"/>
@@ -28778,10 +28839,10 @@
     </row>
     <row r="154" spans="1:20" ht="15" customHeight="1">
       <c r="A154" s="66" t="s">
-        <v>807</v>
+        <v>804</v>
       </c>
       <c r="B154" s="66" t="s">
-        <v>808</v>
+        <v>805</v>
       </c>
       <c r="C154" s="66" t="s">
         <v>96</v>
@@ -28815,14 +28876,14 @@
         <v>1898</v>
       </c>
       <c r="L154" s="66" t="s">
-        <v>809</v>
+        <v>806</v>
       </c>
       <c r="M154" s="66"/>
       <c r="N154" s="66" t="s">
         <v>511</v>
       </c>
       <c r="O154" s="66" t="s">
-        <v>810</v>
+        <v>807</v>
       </c>
       <c r="P154" s="66"/>
       <c r="Q154" s="66"/>
@@ -28832,10 +28893,10 @@
     </row>
     <row r="155" spans="1:20" ht="15" customHeight="1">
       <c r="A155" s="69" t="s">
-        <v>811</v>
+        <v>808</v>
       </c>
       <c r="B155" s="69" t="s">
-        <v>812</v>
+        <v>809</v>
       </c>
       <c r="C155" s="69" t="s">
         <v>96</v>
@@ -28871,10 +28932,10 @@
       <c r="L155" s="69"/>
       <c r="M155" s="69"/>
       <c r="N155" s="69" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="O155" s="69" t="s">
-        <v>813</v>
+        <v>810</v>
       </c>
       <c r="P155" s="69"/>
       <c r="Q155" s="69"/>
@@ -28884,10 +28945,10 @@
     </row>
     <row r="156" spans="1:20" ht="15" customHeight="1">
       <c r="A156" s="66" t="s">
-        <v>814</v>
+        <v>811</v>
       </c>
       <c r="B156" s="66" t="s">
-        <v>815</v>
+        <v>812</v>
       </c>
       <c r="C156" s="66" t="s">
         <v>96</v>
@@ -28921,14 +28982,14 @@
         <v>2850</v>
       </c>
       <c r="L156" s="66" t="s">
-        <v>816</v>
+        <v>813</v>
       </c>
       <c r="M156" s="66"/>
       <c r="N156" s="66" t="s">
         <v>511</v>
       </c>
       <c r="O156" s="66" t="s">
-        <v>813</v>
+        <v>810</v>
       </c>
       <c r="P156" s="66"/>
       <c r="Q156" s="66"/>
@@ -28938,10 +28999,10 @@
     </row>
     <row r="157" spans="1:20" ht="15" customHeight="1">
       <c r="A157" s="69" t="s">
-        <v>817</v>
+        <v>814</v>
       </c>
       <c r="B157" s="69" t="s">
-        <v>818</v>
+        <v>815</v>
       </c>
       <c r="C157" s="69" t="s">
         <v>96</v>
@@ -28975,14 +29036,14 @@
         <v>1575</v>
       </c>
       <c r="L157" s="69" t="s">
-        <v>819</v>
+        <v>816</v>
       </c>
       <c r="M157" s="69"/>
       <c r="N157" s="69" t="s">
         <v>511</v>
       </c>
       <c r="O157" s="69" t="s">
-        <v>820</v>
+        <v>817</v>
       </c>
       <c r="P157" s="69"/>
       <c r="Q157" s="69"/>
@@ -28992,10 +29053,10 @@
     </row>
     <row r="158" spans="1:20" ht="15" customHeight="1">
       <c r="A158" s="66" t="s">
-        <v>821</v>
+        <v>818</v>
       </c>
       <c r="B158" s="66" t="s">
-        <v>822</v>
+        <v>819</v>
       </c>
       <c r="C158" s="66" t="s">
         <v>96</v>
@@ -29029,14 +29090,14 @@
         <v>3356</v>
       </c>
       <c r="L158" s="66" t="s">
-        <v>823</v>
+        <v>820</v>
       </c>
       <c r="M158" s="66"/>
       <c r="N158" s="66" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="O158" s="66" t="s">
-        <v>824</v>
+        <v>821</v>
       </c>
       <c r="P158" s="66"/>
       <c r="Q158" s="66"/>
@@ -29046,10 +29107,10 @@
     </row>
     <row r="159" spans="1:20" ht="15" customHeight="1">
       <c r="A159" s="69" t="s">
-        <v>825</v>
+        <v>822</v>
       </c>
       <c r="B159" s="69" t="s">
-        <v>826</v>
+        <v>823</v>
       </c>
       <c r="C159" s="69" t="s">
         <v>96</v>
@@ -29083,14 +29144,14 @@
         <v>2517</v>
       </c>
       <c r="L159" s="69" t="s">
-        <v>827</v>
+        <v>824</v>
       </c>
       <c r="M159" s="69"/>
       <c r="N159" s="69" t="s">
         <v>511</v>
       </c>
       <c r="O159" s="69" t="s">
-        <v>828</v>
+        <v>825</v>
       </c>
       <c r="P159" s="69"/>
       <c r="Q159" s="69"/>
@@ -29100,10 +29161,10 @@
     </row>
     <row r="160" spans="1:20" ht="15" customHeight="1">
       <c r="A160" s="66" t="s">
-        <v>829</v>
+        <v>826</v>
       </c>
       <c r="B160" s="66" t="s">
-        <v>830</v>
+        <v>827</v>
       </c>
       <c r="C160" s="66" t="s">
         <v>95</v>
@@ -29152,10 +29213,10 @@
     </row>
     <row r="161" spans="1:20" ht="15" customHeight="1">
       <c r="A161" s="69" t="s">
-        <v>831</v>
+        <v>828</v>
       </c>
       <c r="B161" s="69" t="s">
-        <v>832</v>
+        <v>829</v>
       </c>
       <c r="C161" s="69" t="s">
         <v>95</v>
@@ -29204,10 +29265,10 @@
     </row>
     <row r="162" spans="1:20" ht="15" customHeight="1">
       <c r="A162" s="66" t="s">
-        <v>833</v>
+        <v>830</v>
       </c>
       <c r="B162" s="66" t="s">
-        <v>834</v>
+        <v>831</v>
       </c>
       <c r="C162" s="66" t="s">
         <v>95</v>
@@ -29256,10 +29317,10 @@
     </row>
     <row r="163" spans="1:20" ht="15" customHeight="1">
       <c r="A163" s="69" t="s">
-        <v>835</v>
+        <v>832</v>
       </c>
       <c r="B163" s="69" t="s">
-        <v>836</v>
+        <v>833</v>
       </c>
       <c r="C163" s="69" t="s">
         <v>95</v>
@@ -29295,7 +29356,7 @@
       <c r="L163" s="69"/>
       <c r="M163" s="69"/>
       <c r="N163" s="69" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="O163" s="69"/>
       <c r="P163" s="69"/>
@@ -29306,10 +29367,10 @@
     </row>
     <row r="164" spans="1:20" ht="60" customHeight="1">
       <c r="A164" s="66" t="s">
-        <v>837</v>
+        <v>834</v>
       </c>
       <c r="B164" s="66" t="s">
-        <v>838</v>
+        <v>835</v>
       </c>
       <c r="C164" s="66" t="s">
         <v>95</v>
@@ -29343,7 +29404,7 @@
         <v>2026</v>
       </c>
       <c r="L164" s="66" t="s">
-        <v>839</v>
+        <v>836</v>
       </c>
       <c r="M164" s="66"/>
       <c r="N164" s="66" t="s">
@@ -29351,7 +29412,7 @@
       </c>
       <c r="O164" s="66"/>
       <c r="P164" s="66" t="s">
-        <v>840</v>
+        <v>837</v>
       </c>
       <c r="Q164" s="66"/>
       <c r="R164" s="66"/>
@@ -29360,10 +29421,10 @@
     </row>
     <row r="165" spans="1:20" ht="15" customHeight="1">
       <c r="A165" s="69" t="s">
-        <v>841</v>
+        <v>838</v>
       </c>
       <c r="B165" s="69" t="s">
-        <v>842</v>
+        <v>839</v>
       </c>
       <c r="C165" s="69" t="s">
         <v>95</v>
@@ -29405,7 +29466,7 @@
       </c>
       <c r="O165" s="69"/>
       <c r="P165" s="69" t="s">
-        <v>843</v>
+        <v>840</v>
       </c>
       <c r="Q165" s="69"/>
       <c r="R165" s="69"/>
@@ -29414,10 +29475,10 @@
     </row>
     <row r="166" spans="1:20" ht="15" customHeight="1">
       <c r="A166" s="66" t="s">
-        <v>844</v>
+        <v>841</v>
       </c>
       <c r="B166" s="66" t="s">
-        <v>845</v>
+        <v>842</v>
       </c>
       <c r="C166" s="66" t="s">
         <v>95</v>
@@ -29453,11 +29514,11 @@
       <c r="L166" s="66"/>
       <c r="M166" s="66"/>
       <c r="N166" s="66" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="O166" s="66"/>
       <c r="P166" s="66" t="s">
-        <v>846</v>
+        <v>843</v>
       </c>
       <c r="Q166" s="66"/>
       <c r="R166" s="66"/>
@@ -29466,10 +29527,10 @@
     </row>
     <row r="167" spans="1:20" ht="15" customHeight="1">
       <c r="A167" s="69" t="s">
-        <v>847</v>
+        <v>844</v>
       </c>
       <c r="B167" s="69" t="s">
-        <v>848</v>
+        <v>845</v>
       </c>
       <c r="C167" s="69" t="s">
         <v>95</v>
@@ -29503,7 +29564,7 @@
         <v>2220</v>
       </c>
       <c r="L167" s="69" t="s">
-        <v>849</v>
+        <v>846</v>
       </c>
       <c r="M167" s="69"/>
       <c r="N167" s="69" t="s">
@@ -29511,7 +29572,7 @@
       </c>
       <c r="O167" s="69"/>
       <c r="P167" s="69" t="s">
-        <v>850</v>
+        <v>847</v>
       </c>
       <c r="Q167" s="69"/>
       <c r="R167" s="69"/>
@@ -29520,10 +29581,10 @@
     </row>
     <row r="168" spans="1:20" ht="15" customHeight="1">
       <c r="A168" s="66" t="s">
-        <v>851</v>
+        <v>848</v>
       </c>
       <c r="B168" s="66" t="s">
-        <v>852</v>
+        <v>849</v>
       </c>
       <c r="C168" s="66" t="s">
         <v>95</v>
@@ -29557,7 +29618,7 @@
         <v>1216</v>
       </c>
       <c r="L168" s="66" t="s">
-        <v>853</v>
+        <v>850</v>
       </c>
       <c r="M168" s="66"/>
       <c r="N168" s="66" t="s">
@@ -29565,7 +29626,7 @@
       </c>
       <c r="O168" s="66"/>
       <c r="P168" s="66" t="s">
-        <v>854</v>
+        <v>851</v>
       </c>
       <c r="Q168" s="66"/>
       <c r="R168" s="66"/>
@@ -29574,10 +29635,10 @@
     </row>
     <row r="169" spans="1:20" ht="15" customHeight="1">
       <c r="A169" s="69" t="s">
-        <v>855</v>
+        <v>852</v>
       </c>
       <c r="B169" s="69" t="s">
-        <v>856</v>
+        <v>853</v>
       </c>
       <c r="C169" s="69" t="s">
         <v>95</v>
@@ -29613,11 +29674,11 @@
       <c r="L169" s="69"/>
       <c r="M169" s="69"/>
       <c r="N169" s="69" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="O169" s="69"/>
       <c r="P169" s="69" t="s">
-        <v>857</v>
+        <v>854</v>
       </c>
       <c r="Q169" s="69"/>
       <c r="R169" s="69"/>
@@ -29626,10 +29687,10 @@
     </row>
     <row r="170" spans="1:20" ht="30" customHeight="1">
       <c r="A170" s="66" t="s">
-        <v>858</v>
+        <v>855</v>
       </c>
       <c r="B170" s="66" t="s">
-        <v>859</v>
+        <v>856</v>
       </c>
       <c r="C170" s="66" t="s">
         <v>95</v>
@@ -29663,7 +29724,7 @@
         <v>0</v>
       </c>
       <c r="L170" s="66" t="s">
-        <v>860</v>
+        <v>857</v>
       </c>
       <c r="M170" s="66"/>
       <c r="N170" s="66" t="s">
@@ -29671,7 +29732,7 @@
       </c>
       <c r="O170" s="66"/>
       <c r="P170" s="66" t="s">
-        <v>861</v>
+        <v>858</v>
       </c>
       <c r="Q170" s="66"/>
       <c r="R170" s="66"/>
@@ -29680,10 +29741,10 @@
     </row>
     <row r="171" spans="1:20" ht="31.5" customHeight="1">
       <c r="A171" s="69" t="s">
-        <v>862</v>
+        <v>859</v>
       </c>
       <c r="B171" s="66" t="s">
-        <v>863</v>
+        <v>860</v>
       </c>
       <c r="C171" s="69" t="s">
         <v>95</v>
@@ -29717,7 +29778,7 @@
         <v>0</v>
       </c>
       <c r="L171" s="69" t="s">
-        <v>864</v>
+        <v>861</v>
       </c>
       <c r="M171" s="69"/>
       <c r="N171" s="69" t="s">
@@ -29732,10 +29793,10 @@
     </row>
     <row r="172" spans="1:20" ht="15" customHeight="1">
       <c r="A172" s="66" t="s">
-        <v>865</v>
+        <v>862</v>
       </c>
       <c r="B172" s="66" t="s">
-        <v>866</v>
+        <v>863</v>
       </c>
       <c r="C172" s="66" t="s">
         <v>95</v>
@@ -29747,10 +29808,10 @@
         <v>1550</v>
       </c>
       <c r="F172" s="81">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G172" s="81">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H172" s="80">
         <f t="shared" si="15"/>
@@ -29762,16 +29823,18 @@
       </c>
       <c r="J172" s="80">
         <f t="shared" si="16"/>
-        <v>0</v>
+        <v>1047</v>
       </c>
       <c r="K172" s="80">
         <f t="shared" si="17"/>
-        <v>4188</v>
-      </c>
-      <c r="L172" s="66"/>
+        <v>3141</v>
+      </c>
+      <c r="L172" s="66" t="s">
+        <v>931</v>
+      </c>
       <c r="M172" s="66"/>
       <c r="N172" s="66" t="s">
-        <v>601</v>
+        <v>511</v>
       </c>
       <c r="O172" s="66"/>
       <c r="P172" s="66"/>
@@ -29782,10 +29845,10 @@
     </row>
     <row r="173" spans="1:20" ht="15" customHeight="1">
       <c r="A173" s="69" t="s">
-        <v>867</v>
+        <v>864</v>
       </c>
       <c r="B173" s="69" t="s">
-        <v>868</v>
+        <v>865</v>
       </c>
       <c r="C173" s="69" t="s">
         <v>95</v>
@@ -29834,10 +29897,10 @@
     </row>
     <row r="174" spans="1:20" ht="15" customHeight="1">
       <c r="A174" s="66" t="s">
-        <v>869</v>
+        <v>866</v>
       </c>
       <c r="B174" s="66" t="s">
-        <v>870</v>
+        <v>867</v>
       </c>
       <c r="C174" s="66" t="s">
         <v>95</v>
@@ -29871,7 +29934,7 @@
         <v>0</v>
       </c>
       <c r="L174" s="66" t="s">
-        <v>871</v>
+        <v>868</v>
       </c>
       <c r="M174" s="66"/>
       <c r="N174" s="66" t="s">
@@ -29886,10 +29949,10 @@
     </row>
     <row r="175" spans="1:20" ht="90" customHeight="1">
       <c r="A175" s="69" t="s">
-        <v>872</v>
+        <v>869</v>
       </c>
       <c r="B175" s="69" t="s">
-        <v>873</v>
+        <v>870</v>
       </c>
       <c r="C175" s="69" t="s">
         <v>95</v>
@@ -29923,7 +29986,7 @@
         <v>4887.75</v>
       </c>
       <c r="L175" s="69" t="s">
-        <v>874</v>
+        <v>871</v>
       </c>
       <c r="M175" s="69"/>
       <c r="N175" s="69" t="s">
@@ -29931,7 +29994,7 @@
       </c>
       <c r="O175" s="69"/>
       <c r="P175" s="69" t="s">
-        <v>875</v>
+        <v>872</v>
       </c>
       <c r="Q175" s="69"/>
       <c r="R175" s="69"/>
@@ -29940,10 +30003,10 @@
     </row>
     <row r="176" spans="1:20" ht="15" customHeight="1">
       <c r="A176" s="66" t="s">
-        <v>876</v>
+        <v>873</v>
       </c>
       <c r="B176" s="66" t="s">
-        <v>877</v>
+        <v>874</v>
       </c>
       <c r="C176" s="66" t="s">
         <v>95</v>
@@ -29977,15 +30040,15 @@
         <v>1816</v>
       </c>
       <c r="L176" s="66" t="s">
-        <v>878</v>
+        <v>875</v>
       </c>
       <c r="M176" s="66"/>
       <c r="N176" s="66" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="O176" s="66"/>
       <c r="P176" s="66" t="s">
-        <v>879</v>
+        <v>876</v>
       </c>
       <c r="Q176" s="66"/>
       <c r="R176" s="66"/>
@@ -29994,10 +30057,10 @@
     </row>
     <row r="177" spans="1:20" ht="15" customHeight="1">
       <c r="A177" s="69" t="s">
-        <v>880</v>
+        <v>877</v>
       </c>
       <c r="B177" s="69" t="s">
-        <v>881</v>
+        <v>878</v>
       </c>
       <c r="C177" s="69" t="s">
         <v>95</v>
@@ -30031,7 +30094,7 @@
         <v>1812</v>
       </c>
       <c r="L177" s="69" t="s">
-        <v>882</v>
+        <v>879</v>
       </c>
       <c r="M177" s="69"/>
       <c r="N177" s="69" t="s">
@@ -30039,7 +30102,7 @@
       </c>
       <c r="O177" s="69"/>
       <c r="P177" s="69" t="s">
-        <v>883</v>
+        <v>880</v>
       </c>
       <c r="Q177" s="69"/>
       <c r="R177" s="69"/>
@@ -30048,10 +30111,10 @@
     </row>
     <row r="178" spans="1:20" ht="15" customHeight="1">
       <c r="A178" s="66" t="s">
-        <v>884</v>
+        <v>881</v>
       </c>
       <c r="B178" s="66" t="s">
-        <v>885</v>
+        <v>882</v>
       </c>
       <c r="C178" s="66" t="s">
         <v>95</v>
@@ -30063,10 +30126,10 @@
         <v>1400</v>
       </c>
       <c r="F178" s="81">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G178" s="81">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H178" s="80">
         <f t="shared" si="15"/>
@@ -30078,22 +30141,22 @@
       </c>
       <c r="J178" s="80">
         <f t="shared" si="16"/>
-        <v>938</v>
+        <v>0</v>
       </c>
       <c r="K178" s="80">
         <f t="shared" si="17"/>
-        <v>938</v>
+        <v>1876</v>
       </c>
       <c r="L178" s="66" t="s">
-        <v>886</v>
+        <v>939</v>
       </c>
       <c r="M178" s="66"/>
       <c r="N178" s="66" t="s">
-        <v>511</v>
+        <v>426</v>
       </c>
       <c r="O178" s="66"/>
       <c r="P178" s="66" t="s">
-        <v>887</v>
+        <v>883</v>
       </c>
       <c r="Q178" s="66"/>
       <c r="R178" s="66"/>
@@ -30102,10 +30165,10 @@
     </row>
     <row r="179" spans="1:20" ht="30" customHeight="1">
       <c r="A179" s="69" t="s">
-        <v>888</v>
+        <v>884</v>
       </c>
       <c r="B179" s="69" t="s">
-        <v>889</v>
+        <v>885</v>
       </c>
       <c r="C179" s="69" t="s">
         <v>95</v>
@@ -30139,7 +30202,7 @@
         <v>0</v>
       </c>
       <c r="L179" s="69" t="s">
-        <v>890</v>
+        <v>886</v>
       </c>
       <c r="M179" s="69"/>
       <c r="N179" s="69" t="s">
@@ -30147,7 +30210,7 @@
       </c>
       <c r="O179" s="69"/>
       <c r="P179" s="69" t="s">
-        <v>891</v>
+        <v>887</v>
       </c>
       <c r="Q179" s="69"/>
       <c r="R179" s="69"/>
@@ -30156,10 +30219,10 @@
     </row>
     <row r="180" spans="1:20" ht="15" customHeight="1">
       <c r="A180" s="66" t="s">
-        <v>892</v>
+        <v>888</v>
       </c>
       <c r="B180" s="66" t="s">
-        <v>893</v>
+        <v>889</v>
       </c>
       <c r="C180" s="66" t="s">
         <v>95</v>
@@ -30171,10 +30234,10 @@
         <v>1380</v>
       </c>
       <c r="F180" s="81">
+        <v>2</v>
+      </c>
+      <c r="G180" s="81">
         <v>1</v>
-      </c>
-      <c r="G180" s="81">
-        <v>2</v>
       </c>
       <c r="H180" s="80">
         <f t="shared" si="15"/>
@@ -30186,14 +30249,14 @@
       </c>
       <c r="J180" s="80">
         <f t="shared" si="16"/>
-        <v>919</v>
+        <v>1838</v>
       </c>
       <c r="K180" s="80">
         <f t="shared" si="17"/>
-        <v>1838</v>
+        <v>919</v>
       </c>
       <c r="L180" s="66" t="s">
-        <v>894</v>
+        <v>929</v>
       </c>
       <c r="M180" s="66"/>
       <c r="N180" s="66" t="s">
@@ -30201,7 +30264,7 @@
       </c>
       <c r="O180" s="66"/>
       <c r="P180" s="66" t="s">
-        <v>895</v>
+        <v>930</v>
       </c>
       <c r="Q180" s="66"/>
       <c r="R180" s="66"/>
@@ -30210,7 +30273,7 @@
     </row>
     <row r="181" spans="1:20" ht="15" customHeight="1">
       <c r="A181" s="69" t="s">
-        <v>896</v>
+        <v>890</v>
       </c>
       <c r="B181" s="69"/>
       <c r="C181" s="69"/>
@@ -30234,7 +30297,7 @@
     </row>
     <row r="182" spans="1:20" ht="15" customHeight="1">
       <c r="A182" s="66" t="s">
-        <v>897</v>
+        <v>891</v>
       </c>
       <c r="B182" s="66"/>
       <c r="C182" s="66"/>
@@ -30258,7 +30321,7 @@
     </row>
     <row r="183" spans="1:20" ht="15" customHeight="1">
       <c r="A183" s="69" t="s">
-        <v>898</v>
+        <v>892</v>
       </c>
       <c r="B183" s="69"/>
       <c r="C183" s="69"/>
@@ -30282,7 +30345,7 @@
     </row>
     <row r="184" spans="1:20" ht="15" customHeight="1">
       <c r="A184" s="66" t="s">
-        <v>899</v>
+        <v>893</v>
       </c>
       <c r="B184" s="66"/>
       <c r="C184" s="66"/>
@@ -30306,7 +30369,7 @@
     </row>
     <row r="185" spans="1:20" ht="15" customHeight="1">
       <c r="A185" s="69" t="s">
-        <v>900</v>
+        <v>894</v>
       </c>
       <c r="B185" s="69"/>
       <c r="C185" s="69"/>
@@ -30330,7 +30393,7 @@
     </row>
     <row r="186" spans="1:20" ht="15" customHeight="1">
       <c r="A186" s="66" t="s">
-        <v>901</v>
+        <v>895</v>
       </c>
       <c r="B186" s="66"/>
       <c r="C186" s="66"/>
@@ -30354,7 +30417,7 @@
     </row>
     <row r="187" spans="1:20" ht="15" customHeight="1">
       <c r="A187" s="69" t="s">
-        <v>902</v>
+        <v>896</v>
       </c>
       <c r="B187" s="69"/>
       <c r="C187" s="69"/>
@@ -30378,7 +30441,7 @@
     </row>
     <row r="188" spans="1:20" ht="15" customHeight="1">
       <c r="A188" s="66" t="s">
-        <v>903</v>
+        <v>897</v>
       </c>
       <c r="B188" s="66"/>
       <c r="C188" s="66"/>
@@ -34452,7 +34515,7 @@
   <sheetData>
     <row r="1" spans="1:8" ht="15" customHeight="1">
       <c r="A1" s="95" t="s">
-        <v>904</v>
+        <v>898</v>
       </c>
       <c r="B1" s="95"/>
     </row>
@@ -34461,7 +34524,7 @@
         <v>42</v>
       </c>
       <c r="B2" s="8" t="s">
-        <v>905</v>
+        <v>899</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="13.5" customHeight="1">
@@ -34493,25 +34556,25 @@
         <v>42</v>
       </c>
       <c r="B7" s="86" t="s">
+        <v>900</v>
+      </c>
+      <c r="C7" s="86" t="s">
+        <v>901</v>
+      </c>
+      <c r="D7" s="86" t="s">
+        <v>902</v>
+      </c>
+      <c r="E7" s="86" t="s">
+        <v>903</v>
+      </c>
+      <c r="F7" s="86" t="s">
+        <v>904</v>
+      </c>
+      <c r="G7" s="86" t="s">
+        <v>905</v>
+      </c>
+      <c r="H7" s="86" t="s">
         <v>906</v>
-      </c>
-      <c r="C7" s="86" t="s">
-        <v>907</v>
-      </c>
-      <c r="D7" s="86" t="s">
-        <v>908</v>
-      </c>
-      <c r="E7" s="86" t="s">
-        <v>909</v>
-      </c>
-      <c r="F7" s="86" t="s">
-        <v>910</v>
-      </c>
-      <c r="G7" s="86" t="s">
-        <v>911</v>
-      </c>
-      <c r="H7" s="86" t="s">
-        <v>912</v>
       </c>
     </row>
     <row r="8" spans="1:8" ht="13.5" customHeight="1">
@@ -34615,7 +34678,7 @@
     </row>
     <row r="12" spans="1:8" s="90" customFormat="1" ht="15.75" customHeight="1">
       <c r="A12" s="96" t="s">
-        <v>913</v>
+        <v>907</v>
       </c>
       <c r="B12" s="96"/>
       <c r="C12" s="96"/>
@@ -34628,13 +34691,13 @@
         <v>98</v>
       </c>
       <c r="B13" s="86" t="s">
-        <v>914</v>
+        <v>908</v>
       </c>
       <c r="C13" s="86" t="s">
-        <v>915</v>
+        <v>909</v>
       </c>
       <c r="D13" s="86" t="s">
-        <v>916</v>
+        <v>910</v>
       </c>
       <c r="E13" s="86" t="s">
         <v>99</v>
@@ -34648,7 +34711,7 @@
         <v>45952</v>
       </c>
       <c r="B14" s="9" t="s">
-        <v>917</v>
+        <v>911</v>
       </c>
       <c r="C14" s="9" t="s">
         <v>51</v>
@@ -34666,7 +34729,7 @@
         <v>45952</v>
       </c>
       <c r="B15" s="11" t="s">
-        <v>917</v>
+        <v>911</v>
       </c>
       <c r="C15" s="11" t="s">
         <v>51</v>
@@ -34720,7 +34783,7 @@
         <v>45970</v>
       </c>
       <c r="B18" s="9" t="s">
-        <v>917</v>
+        <v>911</v>
       </c>
       <c r="C18" s="9" t="s">
         <v>50</v>
@@ -34738,7 +34801,7 @@
         <v>45970</v>
       </c>
       <c r="B19" s="11" t="s">
-        <v>917</v>
+        <v>911</v>
       </c>
       <c r="C19" s="11" t="s">
         <v>50</v>
@@ -34756,7 +34819,7 @@
         <v>45973</v>
       </c>
       <c r="B20" s="9" t="s">
-        <v>917</v>
+        <v>911</v>
       </c>
       <c r="C20" s="9" t="s">
         <v>50</v>
@@ -34774,7 +34837,7 @@
         <v>45973</v>
       </c>
       <c r="B21" s="11" t="s">
-        <v>917</v>
+        <v>911</v>
       </c>
       <c r="C21" s="11" t="s">
         <v>49</v>
@@ -34792,7 +34855,7 @@
         <v>46058</v>
       </c>
       <c r="B22" s="9" t="s">
-        <v>917</v>
+        <v>911</v>
       </c>
       <c r="C22" s="9" t="s">
         <v>51</v>
@@ -34828,7 +34891,7 @@
         <v>46059</v>
       </c>
       <c r="B24" s="9" t="s">
-        <v>917</v>
+        <v>911</v>
       </c>
       <c r="C24" s="9" t="s">
         <v>49</v>
@@ -34864,7 +34927,7 @@
         <v>46093</v>
       </c>
       <c r="B26" s="9" t="s">
-        <v>917</v>
+        <v>911</v>
       </c>
       <c r="C26" s="9" t="s">
         <v>50</v>
@@ -34882,7 +34945,7 @@
         <v>46093</v>
       </c>
       <c r="B27" s="11" t="s">
-        <v>917</v>
+        <v>911</v>
       </c>
       <c r="C27" s="11" t="s">
         <v>51</v>
@@ -34965,7 +35028,7 @@
     </row>
     <row r="58" spans="2:2" ht="13.5" customHeight="1">
       <c r="B58" s="6" t="s">
-        <v>918</v>
+        <v>912</v>
       </c>
     </row>
   </sheetData>
@@ -34995,7 +35058,7 @@
   <sheetData>
     <row r="1" spans="1:7" ht="13.5" customHeight="1">
       <c r="A1" s="93" t="s">
-        <v>919</v>
+        <v>913</v>
       </c>
     </row>
     <row r="3" spans="1:7" s="87" customFormat="1" ht="13.5" customHeight="1">
@@ -35003,22 +35066,22 @@
         <v>42</v>
       </c>
       <c r="B3" s="86" t="s">
-        <v>920</v>
+        <v>914</v>
       </c>
       <c r="C3" s="86" t="s">
-        <v>905</v>
+        <v>899</v>
       </c>
       <c r="D3" s="86" t="s">
-        <v>921</v>
+        <v>915</v>
       </c>
       <c r="E3" s="86" t="s">
-        <v>922</v>
+        <v>916</v>
       </c>
       <c r="F3" s="86" t="s">
-        <v>923</v>
+        <v>917</v>
       </c>
       <c r="G3" s="86" t="s">
-        <v>924</v>
+        <v>918</v>
       </c>
     </row>
     <row r="4" spans="1:7" ht="13.5" customHeight="1">
@@ -35035,11 +35098,11 @@
       </c>
       <c r="D4" s="9">
         <f>Summary!$B$4*C4</f>
-        <v>109761.2812</v>
+        <v>111494.96119999999</v>
       </c>
       <c r="E4" s="9">
         <f>B4-D4</f>
-        <v>166557.7188</v>
+        <v>164824.03880000001</v>
       </c>
       <c r="F4" s="9">
         <f>IFERROR(SUMIFS(PartnerShares!$E$13:$E$499,PartnerShares!$D$13:$D$499,$A4,PartnerShares!$B$13:$B$499,"Cash"),0)-IFERROR(SUMIFS(PartnerShares!$E$13:$E$499,PartnerShares!$C$13:$C$499,$A4,PartnerShares!$B$13:$B$499,"Cash"),0)</f>
@@ -35047,7 +35110,7 @@
       </c>
       <c r="G4" s="88">
         <f>E4+F4</f>
-        <v>29247.69279999999</v>
+        <v>27514.012799999997</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="13.5" customHeight="1">
@@ -35056,7 +35119,7 @@
       </c>
       <c r="B5" s="11">
         <f>IFERROR(SUMIFS(Sales!$C:$C,Sales!$E:$E,$A5,Sales!$I:$I,"Completed"),0)</f>
-        <v>40369</v>
+        <v>45569</v>
       </c>
       <c r="C5" s="11">
         <f>VLOOKUP($A5,PartnerShares!$A$3:$B$5,2,FALSE())</f>
@@ -35064,11 +35127,11 @@
       </c>
       <c r="D5" s="11">
         <f>Summary!$B$4*C5</f>
-        <v>109695.4376</v>
+        <v>111428.0776</v>
       </c>
       <c r="E5" s="11">
         <f>B5-D5</f>
-        <v>-69326.437600000005</v>
+        <v>-65859.077600000004</v>
       </c>
       <c r="F5" s="11">
         <f>IFERROR(SUMIFS(PartnerShares!$E$13:$E$499,PartnerShares!$D$13:$D$499,$A5,PartnerShares!$B$13:$B$499,"Cash"),0)-IFERROR(SUMIFS(PartnerShares!$E$13:$E$499,PartnerShares!$C$13:$C$499,$A5,PartnerShares!$B$13:$B$499,"Cash"),0)</f>
@@ -35076,7 +35139,7 @@
       </c>
       <c r="G5" s="89">
         <f>E5+F5</f>
-        <v>2260.6043999999965</v>
+        <v>5727.9643999999971</v>
       </c>
     </row>
     <row r="6" spans="1:7" ht="13.5" customHeight="1">
@@ -35093,11 +35156,11 @@
       </c>
       <c r="D6" s="9">
         <f>Summary!$B$4*C6</f>
-        <v>109761.2812</v>
+        <v>111494.96119999999</v>
       </c>
       <c r="E6" s="9">
         <f>B6-D6</f>
-        <v>-97231.281199999998</v>
+        <v>-98964.961199999991</v>
       </c>
       <c r="F6" s="9">
         <f>IFERROR(SUMIFS(PartnerShares!$E$13:$E$499,PartnerShares!$D$13:$D$499,$A6,PartnerShares!$B$13:$B$499,"Cash"),0)-IFERROR(SUMIFS(PartnerShares!$E$13:$E$499,PartnerShares!$C$13:$C$499,$A6,PartnerShares!$B$13:$B$499,"Cash"),0)</f>
@@ -35105,7 +35168,7 @@
       </c>
       <c r="G6" s="88">
         <f>E6+F6</f>
-        <v>-31508.297199999986</v>
+        <v>-33241.977199999979</v>
       </c>
     </row>
     <row r="9" spans="1:7" ht="13.5" customHeight="1">
@@ -35115,27 +35178,27 @@
     </row>
     <row r="10" spans="1:7" ht="13.5" customHeight="1">
       <c r="A10" s="6" t="s">
-        <v>925</v>
+        <v>919</v>
       </c>
     </row>
     <row r="11" spans="1:7" ht="13.5" customHeight="1">
       <c r="A11" s="6" t="s">
-        <v>926</v>
+        <v>920</v>
       </c>
     </row>
     <row r="12" spans="1:7" ht="13.5" customHeight="1">
       <c r="A12" s="6" t="s">
-        <v>927</v>
+        <v>921</v>
       </c>
     </row>
     <row r="13" spans="1:7" ht="13.5" customHeight="1">
       <c r="A13" s="6" t="s">
-        <v>928</v>
+        <v>922</v>
       </c>
     </row>
     <row r="14" spans="1:7" ht="13.5" customHeight="1">
       <c r="A14" s="6" t="s">
-        <v>929</v>
+        <v>923</v>
       </c>
     </row>
   </sheetData>
